--- a/school_1/walls/vor_spartac_1_walls.xlsx
+++ b/school_1/walls/vor_spartac_1_walls.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="23268" yWindow="5568" windowWidth="5532" windowHeight="6108" activeTab="1"/>
+    <workbookView xWindow="23268" yWindow="5568" windowWidth="5532" windowHeight="6108" firstSheet="1" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Общий" sheetId="8" r:id="rId1"/>
@@ -21,13 +21,14 @@
     <sheet name="ВОР2FB" sheetId="5" r:id="rId7"/>
     <sheet name="1.030 ВОР" sheetId="7" r:id="rId8"/>
     <sheet name="1.032 ВОР" sheetId="6" r:id="rId9"/>
+    <sheet name="1.032 ВОР (2)" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="152511" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="255">
   <si>
     <t>Штукатурка цементным составом толщиной 16‐20 мм</t>
   </si>
@@ -793,6 +794,9 @@
   </si>
   <si>
     <t>Объем.</t>
+  </si>
+  <si>
+    <t>Штукатурка стен цементным, цементно-песчаным раствором с предварительной огрунтовкой / толщ. до 20 мм / высотой до 4 метров</t>
   </si>
 </sst>
 </file>
@@ -897,11 +901,15 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1750,6 +1758,24 @@
     <xf numFmtId="165" fontId="11" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1770,24 +1796,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2131,15 +2139,15 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="132" t="s">
+      <c r="A2" s="138" t="s">
         <v>251</v>
       </c>
-      <c r="B2" s="133"/>
-      <c r="C2" s="133"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="133"/>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
+      <c r="B2" s="139"/>
+      <c r="C2" s="139"/>
+      <c r="D2" s="139"/>
+      <c r="E2" s="139"/>
+      <c r="F2" s="139"/>
+      <c r="G2" s="139"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="117" t="s">
@@ -2148,13 +2156,13 @@
       <c r="B3" s="117" t="s">
         <v>249</v>
       </c>
-      <c r="C3" s="129" t="s">
+      <c r="C3" s="135" t="s">
         <v>248</v>
       </c>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="136"/>
     </row>
     <row r="4" spans="1:7" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="117" t="s">
@@ -2262,13 +2270,13 @@
       <c r="B9" s="117" t="s">
         <v>129</v>
       </c>
-      <c r="C9" s="129" t="s">
+      <c r="C9" s="135" t="s">
         <v>130</v>
       </c>
-      <c r="D9" s="130"/>
-      <c r="E9" s="130"/>
-      <c r="F9" s="130"/>
-      <c r="G9" s="131"/>
+      <c r="D9" s="136"/>
+      <c r="E9" s="136"/>
+      <c r="F9" s="136"/>
+      <c r="G9" s="137"/>
     </row>
     <row r="10" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A10" s="117" t="s">
@@ -3745,13 +3753,13 @@
       <c r="B83" s="117" t="s">
         <v>229</v>
       </c>
-      <c r="C83" s="129" t="s">
+      <c r="C83" s="135" t="s">
         <v>230</v>
       </c>
-      <c r="D83" s="130"/>
-      <c r="E83" s="130"/>
-      <c r="F83" s="130"/>
-      <c r="G83" s="131"/>
+      <c r="D83" s="136"/>
+      <c r="E83" s="136"/>
+      <c r="F83" s="136"/>
+      <c r="G83" s="137"/>
     </row>
     <row r="84" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A84" s="117" t="s">
@@ -3801,7 +3809,7 @@
         <v>113.11499999999999</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A86" s="117" t="s">
         <v>235</v>
       </c>
@@ -3831,6 +3839,556 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.5546875" customWidth="1"/>
+    <col min="2" max="2" width="54.88671875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="69"/>
+      <c r="B1" s="70" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="72"/>
+    </row>
+    <row r="2" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="73" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="63">
+        <v>1</v>
+      </c>
+      <c r="E2" s="74">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="63">
+        <v>0.1</v>
+      </c>
+      <c r="E3" s="74">
+        <f>D3*E2</f>
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="76" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="78">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E4" s="79">
+        <f>D4*E2</f>
+        <v>23.87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="80" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="81" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="82" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="83">
+        <v>1</v>
+      </c>
+      <c r="E5" s="84">
+        <v>30.17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="73" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="85" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="63">
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="74">
+        <f>E5*D6</f>
+        <v>7.5425000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="73" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="87" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="88">
+        <v>1.8</v>
+      </c>
+      <c r="E7" s="89">
+        <f>E5*D7*20</f>
+        <v>1086.1200000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="73" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="86" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="87" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="88">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E8" s="89">
+        <f>E5*D8</f>
+        <v>33.187000000000005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="90" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="91" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="92" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="93">
+        <v>1</v>
+      </c>
+      <c r="E9" s="94">
+        <v>104.41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="73" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="85" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="63">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E10" s="74">
+        <f>E9*D10</f>
+        <v>114.851</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="73" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="85" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="63">
+        <v>1.8</v>
+      </c>
+      <c r="E11" s="74">
+        <f>E9*D11*20</f>
+        <v>3758.7599999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="73" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="104" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="74">
+        <f>E9*D12</f>
+        <v>15.661499999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="75" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="95" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="78">
+        <v>1</v>
+      </c>
+      <c r="E13" s="79">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="107"/>
+      <c r="B14" s="107"/>
+      <c r="C14" s="107"/>
+      <c r="D14" s="107"/>
+      <c r="E14" s="107"/>
+      <c r="F14" s="107"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="108"/>
+      <c r="B15" s="109" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="110"/>
+      <c r="D15" s="110"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="107"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="113" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" s="107"/>
+    </row>
+    <row r="17" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="73">
+        <v>1</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="63">
+        <v>1</v>
+      </c>
+      <c r="E17" s="74">
+        <f>E9+E5</f>
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F17" s="107"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B18" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="63">
+        <v>2</v>
+      </c>
+      <c r="E18" s="74">
+        <f>E17*D18</f>
+        <v>269.15999999999997</v>
+      </c>
+      <c r="F18" s="107"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E19" s="74">
+        <f>ROUNDDOWN(E17*D19,0)</f>
+        <v>40</v>
+      </c>
+      <c r="F19" s="107"/>
+    </row>
+    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="78">
+        <v>0.15</v>
+      </c>
+      <c r="E20" s="79">
+        <f>D20*E17</f>
+        <v>20.186999999999998</v>
+      </c>
+      <c r="F20" s="107"/>
+    </row>
+    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="114"/>
+      <c r="B21" s="114"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="114"/>
+      <c r="E21" s="114"/>
+      <c r="F21" s="107"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="108"/>
+      <c r="B22" s="109" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="110"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="111"/>
+      <c r="F22" s="107"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="113" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="107"/>
+    </row>
+    <row r="24" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="73">
+        <v>1</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="63">
+        <v>1</v>
+      </c>
+      <c r="E24" s="74">
+        <f>E17</f>
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F24" s="107"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B25" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E25" s="74">
+        <f>E24*D25</f>
+        <v>20.186999999999998</v>
+      </c>
+      <c r="F25" s="107"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="65" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E26" s="74">
+        <f>ROUNDDOWN(E24*D26,0)</f>
+        <v>40</v>
+      </c>
+      <c r="F26" s="107"/>
+    </row>
+    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" s="105" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="78">
+        <v>1</v>
+      </c>
+      <c r="E27" s="79">
+        <f>D27*E24</f>
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F27" s="107"/>
+    </row>
+    <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="107"/>
+      <c r="B28" s="107"/>
+      <c r="C28" s="107"/>
+      <c r="D28" s="107"/>
+      <c r="E28" s="107"/>
+      <c r="F28" s="107"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="108"/>
+      <c r="B29" s="109" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="110"/>
+      <c r="D29" s="110"/>
+      <c r="E29" s="111"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30" s="113" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="73">
+        <v>1</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="63">
+        <v>1</v>
+      </c>
+      <c r="E31" s="74">
+        <f>E24</f>
+        <v>134.57999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B32" s="85" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E32" s="74">
+        <f>D32*E31</f>
+        <v>20.186999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="95" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="78">
+        <v>0.3</v>
+      </c>
+      <c r="E33" s="79">
+        <f>D33*E31</f>
+        <v>40.373999999999995</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -3845,24 +4403,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="132" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="140" t="s">
+      <c r="B1" s="133" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="141" t="s">
+      <c r="C1" s="134" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="136" t="s">
+      <c r="A2" s="129" t="s">
         <v>252</v>
       </c>
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="130" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="138">
+      <c r="C2" s="131">
         <v>675.39</v>
       </c>
     </row>
@@ -5168,11 +5726,11 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="134"/>
-      <c r="B4" s="134"/>
-      <c r="C4" s="134"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="134"/>
+      <c r="A4" s="140"/>
+      <c r="B4" s="140"/>
+      <c r="C4" s="140"/>
+      <c r="D4" s="140"/>
+      <c r="E4" s="140"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="58"/>
@@ -5254,11 +5812,11 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="135"/>
-      <c r="B10" s="135"/>
-      <c r="C10" s="135"/>
-      <c r="D10" s="135"/>
-      <c r="E10" s="135"/>
+      <c r="A10" s="141"/>
+      <c r="B10" s="141"/>
+      <c r="C10" s="141"/>
+      <c r="D10" s="141"/>
+      <c r="E10" s="141"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="58"/>
@@ -5341,11 +5899,11 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="134"/>
-      <c r="B16" s="134"/>
-      <c r="C16" s="134"/>
-      <c r="D16" s="134"/>
-      <c r="E16" s="134"/>
+      <c r="A16" s="140"/>
+      <c r="B16" s="140"/>
+      <c r="C16" s="140"/>
+      <c r="D16" s="140"/>
+      <c r="E16" s="140"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="58"/>
@@ -5551,11 +6109,11 @@
       <c r="G6" s="67"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="134"/>
-      <c r="B7" s="134"/>
-      <c r="C7" s="134"/>
-      <c r="D7" s="134"/>
-      <c r="E7" s="134"/>
+      <c r="A7" s="140"/>
+      <c r="B7" s="140"/>
+      <c r="C7" s="140"/>
+      <c r="D7" s="140"/>
+      <c r="E7" s="140"/>
       <c r="G7" s="67"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -5643,11 +6201,11 @@
       <c r="G12" s="66"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="135"/>
-      <c r="B13" s="135"/>
-      <c r="C13" s="135"/>
-      <c r="D13" s="135"/>
-      <c r="E13" s="135"/>
+      <c r="A13" s="141"/>
+      <c r="B13" s="141"/>
+      <c r="C13" s="141"/>
+      <c r="D13" s="141"/>
+      <c r="E13" s="141"/>
       <c r="G13" s="66"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -5736,11 +6294,11 @@
       <c r="G18" s="66"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="134"/>
-      <c r="B19" s="134"/>
-      <c r="C19" s="134"/>
-      <c r="D19" s="134"/>
-      <c r="E19" s="134"/>
+      <c r="A19" s="140"/>
+      <c r="B19" s="140"/>
+      <c r="C19" s="140"/>
+      <c r="D19" s="140"/>
+      <c r="E19" s="140"/>
       <c r="G19" s="66"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -6422,7 +6980,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5546875" customWidth="1"/>
@@ -6441,7 +6999,7 @@
       <c r="D1" s="71"/>
       <c r="E1" s="72"/>
     </row>
-    <row r="2" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="73" t="s">
         <v>82</v>
       </c>
@@ -6458,510 +7016,332 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="73" t="s">
+    <row r="3" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="80" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="81" t="s">
+        <v>254</v>
+      </c>
+      <c r="C3" s="82" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="83">
+        <v>1</v>
+      </c>
+      <c r="E3" s="84">
+        <v>134.57999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="107"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="108"/>
+      <c r="B5" s="109" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="111"/>
+      <c r="F5" s="107"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="113" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="107"/>
+    </row>
+    <row r="7" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="73">
+        <v>1</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="63">
+        <v>1</v>
+      </c>
+      <c r="E7" s="74">
+        <f>E3</f>
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F7" s="107"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="63">
+        <v>2</v>
+      </c>
+      <c r="E8" s="74">
+        <f>E7*D8</f>
+        <v>269.15999999999997</v>
+      </c>
+      <c r="F8" s="107"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="17" t="s">
+      <c r="B9" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E9" s="74">
+        <f>ROUNDDOWN(E7*D9,0)</f>
+        <v>40</v>
+      </c>
+      <c r="F9" s="107"/>
+    </row>
+    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="63">
-        <v>0.1</v>
-      </c>
-      <c r="E3" s="74">
-        <f>D3*E2</f>
-        <v>2.17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="75" t="s">
+      <c r="D10" s="78">
+        <v>0.15</v>
+      </c>
+      <c r="E10" s="79">
+        <f>D10*E7</f>
+        <v>20.186999999999998</v>
+      </c>
+      <c r="F10" s="107"/>
+    </row>
+    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="114"/>
+      <c r="B11" s="114"/>
+      <c r="C11" s="114"/>
+      <c r="D11" s="114"/>
+      <c r="E11" s="114"/>
+      <c r="F11" s="107"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="108"/>
+      <c r="B12" s="109" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="110"/>
+      <c r="D12" s="110"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="107"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="113" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="107"/>
+    </row>
+    <row r="14" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="73">
+        <v>1</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="63">
+        <v>1</v>
+      </c>
+      <c r="E14" s="74">
+        <f>E7</f>
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F14" s="107"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B15" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E15" s="74">
+        <f>E14*D15</f>
+        <v>20.186999999999998</v>
+      </c>
+      <c r="F15" s="107"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="65" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E16" s="74">
+        <f>ROUNDDOWN(E14*D16,0)</f>
+        <v>40</v>
+      </c>
+      <c r="F16" s="107"/>
+    </row>
+    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="76" t="s">
-        <v>85</v>
-      </c>
-      <c r="C4" s="77" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" s="78">
+      <c r="B17" s="105" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="78">
+        <v>1</v>
+      </c>
+      <c r="E17" s="79">
+        <f>D17*E14</f>
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F17" s="107"/>
+    </row>
+    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="107"/>
+      <c r="B18" s="107"/>
+      <c r="C18" s="107"/>
+      <c r="D18" s="107"/>
+      <c r="E18" s="107"/>
+      <c r="F18" s="107"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="108"/>
+      <c r="B19" s="109" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="110"/>
+      <c r="D19" s="110"/>
+      <c r="E19" s="111"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="113" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="73">
+        <v>1</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="63">
+        <v>1</v>
+      </c>
+      <c r="E21" s="74">
+        <f>E14</f>
+        <v>134.57999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="73">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E4" s="79">
-        <f>D4*E2</f>
-        <v>23.87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="80" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" s="81" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" s="82" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="83">
-        <v>1</v>
-      </c>
-      <c r="E5" s="84">
-        <v>30.17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="73" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="85" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="17" t="s">
+      <c r="B22" s="85" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="63">
-        <v>0.25</v>
-      </c>
-      <c r="E6" s="74">
-        <f>E5*D6</f>
-        <v>7.5425000000000004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="73" t="s">
-        <v>88</v>
-      </c>
-      <c r="B7" s="86" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="87" t="s">
+      <c r="D22" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E22" s="74">
+        <f>D22*E21</f>
+        <v>20.186999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="95" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="88">
-        <v>1.8</v>
-      </c>
-      <c r="E7" s="89">
-        <f>E5*D7*20</f>
-        <v>1086.1200000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="73" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="86" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="87" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" s="88">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E8" s="89">
-        <f>E5*D8</f>
-        <v>33.187000000000005</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="90" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="91" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9" s="92" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="93">
-        <v>1</v>
-      </c>
-      <c r="E9" s="94">
-        <v>104.41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="73" t="s">
-        <v>90</v>
-      </c>
-      <c r="B10" s="85" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" s="63">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E10" s="74">
-        <f>E9*D10</f>
-        <v>114.851</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="73" t="s">
-        <v>91</v>
-      </c>
-      <c r="B11" s="85" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="63">
-        <v>1.8</v>
-      </c>
-      <c r="E11" s="74">
-        <f>E9*D11*20</f>
-        <v>3758.7599999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="73" t="s">
-        <v>92</v>
-      </c>
-      <c r="B12" s="104" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E12" s="74">
-        <f>E9*D12</f>
-        <v>15.661499999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="75" t="s">
-        <v>93</v>
-      </c>
-      <c r="B13" s="95" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="77" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="78">
-        <v>1</v>
-      </c>
-      <c r="E13" s="79">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="107"/>
-      <c r="B14" s="107"/>
-      <c r="C14" s="107"/>
-      <c r="D14" s="107"/>
-      <c r="E14" s="107"/>
-      <c r="F14" s="107"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="108"/>
-      <c r="B15" s="109" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="110"/>
-      <c r="D15" s="110"/>
-      <c r="E15" s="111"/>
-      <c r="F15" s="107"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="113" t="s">
-        <v>51</v>
-      </c>
-      <c r="F16" s="107"/>
-    </row>
-    <row r="17" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="73">
-        <v>1</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="63">
-        <v>1</v>
-      </c>
-      <c r="E17" s="74">
-        <f>E9+E5</f>
-        <v>134.57999999999998</v>
-      </c>
-      <c r="F17" s="107"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B18" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="63">
-        <v>2</v>
-      </c>
-      <c r="E18" s="74">
-        <f>E17*D18</f>
-        <v>269.15999999999997</v>
-      </c>
-      <c r="F18" s="107"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" s="63">
+      <c r="D23" s="78">
         <v>0.3</v>
       </c>
-      <c r="E19" s="74">
-        <f>ROUNDDOWN(E17*D19,0)</f>
-        <v>40</v>
-      </c>
-      <c r="F19" s="107"/>
-    </row>
-    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="75" t="s">
-        <v>72</v>
-      </c>
-      <c r="B20" s="106" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="78">
-        <v>0.15</v>
-      </c>
-      <c r="E20" s="79">
-        <f>D20*E17</f>
-        <v>20.186999999999998</v>
-      </c>
-      <c r="F20" s="107"/>
-    </row>
-    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="114"/>
-      <c r="B21" s="114"/>
-      <c r="C21" s="114"/>
-      <c r="D21" s="114"/>
-      <c r="E21" s="114"/>
-      <c r="F21" s="107"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="108"/>
-      <c r="B22" s="109" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" s="110"/>
-      <c r="D22" s="110"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="107"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23" s="113" t="s">
-        <v>51</v>
-      </c>
-      <c r="F23" s="107"/>
-    </row>
-    <row r="24" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="73">
-        <v>1</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="63">
-        <v>1</v>
-      </c>
-      <c r="E24" s="74">
-        <f>E17</f>
-        <v>134.57999999999998</v>
-      </c>
-      <c r="F24" s="107"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B25" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E25" s="74">
-        <f>E24*D25</f>
-        <v>20.186999999999998</v>
-      </c>
-      <c r="F25" s="107"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="65" t="s">
-        <v>106</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="63">
-        <v>0.3</v>
-      </c>
-      <c r="E26" s="74">
-        <f>ROUNDDOWN(E24*D26,0)</f>
-        <v>40</v>
-      </c>
-      <c r="F26" s="107"/>
-    </row>
-    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="75" t="s">
-        <v>72</v>
-      </c>
-      <c r="B27" s="105" t="s">
-        <v>107</v>
-      </c>
-      <c r="C27" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" s="78">
-        <v>1</v>
-      </c>
-      <c r="E27" s="79">
-        <f>D27*E24</f>
-        <v>134.57999999999998</v>
-      </c>
-      <c r="F27" s="107"/>
-    </row>
-    <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="107"/>
-      <c r="B28" s="107"/>
-      <c r="C28" s="107"/>
-      <c r="D28" s="107"/>
-      <c r="E28" s="107"/>
-      <c r="F28" s="107"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="108"/>
-      <c r="B29" s="109" t="s">
-        <v>60</v>
-      </c>
-      <c r="C29" s="110"/>
-      <c r="D29" s="110"/>
-      <c r="E29" s="111"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D30" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E30" s="113" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="73">
-        <v>1</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31" s="63">
-        <v>1</v>
-      </c>
-      <c r="E31" s="74">
-        <f>E24</f>
-        <v>134.57999999999998</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B32" s="85" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D32" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E32" s="74">
-        <f>D32*E31</f>
-        <v>20.186999999999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="75" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" s="95" t="s">
-        <v>97</v>
-      </c>
-      <c r="C33" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D33" s="78">
-        <v>0.3</v>
-      </c>
-      <c r="E33" s="79">
-        <f>D33*E31</f>
+      <c r="E23" s="79">
+        <f>D23*E21</f>
         <v>40.373999999999995</v>
       </c>
     </row>

--- a/school_1/walls/vor_spartac_1_walls.xlsx
+++ b/school_1/walls/vor_spartac_1_walls.xlsx
@@ -9,26 +9,29 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="23268" yWindow="5568" windowWidth="5532" windowHeight="6108" firstSheet="1" activeTab="8"/>
+    <workbookView xWindow="23268" yWindow="5568" windowWidth="5532" windowHeight="6108" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Общий" sheetId="8" r:id="rId1"/>
-    <sheet name="1-С-Ш1" sheetId="9" r:id="rId2"/>
-    <sheet name="Пример" sheetId="1" r:id="rId3"/>
-    <sheet name="Спортзал" sheetId="2" r:id="rId4"/>
-    <sheet name="библиотека" sheetId="3" r:id="rId5"/>
-    <sheet name="Библ откосы" sheetId="4" r:id="rId6"/>
-    <sheet name="ВОР2FB" sheetId="5" r:id="rId7"/>
-    <sheet name="1.030 ВОР" sheetId="7" r:id="rId8"/>
-    <sheet name="1.032 ВОР" sheetId="6" r:id="rId9"/>
-    <sheet name="1.032 ВОР (2)" sheetId="10" r:id="rId10"/>
+    <sheet name="4-С-Ш1" sheetId="13" r:id="rId1"/>
+    <sheet name="3-С-Ш1фин" sheetId="12" r:id="rId2"/>
+    <sheet name="2-С-Ш1, баз" sheetId="11" r:id="rId3"/>
+    <sheet name="1-С-Ш1, ГКЛ" sheetId="9" r:id="rId4"/>
+    <sheet name="Общий" sheetId="8" r:id="rId5"/>
+    <sheet name="Пример" sheetId="1" r:id="rId6"/>
+    <sheet name="Спортзал" sheetId="2" r:id="rId7"/>
+    <sheet name="библиотека" sheetId="3" r:id="rId8"/>
+    <sheet name="Библ откосы" sheetId="4" r:id="rId9"/>
+    <sheet name="ВОР2FB" sheetId="5" r:id="rId10"/>
+    <sheet name="1.030 ВОР" sheetId="7" r:id="rId11"/>
+    <sheet name="1.032 ВОР" sheetId="6" r:id="rId12"/>
+    <sheet name="1.032 ВОР (2)" sheetId="10" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="152511" refMode="R1C1"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="274">
   <si>
     <t>Штукатурка цементным составом толщиной 16‐20 мм</t>
   </si>
@@ -793,10 +796,67 @@
     <t>Устройство перегородок на металлическом каркасе по системе Knauf / С-112 / А2-12, А2-5, А2-25</t>
   </si>
   <si>
-    <t>Объем.</t>
-  </si>
-  <si>
     <t>Штукатурка стен цементным, цементно-песчаным раствором с предварительной огрунтовкой / толщ. до 20 мм / высотой до 4 метров</t>
+  </si>
+  <si>
+    <t>Прочие материалы для перегородок из ГКЛ (лента, шпатлевка, грунтовка, шуруп, дюбель и пр.) / одинарный каркас / 2 слоя облицовки</t>
+  </si>
+  <si>
+    <t>Профиль_/направляющий/75*40*0,60/3м</t>
+  </si>
+  <si>
+    <t>Профиль ЛСТК ВП U 150-63-1,5 сталь350цинк275г/м2 L=3000мм</t>
+  </si>
+  <si>
+    <t>Профиль_ / стоечный  / 75*50*0,6 / 2415</t>
+  </si>
+  <si>
+    <t>Профиль ЛСТК ВП С 150-50-1,5 сталь350цинк275г/м2 L=3200мм</t>
+  </si>
+  <si>
+    <t>Гипсовые строительные плиты_ / влагостойкий и огнестойкий / 12,5*1200*2500</t>
+  </si>
+  <si>
+    <t>КНАУФ "Суперлист" ГВЛ 12,5мм</t>
+  </si>
+  <si>
+    <t>Плита минераловатная_ / Knauf Insulation Aquastatik TS 034</t>
+  </si>
+  <si>
+    <t>м3</t>
+  </si>
+  <si>
+    <t>Шпаклевка базовая</t>
+  </si>
+  <si>
+    <t>Уголок малярный_/перфорированный/25*25*3000мм</t>
+  </si>
+  <si>
+    <t>Шпаклевка финишная</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>Устройство противопожарных стен 2-го типа</t>
+  </si>
+  <si>
+    <t>Теплоизоляция КНАУФ Инсулейшн</t>
+  </si>
+  <si>
+    <t>Описание</t>
+  </si>
+  <si>
+    <t>Наименование работ</t>
+  </si>
+  <si>
+    <t>Устройство файерборд</t>
+  </si>
+  <si>
+    <t>(2 слоя)</t>
   </si>
 </sst>
 </file>
@@ -807,7 +867,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -905,10 +965,78 @@
       <charset val="204"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
       <charset val="204"/>
     </font>
   </fonts>
@@ -1386,11 +1514,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="171">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1758,23 +1887,96 @@
     <xf numFmtId="165" fontId="11" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="21" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="21" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1797,10 +1999,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1"/>
+    <cellStyle name="Обычный 3" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2102,6 +2317,2488 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.21875" style="159" customWidth="1"/>
+    <col min="2" max="2" width="54.77734375" style="142" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" style="142" customWidth="1"/>
+    <col min="4" max="4" width="18.21875" style="142" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="142"/>
+    <col min="6" max="6" width="17.77734375" style="142" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="142"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="141" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="150" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1" s="150" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1" s="150" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="150" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1" s="150" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="130">
+        <v>1</v>
+      </c>
+      <c r="B2" s="151" t="s">
+        <v>272</v>
+      </c>
+      <c r="C2" s="152" t="s">
+        <v>273</v>
+      </c>
+      <c r="D2" s="152" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="153">
+        <v>1</v>
+      </c>
+      <c r="F2" s="154">
+        <f>(2.1*2+1.15)*0.125*17</f>
+        <v>11.368749999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="130">
+        <v>2</v>
+      </c>
+      <c r="B3" s="151" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="152" t="s">
+        <v>263</v>
+      </c>
+      <c r="D3" s="152" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="153">
+        <v>1</v>
+      </c>
+      <c r="F3" s="154">
+        <f>F2</f>
+        <v>11.368749999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="146" t="s">
+        <v>267</v>
+      </c>
+      <c r="B4" s="155" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="152"/>
+      <c r="D4" s="156" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="157">
+        <v>1.5</v>
+      </c>
+      <c r="F4" s="158">
+        <f>$F$3*E4</f>
+        <v>17.053124999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="146" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="155" t="s">
+        <v>264</v>
+      </c>
+      <c r="C5" s="152"/>
+      <c r="D5" s="156" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="157">
+        <v>0.3</v>
+      </c>
+      <c r="F5" s="158">
+        <f t="shared" ref="F5:F9" si="0">$F$3*E5</f>
+        <v>3.4106249999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="146" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="155" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="152"/>
+      <c r="D6" s="156" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="157">
+        <v>0.15</v>
+      </c>
+      <c r="F6" s="158">
+        <f t="shared" si="0"/>
+        <v>1.7053124999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="130">
+        <v>3</v>
+      </c>
+      <c r="B7" s="151" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="152" t="s">
+        <v>265</v>
+      </c>
+      <c r="D7" s="152" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="153">
+        <v>1</v>
+      </c>
+      <c r="F7" s="158">
+        <f t="shared" si="0"/>
+        <v>11.368749999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="146" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="155" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="152"/>
+      <c r="D8" s="156" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="157">
+        <v>0.15</v>
+      </c>
+      <c r="F8" s="158">
+        <f t="shared" si="0"/>
+        <v>1.7053124999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="146" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="155" t="s">
+        <v>201</v>
+      </c>
+      <c r="C9" s="152"/>
+      <c r="D9" s="156" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="157">
+        <v>1.5</v>
+      </c>
+      <c r="F9" s="158">
+        <f t="shared" si="0"/>
+        <v>17.053124999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="51" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="58"/>
+      <c r="B1" s="59" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="G1" s="67"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="67"/>
+    </row>
+    <row r="3" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="62">
+        <v>1</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="63">
+        <v>1</v>
+      </c>
+      <c r="E3" s="17">
+        <v>37.44</v>
+      </c>
+      <c r="F3" s="68"/>
+      <c r="G3" s="67"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="63">
+        <v>1</v>
+      </c>
+      <c r="E4" s="17">
+        <v>22</v>
+      </c>
+      <c r="F4" s="68"/>
+      <c r="G4" s="67"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="63">
+        <v>1</v>
+      </c>
+      <c r="E5" s="17">
+        <v>201</v>
+      </c>
+      <c r="F5" s="68"/>
+      <c r="G5" s="67"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="62" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="63">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E6" s="17">
+        <v>41.183999999999997</v>
+      </c>
+      <c r="F6" s="68"/>
+      <c r="G6" s="67"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="165"/>
+      <c r="B7" s="165"/>
+      <c r="C7" s="165"/>
+      <c r="D7" s="165"/>
+      <c r="E7" s="165"/>
+      <c r="G7" s="67"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="58"/>
+      <c r="B8" s="59" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="G8" s="66"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="66"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="62">
+        <v>1</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="63">
+        <v>1</v>
+      </c>
+      <c r="E10" s="17">
+        <v>37.44</v>
+      </c>
+      <c r="G10" s="66"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="62">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B11" s="64" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="63">
+        <v>1.8</v>
+      </c>
+      <c r="E11" s="17">
+        <f>E10*D11</f>
+        <v>67.391999999999996</v>
+      </c>
+      <c r="G11" s="66"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="17">
+        <f>E10*D12</f>
+        <v>5.6159999999999997</v>
+      </c>
+      <c r="G12" s="66"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="166"/>
+      <c r="B13" s="166"/>
+      <c r="C13" s="166"/>
+      <c r="D13" s="166"/>
+      <c r="E13" s="166"/>
+      <c r="G13" s="66"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="58"/>
+      <c r="B14" s="59" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="G14" s="66"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15" s="66"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="62">
+        <v>1</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="63">
+        <v>1</v>
+      </c>
+      <c r="E16" s="17">
+        <f>E10</f>
+        <v>37.44</v>
+      </c>
+      <c r="G16" s="66"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="62">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B17" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E17" s="17">
+        <f>E16*D17</f>
+        <v>5.6159999999999997</v>
+      </c>
+      <c r="G17" s="66"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="65" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="63">
+        <v>1.8</v>
+      </c>
+      <c r="E18" s="17">
+        <f>E16*D18</f>
+        <v>67.391999999999996</v>
+      </c>
+      <c r="G18" s="66"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="165"/>
+      <c r="B19" s="165"/>
+      <c r="C19" s="165"/>
+      <c r="D19" s="165"/>
+      <c r="E19" s="165"/>
+      <c r="G19" s="66"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="58"/>
+      <c r="B20" s="59" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="G20" s="66"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" s="66"/>
+    </row>
+    <row r="22" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="62">
+        <v>1</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="63">
+        <v>1</v>
+      </c>
+      <c r="E22" s="17">
+        <v>37.44</v>
+      </c>
+      <c r="G22" s="66"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="62">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B23" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E23" s="17">
+        <f>E22*D23</f>
+        <v>5.6159999999999997</v>
+      </c>
+      <c r="G23" s="66"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E24" s="17">
+        <f>E22*D24</f>
+        <v>11.231999999999999</v>
+      </c>
+      <c r="G24" s="66"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A13:E13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.5546875" customWidth="1"/>
+    <col min="2" max="2" width="54.88671875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="58"/>
+      <c r="B1" s="116" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+    </row>
+    <row r="2" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="60" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="62">
+        <v>1</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="63">
+        <v>1</v>
+      </c>
+      <c r="E3" s="17">
+        <v>16.54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" s="63">
+        <v>1</v>
+      </c>
+      <c r="E4" s="17">
+        <f>E3</f>
+        <v>16.54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="63">
+        <v>1.42</v>
+      </c>
+      <c r="E5" s="17">
+        <f>D5*E3*2</f>
+        <v>46.973599999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="62" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="63">
+        <v>2.1</v>
+      </c>
+      <c r="E6" s="17">
+        <f>D6*E3</f>
+        <v>34.734000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="62" t="s">
+        <v>120</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="63">
+        <v>4.07</v>
+      </c>
+      <c r="E7" s="17">
+        <f>D7*E3</f>
+        <v>67.317800000000005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="107"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="96"/>
+      <c r="B9" s="97" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="98"/>
+      <c r="D9" s="98"/>
+      <c r="E9" s="99"/>
+    </row>
+    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="100" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="101" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="102" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="102" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="103" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="90">
+        <v>1</v>
+      </c>
+      <c r="B11" s="91" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="92" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="93">
+        <v>1</v>
+      </c>
+      <c r="E11" s="94">
+        <v>33.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B12" s="85" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E12" s="74">
+        <f>E11*D12</f>
+        <v>9.9749999999999996</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="85" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="63">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E13" s="74">
+        <f>D13*E11</f>
+        <v>36.575000000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="107"/>
+      <c r="B14" s="107"/>
+      <c r="C14" s="107"/>
+      <c r="D14" s="107"/>
+      <c r="E14" s="107"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="108"/>
+      <c r="B15" s="109" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="110"/>
+      <c r="D15" s="110"/>
+      <c r="E15" s="111"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="113" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="73">
+        <v>1</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="63">
+        <v>1</v>
+      </c>
+      <c r="E17" s="74">
+        <f>E3</f>
+        <v>16.54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B18" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="63">
+        <v>2</v>
+      </c>
+      <c r="E18" s="74">
+        <f>E17*D18</f>
+        <v>33.08</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E19" s="74">
+        <f>ROUNDDOWN(E17*D19,0)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="78">
+        <v>0.15</v>
+      </c>
+      <c r="E20" s="79">
+        <f>D20*E17</f>
+        <v>2.4809999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="107"/>
+      <c r="B21" s="107"/>
+      <c r="C21" s="107"/>
+      <c r="D21" s="107"/>
+      <c r="E21" s="107"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="108"/>
+      <c r="B22" s="109" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" s="110"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="111"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="113" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="73">
+        <v>1</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="63">
+        <v>1</v>
+      </c>
+      <c r="E24" s="74">
+        <f>79.16+E3</f>
+        <v>95.699999999999989</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B25" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E25" s="115">
+        <f>E24*D25</f>
+        <v>14.354999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="65" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="63">
+        <v>2</v>
+      </c>
+      <c r="E26" s="74">
+        <f>E24*D26</f>
+        <v>191.39999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="107"/>
+      <c r="B27" s="107"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="107"/>
+      <c r="E27" s="107"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="108"/>
+      <c r="B28" s="109" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" s="110"/>
+      <c r="D28" s="110"/>
+      <c r="E28" s="111"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29" s="113" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="73">
+        <v>1</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" s="63">
+        <v>1</v>
+      </c>
+      <c r="E30" s="74">
+        <v>970.52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B31" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E31" s="74">
+        <f>E30*D31</f>
+        <v>145.578</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="105" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="78">
+        <v>2</v>
+      </c>
+      <c r="E32" s="79">
+        <f>D32*E30</f>
+        <v>1941.04</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="107"/>
+      <c r="B33" s="107"/>
+      <c r="C33" s="107"/>
+      <c r="D33" s="107"/>
+      <c r="E33" s="107"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="96"/>
+      <c r="B34" s="97" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" s="98"/>
+      <c r="D34" s="98"/>
+      <c r="E34" s="99"/>
+    </row>
+    <row r="35" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="100" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" s="101" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="102" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="102" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="103" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A36" s="90">
+        <v>1</v>
+      </c>
+      <c r="B36" s="91" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" s="93">
+        <v>1</v>
+      </c>
+      <c r="E36" s="94">
+        <f>E24+E30</f>
+        <v>1066.22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B37" s="86" t="s">
+        <v>96</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" s="88">
+        <v>0.15</v>
+      </c>
+      <c r="E37" s="89">
+        <f>D37*E36</f>
+        <v>159.93299999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="95" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D38" s="78">
+        <v>0.3</v>
+      </c>
+      <c r="E38" s="79">
+        <f>D38*E36</f>
+        <v>319.86599999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.5546875" customWidth="1"/>
+    <col min="2" max="2" width="54.88671875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="69"/>
+      <c r="B1" s="70" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="72"/>
+    </row>
+    <row r="2" spans="1:6" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="73" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="63">
+        <v>1</v>
+      </c>
+      <c r="E2" s="74">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="80" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="81" t="s">
+        <v>253</v>
+      </c>
+      <c r="C3" s="82" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="83">
+        <v>1</v>
+      </c>
+      <c r="E3" s="84">
+        <v>134.57999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="107"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="108"/>
+      <c r="B5" s="109" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="111"/>
+      <c r="F5" s="107"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="113" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="107"/>
+    </row>
+    <row r="7" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="73">
+        <v>1</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="63">
+        <v>1</v>
+      </c>
+      <c r="E7" s="74">
+        <f>E3</f>
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F7" s="107"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="63">
+        <v>2</v>
+      </c>
+      <c r="E8" s="74">
+        <f>E7*D8</f>
+        <v>269.15999999999997</v>
+      </c>
+      <c r="F8" s="107"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E9" s="74">
+        <f>ROUNDDOWN(E7*D9,0)</f>
+        <v>40</v>
+      </c>
+      <c r="F9" s="107"/>
+    </row>
+    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="78">
+        <v>0.15</v>
+      </c>
+      <c r="E10" s="79">
+        <f>D10*E7</f>
+        <v>20.186999999999998</v>
+      </c>
+      <c r="F10" s="107"/>
+    </row>
+    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="114"/>
+      <c r="B11" s="114"/>
+      <c r="C11" s="114"/>
+      <c r="D11" s="114"/>
+      <c r="E11" s="114"/>
+      <c r="F11" s="107"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="108"/>
+      <c r="B12" s="109" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="110"/>
+      <c r="D12" s="110"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="107"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="113" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="107"/>
+    </row>
+    <row r="14" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="73">
+        <v>1</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="63">
+        <v>1</v>
+      </c>
+      <c r="E14" s="74">
+        <f>E7</f>
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F14" s="107"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B15" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E15" s="74">
+        <f>E14*D15</f>
+        <v>20.186999999999998</v>
+      </c>
+      <c r="F15" s="107"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="65" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E16" s="74">
+        <f>ROUNDDOWN(E14*D16,0)</f>
+        <v>40</v>
+      </c>
+      <c r="F16" s="107"/>
+    </row>
+    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="105" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="78">
+        <v>1</v>
+      </c>
+      <c r="E17" s="79">
+        <f>D17*E14</f>
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F17" s="107"/>
+    </row>
+    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="107"/>
+      <c r="B18" s="107"/>
+      <c r="C18" s="107"/>
+      <c r="D18" s="107"/>
+      <c r="E18" s="107"/>
+      <c r="F18" s="107"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="108"/>
+      <c r="B19" s="109" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="110"/>
+      <c r="D19" s="110"/>
+      <c r="E19" s="111"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="113" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="73">
+        <v>1</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="63">
+        <v>1</v>
+      </c>
+      <c r="E21" s="74">
+        <f>E14</f>
+        <v>134.57999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B22" s="85" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E22" s="74">
+        <f>D22*E21</f>
+        <v>20.186999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="95" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="78">
+        <v>0.3</v>
+      </c>
+      <c r="E23" s="79">
+        <f>D23*E21</f>
+        <v>40.373999999999995</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.5546875" customWidth="1"/>
+    <col min="2" max="2" width="54.88671875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="69"/>
+      <c r="B1" s="70" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="72"/>
+    </row>
+    <row r="2" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="73" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="63">
+        <v>1</v>
+      </c>
+      <c r="E2" s="74">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="63">
+        <v>0.1</v>
+      </c>
+      <c r="E3" s="74">
+        <f>D3*E2</f>
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="76" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="78">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E4" s="79">
+        <f>D4*E2</f>
+        <v>23.87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="80" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="81" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="82" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="83">
+        <v>1</v>
+      </c>
+      <c r="E5" s="84">
+        <v>30.17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="73" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="85" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="63">
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="74">
+        <f>E5*D6</f>
+        <v>7.5425000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="73" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="87" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="88">
+        <v>1.8</v>
+      </c>
+      <c r="E7" s="89">
+        <f>E5*D7*20</f>
+        <v>1086.1200000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="73" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="86" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="87" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="88">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E8" s="89">
+        <f>E5*D8</f>
+        <v>33.187000000000005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="90" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="91" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="92" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="93">
+        <v>1</v>
+      </c>
+      <c r="E9" s="94">
+        <v>104.41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="73" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="85" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="63">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E10" s="74">
+        <f>E9*D10</f>
+        <v>114.851</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="73" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="85" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="63">
+        <v>1.8</v>
+      </c>
+      <c r="E11" s="74">
+        <f>E9*D11*20</f>
+        <v>3758.7599999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="73" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="104" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="74">
+        <f>E9*D12</f>
+        <v>15.661499999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="75" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="95" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="78">
+        <v>1</v>
+      </c>
+      <c r="E13" s="79">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="107"/>
+      <c r="B14" s="107"/>
+      <c r="C14" s="107"/>
+      <c r="D14" s="107"/>
+      <c r="E14" s="107"/>
+      <c r="F14" s="107"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="108"/>
+      <c r="B15" s="109" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="110"/>
+      <c r="D15" s="110"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="107"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="113" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" s="107"/>
+    </row>
+    <row r="17" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="73">
+        <v>1</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="63">
+        <v>1</v>
+      </c>
+      <c r="E17" s="74">
+        <f>E9+E5</f>
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F17" s="107"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B18" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="63">
+        <v>2</v>
+      </c>
+      <c r="E18" s="74">
+        <f>E17*D18</f>
+        <v>269.15999999999997</v>
+      </c>
+      <c r="F18" s="107"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E19" s="74">
+        <f>ROUNDDOWN(E17*D19,0)</f>
+        <v>40</v>
+      </c>
+      <c r="F19" s="107"/>
+    </row>
+    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="78">
+        <v>0.15</v>
+      </c>
+      <c r="E20" s="79">
+        <f>D20*E17</f>
+        <v>20.186999999999998</v>
+      </c>
+      <c r="F20" s="107"/>
+    </row>
+    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="114"/>
+      <c r="B21" s="114"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="114"/>
+      <c r="E21" s="114"/>
+      <c r="F21" s="107"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="108"/>
+      <c r="B22" s="109" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="110"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="111"/>
+      <c r="F22" s="107"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="113" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="107"/>
+    </row>
+    <row r="24" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="73">
+        <v>1</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="63">
+        <v>1</v>
+      </c>
+      <c r="E24" s="74">
+        <f>E17</f>
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F24" s="107"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B25" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E25" s="74">
+        <f>E24*D25</f>
+        <v>20.186999999999998</v>
+      </c>
+      <c r="F25" s="107"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="65" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E26" s="74">
+        <f>ROUNDDOWN(E24*D26,0)</f>
+        <v>40</v>
+      </c>
+      <c r="F26" s="107"/>
+    </row>
+    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" s="105" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="78">
+        <v>1</v>
+      </c>
+      <c r="E27" s="79">
+        <f>D27*E24</f>
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F27" s="107"/>
+    </row>
+    <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="107"/>
+      <c r="B28" s="107"/>
+      <c r="C28" s="107"/>
+      <c r="D28" s="107"/>
+      <c r="E28" s="107"/>
+      <c r="F28" s="107"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="108"/>
+      <c r="B29" s="109" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="110"/>
+      <c r="D29" s="110"/>
+      <c r="E29" s="111"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30" s="113" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="73">
+        <v>1</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="63">
+        <v>1</v>
+      </c>
+      <c r="E31" s="74">
+        <f>E24</f>
+        <v>134.57999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B32" s="85" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E32" s="74">
+        <f>D32*E31</f>
+        <v>20.186999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="95" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="78">
+        <v>0.3</v>
+      </c>
+      <c r="E33" s="79">
+        <f>D33*E31</f>
+        <v>40.373999999999995</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.21875" style="149" customWidth="1"/>
+    <col min="2" max="2" width="51.5546875" style="142" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="142" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="142" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="142"/>
+    <col min="6" max="6" width="17.77734375" style="142" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="142"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="141" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="141" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1" s="141" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1" s="141" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="141" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1" s="141" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="130">
+        <v>1</v>
+      </c>
+      <c r="B2" s="143" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="144" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2" s="144" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="145">
+        <v>1</v>
+      </c>
+      <c r="F2" s="169">
+        <f>'2-С-Ш1, баз'!F2</f>
+        <v>1350.87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="146" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="147" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="144"/>
+      <c r="D3" s="130" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="148">
+        <v>0.15</v>
+      </c>
+      <c r="F3" s="170">
+        <f>$F$2*E3</f>
+        <v>202.63049999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="146" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="147" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="144"/>
+      <c r="D4" s="130" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="148">
+        <v>1.5</v>
+      </c>
+      <c r="F4" s="170">
+        <f>$F$2*E4</f>
+        <v>2026.3049999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.21875" style="149" customWidth="1"/>
+    <col min="2" max="2" width="54.77734375" style="142" customWidth="1"/>
+    <col min="3" max="3" width="18.77734375" style="142" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" style="142" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" style="142" customWidth="1"/>
+    <col min="6" max="6" width="17.77734375" style="142" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="142"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="141" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="141" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1" s="141" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1" s="141" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="141" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1" s="141" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="130">
+        <v>1</v>
+      </c>
+      <c r="B2" s="143" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="144" t="s">
+        <v>263</v>
+      </c>
+      <c r="D2" s="144" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="145">
+        <v>1</v>
+      </c>
+      <c r="F2" s="169">
+        <f>611.19+739.68</f>
+        <v>1350.87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="146" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="147" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="144"/>
+      <c r="D3" s="130" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="148">
+        <v>1.5</v>
+      </c>
+      <c r="F3" s="170">
+        <f>$F$2*E3</f>
+        <v>2026.3049999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="146" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="147" t="s">
+        <v>264</v>
+      </c>
+      <c r="C4" s="144"/>
+      <c r="D4" s="130" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="148">
+        <v>0.3</v>
+      </c>
+      <c r="F4" s="170">
+        <f>$F$2*E4</f>
+        <v>405.26099999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="146" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" s="147" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="144"/>
+      <c r="D5" s="130" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="148">
+        <v>0.15</v>
+      </c>
+      <c r="F5" s="170">
+        <f>$F$2*E5</f>
+        <v>202.63049999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.21875" style="139" customWidth="1"/>
+    <col min="2" max="2" width="54.77734375" style="133" customWidth="1"/>
+    <col min="3" max="3" width="41.6640625" style="133" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" style="133" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="133"/>
+    <col min="6" max="6" width="17.77734375" style="133" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="133"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="132" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="132" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1" s="132" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1" s="132" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="132" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1" s="132" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="129">
+        <v>1</v>
+      </c>
+      <c r="B2" s="134" t="s">
+        <v>252</v>
+      </c>
+      <c r="C2" s="135" t="s">
+        <v>268</v>
+      </c>
+      <c r="D2" s="135" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="136">
+        <v>1</v>
+      </c>
+      <c r="F2" s="167">
+        <f>685.31+(3.1+4.2+4.8)*3.12-11</f>
+        <v>712.0619999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="137" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="140" t="s">
+        <v>254</v>
+      </c>
+      <c r="C3" s="131"/>
+      <c r="D3" s="129" t="s">
+        <v>119</v>
+      </c>
+      <c r="E3" s="138">
+        <v>1</v>
+      </c>
+      <c r="F3" s="168">
+        <f>$F$2*E3</f>
+        <v>712.0619999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="137" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="140" t="s">
+        <v>255</v>
+      </c>
+      <c r="C4" s="131" t="s">
+        <v>256</v>
+      </c>
+      <c r="D4" s="129" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="138">
+        <v>0.8</v>
+      </c>
+      <c r="F4" s="168">
+        <f>$F$2*E4</f>
+        <v>569.64959999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="137" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" s="140" t="s">
+        <v>257</v>
+      </c>
+      <c r="C5" s="131" t="s">
+        <v>258</v>
+      </c>
+      <c r="D5" s="129" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="138">
+        <v>2.1</v>
+      </c>
+      <c r="F5" s="168">
+        <f t="shared" ref="F5:F7" si="0">$F$2*E5</f>
+        <v>1495.3301999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="137" t="s">
+        <v>120</v>
+      </c>
+      <c r="B6" s="140" t="s">
+        <v>259</v>
+      </c>
+      <c r="C6" s="131" t="s">
+        <v>260</v>
+      </c>
+      <c r="D6" s="129" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="138">
+        <v>4.2</v>
+      </c>
+      <c r="F6" s="168">
+        <f t="shared" si="0"/>
+        <v>2990.6603999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="137" t="s">
+        <v>266</v>
+      </c>
+      <c r="B7" s="140" t="s">
+        <v>261</v>
+      </c>
+      <c r="C7" s="131" t="s">
+        <v>269</v>
+      </c>
+      <c r="D7" s="129" t="s">
+        <v>262</v>
+      </c>
+      <c r="E7" s="138">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="F7" s="168">
+        <f t="shared" si="0"/>
+        <v>37.02722399999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I86"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2139,15 +4836,15 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="163" t="s">
         <v>251</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="139"/>
-      <c r="G2" s="139"/>
+      <c r="B2" s="164"/>
+      <c r="C2" s="164"/>
+      <c r="D2" s="164"/>
+      <c r="E2" s="164"/>
+      <c r="F2" s="164"/>
+      <c r="G2" s="164"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="117" t="s">
@@ -2156,13 +4853,13 @@
       <c r="B3" s="117" t="s">
         <v>249</v>
       </c>
-      <c r="C3" s="135" t="s">
+      <c r="C3" s="160" t="s">
         <v>248</v>
       </c>
-      <c r="D3" s="136"/>
-      <c r="E3" s="136"/>
-      <c r="F3" s="136"/>
-      <c r="G3" s="136"/>
+      <c r="D3" s="161"/>
+      <c r="E3" s="161"/>
+      <c r="F3" s="161"/>
+      <c r="G3" s="161"/>
     </row>
     <row r="4" spans="1:7" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="117" t="s">
@@ -2270,13 +4967,13 @@
       <c r="B9" s="117" t="s">
         <v>129</v>
       </c>
-      <c r="C9" s="135" t="s">
+      <c r="C9" s="160" t="s">
         <v>130</v>
       </c>
-      <c r="D9" s="136"/>
-      <c r="E9" s="136"/>
-      <c r="F9" s="136"/>
-      <c r="G9" s="137"/>
+      <c r="D9" s="161"/>
+      <c r="E9" s="161"/>
+      <c r="F9" s="161"/>
+      <c r="G9" s="162"/>
     </row>
     <row r="10" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A10" s="117" t="s">
@@ -3753,13 +6450,13 @@
       <c r="B83" s="117" t="s">
         <v>229</v>
       </c>
-      <c r="C83" s="135" t="s">
+      <c r="C83" s="160" t="s">
         <v>230</v>
       </c>
-      <c r="D83" s="136"/>
-      <c r="E83" s="136"/>
-      <c r="F83" s="136"/>
-      <c r="G83" s="137"/>
+      <c r="D83" s="161"/>
+      <c r="E83" s="161"/>
+      <c r="F83" s="161"/>
+      <c r="G83" s="162"/>
     </row>
     <row r="84" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A84" s="117" t="s">
@@ -3809,7 +6506,7 @@
         <v>113.11499999999999</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" ht="66" x14ac:dyDescent="0.25">
       <c r="A86" s="117" t="s">
         <v>235</v>
       </c>
@@ -3842,594 +6539,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7.5546875" customWidth="1"/>
-    <col min="2" max="2" width="54.88671875" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" customWidth="1"/>
-    <col min="4" max="4" width="14.5546875" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="69"/>
-      <c r="B1" s="70" t="s">
-        <v>81</v>
-      </c>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="72"/>
-    </row>
-    <row r="2" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="73" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D2" s="63">
-        <v>1</v>
-      </c>
-      <c r="E2" s="74">
-        <v>21.7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="63">
-        <v>0.1</v>
-      </c>
-      <c r="E3" s="74">
-        <f>D3*E2</f>
-        <v>2.17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="75" t="s">
-        <v>72</v>
-      </c>
-      <c r="B4" s="76" t="s">
-        <v>85</v>
-      </c>
-      <c r="C4" s="77" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" s="78">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E4" s="79">
-        <f>D4*E2</f>
-        <v>23.87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="80" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" s="81" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" s="82" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="83">
-        <v>1</v>
-      </c>
-      <c r="E5" s="84">
-        <v>30.17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="73" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="85" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="63">
-        <v>0.25</v>
-      </c>
-      <c r="E6" s="74">
-        <f>E5*D6</f>
-        <v>7.5425000000000004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="73" t="s">
-        <v>88</v>
-      </c>
-      <c r="B7" s="86" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="87" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" s="88">
-        <v>1.8</v>
-      </c>
-      <c r="E7" s="89">
-        <f>E5*D7*20</f>
-        <v>1086.1200000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="73" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="86" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="87" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" s="88">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E8" s="89">
-        <f>E5*D8</f>
-        <v>33.187000000000005</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="90" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="91" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9" s="92" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="93">
-        <v>1</v>
-      </c>
-      <c r="E9" s="94">
-        <v>104.41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="73" t="s">
-        <v>90</v>
-      </c>
-      <c r="B10" s="85" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" s="63">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E10" s="74">
-        <f>E9*D10</f>
-        <v>114.851</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="73" t="s">
-        <v>91</v>
-      </c>
-      <c r="B11" s="85" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="63">
-        <v>1.8</v>
-      </c>
-      <c r="E11" s="74">
-        <f>E9*D11*20</f>
-        <v>3758.7599999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="73" t="s">
-        <v>92</v>
-      </c>
-      <c r="B12" s="104" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E12" s="74">
-        <f>E9*D12</f>
-        <v>15.661499999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="75" t="s">
-        <v>93</v>
-      </c>
-      <c r="B13" s="95" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="77" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="78">
-        <v>1</v>
-      </c>
-      <c r="E13" s="79">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="107"/>
-      <c r="B14" s="107"/>
-      <c r="C14" s="107"/>
-      <c r="D14" s="107"/>
-      <c r="E14" s="107"/>
-      <c r="F14" s="107"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="108"/>
-      <c r="B15" s="109" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="110"/>
-      <c r="D15" s="110"/>
-      <c r="E15" s="111"/>
-      <c r="F15" s="107"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="113" t="s">
-        <v>51</v>
-      </c>
-      <c r="F16" s="107"/>
-    </row>
-    <row r="17" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="73">
-        <v>1</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="63">
-        <v>1</v>
-      </c>
-      <c r="E17" s="74">
-        <f>E9+E5</f>
-        <v>134.57999999999998</v>
-      </c>
-      <c r="F17" s="107"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B18" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="63">
-        <v>2</v>
-      </c>
-      <c r="E18" s="74">
-        <f>E17*D18</f>
-        <v>269.15999999999997</v>
-      </c>
-      <c r="F18" s="107"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" s="63">
-        <v>0.3</v>
-      </c>
-      <c r="E19" s="74">
-        <f>ROUNDDOWN(E17*D19,0)</f>
-        <v>40</v>
-      </c>
-      <c r="F19" s="107"/>
-    </row>
-    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="75" t="s">
-        <v>72</v>
-      </c>
-      <c r="B20" s="106" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="78">
-        <v>0.15</v>
-      </c>
-      <c r="E20" s="79">
-        <f>D20*E17</f>
-        <v>20.186999999999998</v>
-      </c>
-      <c r="F20" s="107"/>
-    </row>
-    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="114"/>
-      <c r="B21" s="114"/>
-      <c r="C21" s="114"/>
-      <c r="D21" s="114"/>
-      <c r="E21" s="114"/>
-      <c r="F21" s="107"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="108"/>
-      <c r="B22" s="109" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" s="110"/>
-      <c r="D22" s="110"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="107"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23" s="113" t="s">
-        <v>51</v>
-      </c>
-      <c r="F23" s="107"/>
-    </row>
-    <row r="24" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="73">
-        <v>1</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="63">
-        <v>1</v>
-      </c>
-      <c r="E24" s="74">
-        <f>E17</f>
-        <v>134.57999999999998</v>
-      </c>
-      <c r="F24" s="107"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B25" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E25" s="74">
-        <f>E24*D25</f>
-        <v>20.186999999999998</v>
-      </c>
-      <c r="F25" s="107"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="65" t="s">
-        <v>106</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="63">
-        <v>0.3</v>
-      </c>
-      <c r="E26" s="74">
-        <f>ROUNDDOWN(E24*D26,0)</f>
-        <v>40</v>
-      </c>
-      <c r="F26" s="107"/>
-    </row>
-    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="75" t="s">
-        <v>72</v>
-      </c>
-      <c r="B27" s="105" t="s">
-        <v>107</v>
-      </c>
-      <c r="C27" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" s="78">
-        <v>1</v>
-      </c>
-      <c r="E27" s="79">
-        <f>D27*E24</f>
-        <v>134.57999999999998</v>
-      </c>
-      <c r="F27" s="107"/>
-    </row>
-    <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="107"/>
-      <c r="B28" s="107"/>
-      <c r="C28" s="107"/>
-      <c r="D28" s="107"/>
-      <c r="E28" s="107"/>
-      <c r="F28" s="107"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="108"/>
-      <c r="B29" s="109" t="s">
-        <v>60</v>
-      </c>
-      <c r="C29" s="110"/>
-      <c r="D29" s="110"/>
-      <c r="E29" s="111"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D30" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E30" s="113" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="73">
-        <v>1</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31" s="63">
-        <v>1</v>
-      </c>
-      <c r="E31" s="74">
-        <f>E24</f>
-        <v>134.57999999999998</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B32" s="85" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D32" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E32" s="74">
-        <f>D32*E31</f>
-        <v>20.186999999999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="75" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" s="95" t="s">
-        <v>97</v>
-      </c>
-      <c r="C33" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D33" s="78">
-        <v>0.3</v>
-      </c>
-      <c r="E33" s="79">
-        <f>D33*E31</f>
-        <v>40.373999999999995</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="43.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" customWidth="1"/>
-    <col min="3" max="3" width="17.5546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="132" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="133" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="134" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="129" t="s">
-        <v>252</v>
-      </c>
-      <c r="B2" s="130" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" s="131">
-        <v>675.39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:D18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4582,7 +6692,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A4:F92"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
@@ -5442,7 +7552,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A15:E33"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5673,7 +7783,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5726,11 +7836,11 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="140"/>
-      <c r="B4" s="140"/>
-      <c r="C4" s="140"/>
-      <c r="D4" s="140"/>
-      <c r="E4" s="140"/>
+      <c r="A4" s="165"/>
+      <c r="B4" s="165"/>
+      <c r="C4" s="165"/>
+      <c r="D4" s="165"/>
+      <c r="E4" s="165"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="58"/>
@@ -5812,11 +7922,11 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="141"/>
-      <c r="B10" s="141"/>
-      <c r="C10" s="141"/>
-      <c r="D10" s="141"/>
-      <c r="E10" s="141"/>
+      <c r="A10" s="166"/>
+      <c r="B10" s="166"/>
+      <c r="C10" s="166"/>
+      <c r="D10" s="166"/>
+      <c r="E10" s="166"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="58"/>
@@ -5899,11 +8009,11 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="140"/>
-      <c r="B16" s="140"/>
-      <c r="C16" s="140"/>
-      <c r="D16" s="140"/>
-      <c r="E16" s="140"/>
+      <c r="A16" s="165"/>
+      <c r="B16" s="165"/>
+      <c r="C16" s="165"/>
+      <c r="D16" s="165"/>
+      <c r="E16" s="165"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="58"/>
@@ -5993,1359 +8103,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="51" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="58"/>
-      <c r="B1" s="59" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="G1" s="67"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="60" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="67"/>
-    </row>
-    <row r="3" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="62">
-        <v>1</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="63">
-        <v>1</v>
-      </c>
-      <c r="E3" s="17">
-        <v>37.44</v>
-      </c>
-      <c r="F3" s="68"/>
-      <c r="G3" s="67"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="62" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" s="63">
-        <v>1</v>
-      </c>
-      <c r="E4" s="17">
-        <v>22</v>
-      </c>
-      <c r="F4" s="68"/>
-      <c r="G4" s="67"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="62" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" s="63">
-        <v>1</v>
-      </c>
-      <c r="E5" s="17">
-        <v>201</v>
-      </c>
-      <c r="F5" s="68"/>
-      <c r="G5" s="67"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="62" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="63">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E6" s="17">
-        <v>41.183999999999997</v>
-      </c>
-      <c r="F6" s="68"/>
-      <c r="G6" s="67"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="140"/>
-      <c r="B7" s="140"/>
-      <c r="C7" s="140"/>
-      <c r="D7" s="140"/>
-      <c r="E7" s="140"/>
-      <c r="G7" s="67"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="58"/>
-      <c r="B8" s="59" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="60"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="G8" s="66"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="60" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" s="66"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="62">
-        <v>1</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="63">
-        <v>1</v>
-      </c>
-      <c r="E10" s="17">
-        <v>37.44</v>
-      </c>
-      <c r="G10" s="66"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="62">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B11" s="64" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="63">
-        <v>1.8</v>
-      </c>
-      <c r="E11" s="17">
-        <f>E10*D11</f>
-        <v>67.391999999999996</v>
-      </c>
-      <c r="G11" s="66"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="62" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E12" s="17">
-        <f>E10*D12</f>
-        <v>5.6159999999999997</v>
-      </c>
-      <c r="G12" s="66"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="141"/>
-      <c r="B13" s="141"/>
-      <c r="C13" s="141"/>
-      <c r="D13" s="141"/>
-      <c r="E13" s="141"/>
-      <c r="G13" s="66"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="58"/>
-      <c r="B14" s="59" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="G14" s="66"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15" s="60" t="s">
-        <v>51</v>
-      </c>
-      <c r="G15" s="66"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="62">
-        <v>1</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="63">
-        <v>1</v>
-      </c>
-      <c r="E16" s="17">
-        <f>E10</f>
-        <v>37.44</v>
-      </c>
-      <c r="G16" s="66"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="62">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B17" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E17" s="17">
-        <f>E16*D17</f>
-        <v>5.6159999999999997</v>
-      </c>
-      <c r="G17" s="66"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="62" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" s="65" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="63">
-        <v>1.8</v>
-      </c>
-      <c r="E18" s="17">
-        <f>E16*D18</f>
-        <v>67.391999999999996</v>
-      </c>
-      <c r="G18" s="66"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="140"/>
-      <c r="B19" s="140"/>
-      <c r="C19" s="140"/>
-      <c r="D19" s="140"/>
-      <c r="E19" s="140"/>
-      <c r="G19" s="66"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="58"/>
-      <c r="B20" s="59" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="G20" s="66"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21" s="60" t="s">
-        <v>51</v>
-      </c>
-      <c r="G21" s="66"/>
-    </row>
-    <row r="22" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="62">
-        <v>1</v>
-      </c>
-      <c r="B22" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" s="63">
-        <v>1</v>
-      </c>
-      <c r="E22" s="17">
-        <v>37.44</v>
-      </c>
-      <c r="G22" s="66"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="62">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B23" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E23" s="17">
-        <f>E22*D23</f>
-        <v>5.6159999999999997</v>
-      </c>
-      <c r="G23" s="66"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="62" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="65" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" s="63">
-        <v>0.3</v>
-      </c>
-      <c r="E24" s="17">
-        <f>E22*D24</f>
-        <v>11.231999999999999</v>
-      </c>
-      <c r="G24" s="66"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A13:E13"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7.5546875" customWidth="1"/>
-    <col min="2" max="2" width="54.88671875" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" customWidth="1"/>
-    <col min="4" max="4" width="14.5546875" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="58"/>
-      <c r="B1" s="116" t="s">
-        <v>102</v>
-      </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-    </row>
-    <row r="2" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="60" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="62">
-        <v>1</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D3" s="63">
-        <v>1</v>
-      </c>
-      <c r="E3" s="17">
-        <v>16.54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="62" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="D4" s="63">
-        <v>1</v>
-      </c>
-      <c r="E4" s="17">
-        <f>E3</f>
-        <v>16.54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="62" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" s="63">
-        <v>1.42</v>
-      </c>
-      <c r="E5" s="17">
-        <f>D5*E3*2</f>
-        <v>46.973599999999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="62" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="63">
-        <v>2.1</v>
-      </c>
-      <c r="E6" s="17">
-        <f>D6*E3</f>
-        <v>34.734000000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="62" t="s">
-        <v>120</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" s="63">
-        <v>4.07</v>
-      </c>
-      <c r="E7" s="17">
-        <f>D7*E3</f>
-        <v>67.317800000000005</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="107"/>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="96"/>
-      <c r="B9" s="97" t="s">
-        <v>110</v>
-      </c>
-      <c r="C9" s="98"/>
-      <c r="D9" s="98"/>
-      <c r="E9" s="99"/>
-    </row>
-    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="100" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="101" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="102" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="102" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="103" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="90">
-        <v>1</v>
-      </c>
-      <c r="B11" s="91" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" s="92" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="93">
-        <v>1</v>
-      </c>
-      <c r="E11" s="94">
-        <v>33.25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B12" s="85" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="63">
-        <v>0.3</v>
-      </c>
-      <c r="E12" s="74">
-        <f>E11*D12</f>
-        <v>9.9749999999999996</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="85" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="63">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E13" s="74">
-        <f>D13*E11</f>
-        <v>36.575000000000003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="107"/>
-      <c r="B14" s="107"/>
-      <c r="C14" s="107"/>
-      <c r="D14" s="107"/>
-      <c r="E14" s="107"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="108"/>
-      <c r="B15" s="109" t="s">
-        <v>111</v>
-      </c>
-      <c r="C15" s="110"/>
-      <c r="D15" s="110"/>
-      <c r="E15" s="111"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="113" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="73">
-        <v>1</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="63">
-        <v>1</v>
-      </c>
-      <c r="E17" s="74">
-        <f>E3</f>
-        <v>16.54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B18" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="63">
-        <v>2</v>
-      </c>
-      <c r="E18" s="74">
-        <f>E17*D18</f>
-        <v>33.08</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" s="63">
-        <v>0.3</v>
-      </c>
-      <c r="E19" s="74">
-        <f>ROUNDDOWN(E17*D19,0)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="75" t="s">
-        <v>72</v>
-      </c>
-      <c r="B20" s="106" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="78">
-        <v>0.15</v>
-      </c>
-      <c r="E20" s="79">
-        <f>D20*E17</f>
-        <v>2.4809999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="107"/>
-      <c r="B21" s="107"/>
-      <c r="C21" s="107"/>
-      <c r="D21" s="107"/>
-      <c r="E21" s="107"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="108"/>
-      <c r="B22" s="109" t="s">
-        <v>112</v>
-      </c>
-      <c r="C22" s="110"/>
-      <c r="D22" s="110"/>
-      <c r="E22" s="111"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23" s="113" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="73">
-        <v>1</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="63">
-        <v>1</v>
-      </c>
-      <c r="E24" s="74">
-        <f>79.16+E3</f>
-        <v>95.699999999999989</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B25" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E25" s="115">
-        <f>E24*D25</f>
-        <v>14.354999999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="65" t="s">
-        <v>105</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D26" s="63">
-        <v>2</v>
-      </c>
-      <c r="E26" s="74">
-        <f>E24*D26</f>
-        <v>191.39999999999998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="107"/>
-      <c r="B27" s="107"/>
-      <c r="C27" s="107"/>
-      <c r="D27" s="107"/>
-      <c r="E27" s="107"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="108"/>
-      <c r="B28" s="109" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="110"/>
-      <c r="D28" s="110"/>
-      <c r="E28" s="111"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D29" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E29" s="113" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="73">
-        <v>1</v>
-      </c>
-      <c r="B30" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="63">
-        <v>1</v>
-      </c>
-      <c r="E30" s="74">
-        <v>970.52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B31" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D31" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E31" s="74">
-        <f>E30*D31</f>
-        <v>145.578</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="75" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" s="105" t="s">
-        <v>105</v>
-      </c>
-      <c r="C32" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D32" s="78">
-        <v>2</v>
-      </c>
-      <c r="E32" s="79">
-        <f>D32*E30</f>
-        <v>1941.04</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="107"/>
-      <c r="B33" s="107"/>
-      <c r="C33" s="107"/>
-      <c r="D33" s="107"/>
-      <c r="E33" s="107"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="96"/>
-      <c r="B34" s="97" t="s">
-        <v>60</v>
-      </c>
-      <c r="C34" s="98"/>
-      <c r="D34" s="98"/>
-      <c r="E34" s="99"/>
-    </row>
-    <row r="35" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="100" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" s="101" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="102" t="s">
-        <v>49</v>
-      </c>
-      <c r="D35" s="102" t="s">
-        <v>50</v>
-      </c>
-      <c r="E35" s="103" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="90">
-        <v>1</v>
-      </c>
-      <c r="B36" s="91" t="s">
-        <v>95</v>
-      </c>
-      <c r="C36" s="92" t="s">
-        <v>52</v>
-      </c>
-      <c r="D36" s="93">
-        <v>1</v>
-      </c>
-      <c r="E36" s="94">
-        <f>E24+E30</f>
-        <v>1066.22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B37" s="86" t="s">
-        <v>96</v>
-      </c>
-      <c r="C37" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D37" s="88">
-        <v>0.15</v>
-      </c>
-      <c r="E37" s="89">
-        <f>D37*E36</f>
-        <v>159.93299999999999</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="75" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" s="95" t="s">
-        <v>97</v>
-      </c>
-      <c r="C38" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D38" s="78">
-        <v>0.3</v>
-      </c>
-      <c r="E38" s="79">
-        <f>D38*E36</f>
-        <v>319.86599999999999</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7.5546875" customWidth="1"/>
-    <col min="2" max="2" width="54.88671875" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" customWidth="1"/>
-    <col min="4" max="4" width="14.5546875" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="69"/>
-      <c r="B1" s="70" t="s">
-        <v>81</v>
-      </c>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="72"/>
-    </row>
-    <row r="2" spans="1:6" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="73" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D2" s="63">
-        <v>1</v>
-      </c>
-      <c r="E2" s="74">
-        <v>21.7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="80" t="s">
-        <v>86</v>
-      </c>
-      <c r="B3" s="81" t="s">
-        <v>254</v>
-      </c>
-      <c r="C3" s="82" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="83">
-        <v>1</v>
-      </c>
-      <c r="E3" s="84">
-        <v>134.57999999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="107"/>
-      <c r="B4" s="107"/>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="108"/>
-      <c r="B5" s="109" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="107"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="113" t="s">
-        <v>51</v>
-      </c>
-      <c r="F6" s="107"/>
-    </row>
-    <row r="7" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="73">
-        <v>1</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" s="63">
-        <v>1</v>
-      </c>
-      <c r="E7" s="74">
-        <f>E3</f>
-        <v>134.57999999999998</v>
-      </c>
-      <c r="F7" s="107"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B8" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="63">
-        <v>2</v>
-      </c>
-      <c r="E8" s="74">
-        <f>E7*D8</f>
-        <v>269.15999999999997</v>
-      </c>
-      <c r="F8" s="107"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="63">
-        <v>0.3</v>
-      </c>
-      <c r="E9" s="74">
-        <f>ROUNDDOWN(E7*D9,0)</f>
-        <v>40</v>
-      </c>
-      <c r="F9" s="107"/>
-    </row>
-    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="75" t="s">
-        <v>72</v>
-      </c>
-      <c r="B10" s="106" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="78">
-        <v>0.15</v>
-      </c>
-      <c r="E10" s="79">
-        <f>D10*E7</f>
-        <v>20.186999999999998</v>
-      </c>
-      <c r="F10" s="107"/>
-    </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="114"/>
-      <c r="B11" s="114"/>
-      <c r="C11" s="114"/>
-      <c r="D11" s="114"/>
-      <c r="E11" s="114"/>
-      <c r="F11" s="107"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="108"/>
-      <c r="B12" s="109" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="110"/>
-      <c r="E12" s="111"/>
-      <c r="F12" s="107"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="113" t="s">
-        <v>51</v>
-      </c>
-      <c r="F13" s="107"/>
-    </row>
-    <row r="14" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="73">
-        <v>1</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="63">
-        <v>1</v>
-      </c>
-      <c r="E14" s="74">
-        <f>E7</f>
-        <v>134.57999999999998</v>
-      </c>
-      <c r="F14" s="107"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B15" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E15" s="74">
-        <f>E14*D15</f>
-        <v>20.186999999999998</v>
-      </c>
-      <c r="F15" s="107"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" s="65" t="s">
-        <v>106</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" s="63">
-        <v>0.3</v>
-      </c>
-      <c r="E16" s="74">
-        <f>ROUNDDOWN(E14*D16,0)</f>
-        <v>40</v>
-      </c>
-      <c r="F16" s="107"/>
-    </row>
-    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="75" t="s">
-        <v>72</v>
-      </c>
-      <c r="B17" s="105" t="s">
-        <v>107</v>
-      </c>
-      <c r="C17" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="78">
-        <v>1</v>
-      </c>
-      <c r="E17" s="79">
-        <f>D17*E14</f>
-        <v>134.57999999999998</v>
-      </c>
-      <c r="F17" s="107"/>
-    </row>
-    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="107"/>
-      <c r="B18" s="107"/>
-      <c r="C18" s="107"/>
-      <c r="D18" s="107"/>
-      <c r="E18" s="107"/>
-      <c r="F18" s="107"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="108"/>
-      <c r="B19" s="109" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" s="110"/>
-      <c r="D19" s="110"/>
-      <c r="E19" s="111"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E20" s="113" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="73">
-        <v>1</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="63">
-        <v>1</v>
-      </c>
-      <c r="E21" s="74">
-        <f>E14</f>
-        <v>134.57999999999998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B22" s="85" t="s">
-        <v>96</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E22" s="74">
-        <f>D22*E21</f>
-        <v>20.186999999999998</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="75" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="95" t="s">
-        <v>97</v>
-      </c>
-      <c r="C23" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="78">
-        <v>0.3</v>
-      </c>
-      <c r="E23" s="79">
-        <f>D23*E21</f>
-        <v>40.373999999999995</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/school_1/walls/vor_spartac_1_walls.xlsx
+++ b/school_1/walls/vor_spartac_1_walls.xlsx
@@ -9,29 +9,36 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="23268" yWindow="5568" windowWidth="5532" windowHeight="6108" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="5568" windowWidth="5532" windowHeight="1512" firstSheet="4" activeTab="6"/>
   </bookViews>
   <sheets>
-    <sheet name="4-С-Ш1" sheetId="13" r:id="rId1"/>
-    <sheet name="3-С-Ш1фин" sheetId="12" r:id="rId2"/>
-    <sheet name="2-С-Ш1, баз" sheetId="11" r:id="rId3"/>
-    <sheet name="1-С-Ш1, ГКЛ" sheetId="9" r:id="rId4"/>
-    <sheet name="Общий" sheetId="8" r:id="rId5"/>
-    <sheet name="Пример" sheetId="1" r:id="rId6"/>
-    <sheet name="Спортзал" sheetId="2" r:id="rId7"/>
-    <sheet name="библиотека" sheetId="3" r:id="rId8"/>
-    <sheet name="Библ откосы" sheetId="4" r:id="rId9"/>
-    <sheet name="ВОР2FB" sheetId="5" r:id="rId10"/>
-    <sheet name="1.030 ВОР" sheetId="7" r:id="rId11"/>
-    <sheet name="1.032 ВОР" sheetId="6" r:id="rId12"/>
-    <sheet name="1.032 ВОР (2)" sheetId="10" r:id="rId13"/>
+    <sheet name="15ДмПот" sheetId="21" r:id="rId1"/>
+    <sheet name="14МонтСт" sheetId="20" r:id="rId2"/>
+    <sheet name="13МонтСт" sheetId="17" r:id="rId3"/>
+    <sheet name="12ДмСт" sheetId="16" r:id="rId4"/>
+    <sheet name="11ПВХплитка" sheetId="19" r:id="rId5"/>
+    <sheet name="10ПВХплиткаДм" sheetId="15" r:id="rId6"/>
+    <sheet name="9 Краска" sheetId="14" r:id="rId7"/>
+    <sheet name="4-С-Ш1" sheetId="13" r:id="rId8"/>
+    <sheet name="3-С-Ш1фин" sheetId="12" r:id="rId9"/>
+    <sheet name="2-С-Ш1, баз" sheetId="11" r:id="rId10"/>
+    <sheet name="1-С-Ш1, ГКЛ" sheetId="9" r:id="rId11"/>
+    <sheet name="Общий" sheetId="8" r:id="rId12"/>
+    <sheet name="Пример" sheetId="1" r:id="rId13"/>
+    <sheet name="Спортзал" sheetId="2" r:id="rId14"/>
+    <sheet name="библиотека" sheetId="3" r:id="rId15"/>
+    <sheet name="Библ откосы" sheetId="4" r:id="rId16"/>
+    <sheet name="ВОР2FB" sheetId="5" r:id="rId17"/>
+    <sheet name="1.030 ВОР" sheetId="7" r:id="rId18"/>
+    <sheet name="1.032 ВОР" sheetId="6" r:id="rId19"/>
+    <sheet name="1.032 ВОР (2)" sheetId="10" r:id="rId20"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="361">
   <si>
     <t>Штукатурка цементным составом толщиной 16‐20 мм</t>
   </si>
@@ -857,15 +864,280 @@
   </si>
   <si>
     <t>(2 слоя)</t>
+  </si>
+  <si>
+    <t>3.019</t>
+  </si>
+  <si>
+    <t>3.021</t>
+  </si>
+  <si>
+    <t>3.022</t>
+  </si>
+  <si>
+    <t>3.023</t>
+  </si>
+  <si>
+    <t>3.035</t>
+  </si>
+  <si>
+    <t>3.036</t>
+  </si>
+  <si>
+    <t>3.037</t>
+  </si>
+  <si>
+    <t>3.038</t>
+  </si>
+  <si>
+    <t>3.048</t>
+  </si>
+  <si>
+    <t>3.051</t>
+  </si>
+  <si>
+    <t>3.066</t>
+  </si>
+  <si>
+    <t>2.022</t>
+  </si>
+  <si>
+    <t>2.025</t>
+  </si>
+  <si>
+    <t>2.030</t>
+  </si>
+  <si>
+    <t>2.031</t>
+  </si>
+  <si>
+    <t>2.032</t>
+  </si>
+  <si>
+    <t>2.033</t>
+  </si>
+  <si>
+    <t>2.042</t>
+  </si>
+  <si>
+    <t>2.045</t>
+  </si>
+  <si>
+    <t>2.046</t>
+  </si>
+  <si>
+    <t>2.047</t>
+  </si>
+  <si>
+    <t>Лакокрасочные работы СКБ / окраска стен / в 2 слоя</t>
+  </si>
+  <si>
+    <t>СТ-1.3</t>
+  </si>
+  <si>
+    <t>СТ-1.9</t>
+  </si>
+  <si>
+    <t>Итог:</t>
+  </si>
+  <si>
+    <t>2 этаж / КМ1 / 9003</t>
+  </si>
+  <si>
+    <t>2 этаж / КМ0 / СТ-1.3</t>
+  </si>
+  <si>
+    <t>3 этаж / КМ1 / 9003</t>
+  </si>
+  <si>
+    <t>3 этаж / СТ-1.9</t>
+  </si>
+  <si>
+    <t>3 этаж / КМ0 / СТ-1.3</t>
+  </si>
+  <si>
+    <t>№ пом.</t>
+  </si>
+  <si>
+    <t>RL 9003</t>
+  </si>
+  <si>
+    <t>Демонтаж отделки (штукатурка / шпаклевка)</t>
+  </si>
+  <si>
+    <t>Штукатурка стен гипсовыми смесями с предварительной огрунтовкой СКБ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> / толщ. от 21 до 40 мм / высотой от 4,01 до 8 метров</t>
+  </si>
+  <si>
+    <t>2 этаж ПВХ плитка</t>
+  </si>
+  <si>
+    <t>3 этаж ПВХ плитка</t>
+  </si>
+  <si>
+    <t>Демонтаж шпатлевки и/или штукатурки на поверхности стен</t>
+  </si>
+  <si>
+    <t>Демонтаж плинтуса для линолеума</t>
+  </si>
+  <si>
+    <t>пог. м.</t>
+  </si>
+  <si>
+    <t>Установка напольного плинтуса ПВХ</t>
+  </si>
+  <si>
+    <t>2, 3 этаж</t>
+  </si>
+  <si>
+    <t>2 этаж / КМ0 / 7016 / опуск от потолка</t>
+  </si>
+  <si>
+    <t>3 этаж / КМ0 / 7016/ опуск от потолка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Демонтаж напольных покрытий </t>
+  </si>
+  <si>
+    <t>2, 3 этаж 
+ПЛ-2</t>
+  </si>
+  <si>
+    <t>2 этаж  / ПВХ плитка Л-1</t>
+  </si>
+  <si>
+    <t>3 этаж / ПВХ плитка Л-1</t>
+  </si>
+  <si>
+    <t>Устройство покрытия пола из ПВХ плитки</t>
+  </si>
+  <si>
+    <t>3.050</t>
+  </si>
+  <si>
+    <t>Демонтаж подвесного потолка</t>
+  </si>
+  <si>
+    <t>3 этаж  / 
+ПТ-5</t>
+  </si>
+  <si>
+    <t>Общее 
+кол-во</t>
+  </si>
+  <si>
+    <t>2.064</t>
+  </si>
+  <si>
+    <t>2.050</t>
+  </si>
+  <si>
+    <t>3.041</t>
+  </si>
+  <si>
+    <t>3.005</t>
+  </si>
+  <si>
+    <t>3.061</t>
+  </si>
+  <si>
+    <t>3.062</t>
+  </si>
+  <si>
+    <t>2.043</t>
+  </si>
+  <si>
+    <t>2.048</t>
+  </si>
+  <si>
+    <t>2.049</t>
+  </si>
+  <si>
+    <t>2.055</t>
+  </si>
+  <si>
+    <t>2.057</t>
+  </si>
+  <si>
+    <t>2.060</t>
+  </si>
+  <si>
+    <t>2.061</t>
+  </si>
+  <si>
+    <t>2.062</t>
+  </si>
+  <si>
+    <t>2.065</t>
+  </si>
+  <si>
+    <t>2.066</t>
+  </si>
+  <si>
+    <t>2.067</t>
+  </si>
+  <si>
+    <t>2.068</t>
+  </si>
+  <si>
+    <t>2.071</t>
+  </si>
+  <si>
+    <t>3.033</t>
+  </si>
+  <si>
+    <t>3.039</t>
+  </si>
+  <si>
+    <t>3.040</t>
+  </si>
+  <si>
+    <t>3.042</t>
+  </si>
+  <si>
+    <t>3.043</t>
+  </si>
+  <si>
+    <t>3.044</t>
+  </si>
+  <si>
+    <t>3.045</t>
+  </si>
+  <si>
+    <t>3.046</t>
+  </si>
+  <si>
+    <t>3.047</t>
+  </si>
+  <si>
+    <t>3.049</t>
+  </si>
+  <si>
+    <t>3.053</t>
+  </si>
+  <si>
+    <t>3.054</t>
+  </si>
+  <si>
+    <t>3.058</t>
+  </si>
+  <si>
+    <t>3.059</t>
+  </si>
+  <si>
+    <t>3.060</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="23" x14ac:knownFonts="1">
     <font>
@@ -1078,7 +1350,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -1513,13 +1785,86 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="171">
+  <cellXfs count="215">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1978,6 +2323,135 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="19" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="21" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="21" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1999,16 +2473,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="15" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="15" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2317,2206 +2794,133 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="159" customWidth="1"/>
-    <col min="2" max="2" width="54.77734375" style="142" customWidth="1"/>
-    <col min="3" max="3" width="21.6640625" style="142" customWidth="1"/>
-    <col min="4" max="4" width="18.21875" style="142" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="142"/>
-    <col min="6" max="6" width="17.77734375" style="142" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="142"/>
+    <col min="1" max="1" width="9.21875" style="166" customWidth="1"/>
+    <col min="2" max="2" width="12" style="142" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" style="142" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="142" customWidth="1"/>
+    <col min="5" max="5" width="13" style="142" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="142" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5546875" style="142" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="142"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="141" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="150" t="s">
+      <c r="B1" s="180" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="150" t="s">
+      <c r="C1" s="181"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="150" t="s">
         <v>270</v>
       </c>
-      <c r="D1" s="150" t="s">
+      <c r="F1" s="150" t="s">
         <v>49</v>
       </c>
-      <c r="E1" s="150" t="s">
-        <v>126</v>
-      </c>
-      <c r="F1" s="150" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G1" s="150" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="130">
         <v>1</v>
       </c>
-      <c r="B2" s="151" t="s">
-        <v>272</v>
-      </c>
-      <c r="C2" s="152" t="s">
-        <v>273</v>
-      </c>
-      <c r="D2" s="152" t="s">
+      <c r="B2" s="183" t="s">
+        <v>324</v>
+      </c>
+      <c r="C2" s="184"/>
+      <c r="D2" s="185"/>
+      <c r="E2" s="152" t="s">
+        <v>325</v>
+      </c>
+      <c r="F2" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="153">
-        <v>1</v>
-      </c>
-      <c r="F2" s="154">
-        <f>(2.1*2+1.15)*0.125*17</f>
-        <v>11.368749999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="130">
-        <v>2</v>
-      </c>
-      <c r="B3" s="151" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" s="152" t="s">
-        <v>263</v>
-      </c>
-      <c r="D3" s="152" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" s="153">
-        <v>1</v>
-      </c>
-      <c r="F3" s="154">
-        <f>F2</f>
-        <v>11.368749999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="146" t="s">
-        <v>267</v>
-      </c>
-      <c r="B4" s="155" t="s">
-        <v>201</v>
-      </c>
-      <c r="C4" s="152"/>
-      <c r="D4" s="156" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="157">
-        <v>1.5</v>
-      </c>
-      <c r="F4" s="158">
-        <f>$F$3*E4</f>
-        <v>17.053124999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="146" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" s="155" t="s">
-        <v>264</v>
-      </c>
-      <c r="C5" s="152"/>
-      <c r="D5" s="156" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="157">
-        <v>0.3</v>
-      </c>
-      <c r="F5" s="158">
-        <f t="shared" ref="F5:F9" si="0">$F$3*E5</f>
-        <v>3.4106249999999996</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="146" t="s">
-        <v>88</v>
-      </c>
-      <c r="B6" s="155" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="152"/>
-      <c r="D6" s="156" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="157">
-        <v>0.15</v>
-      </c>
-      <c r="F6" s="158">
-        <f t="shared" si="0"/>
-        <v>1.7053124999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="130">
-        <v>3</v>
-      </c>
-      <c r="B7" s="151" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="152" t="s">
-        <v>265</v>
-      </c>
-      <c r="D7" s="152" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="153">
-        <v>1</v>
-      </c>
-      <c r="F7" s="158">
-        <f t="shared" si="0"/>
-        <v>11.368749999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="146" t="s">
-        <v>90</v>
-      </c>
-      <c r="B8" s="155" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="152"/>
-      <c r="D8" s="156" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" s="157">
-        <v>0.15</v>
-      </c>
-      <c r="F8" s="158">
-        <f t="shared" si="0"/>
-        <v>1.7053124999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="146" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="155" t="s">
-        <v>201</v>
-      </c>
-      <c r="C9" s="152"/>
-      <c r="D9" s="156" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" s="157">
-        <v>1.5</v>
-      </c>
-      <c r="F9" s="158">
-        <f t="shared" si="0"/>
-        <v>17.053124999999998</v>
-      </c>
+      <c r="G2" s="154">
+        <f>B7</f>
+        <v>342.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="186"/>
+      <c r="B3" s="186"/>
+      <c r="C3" s="186"/>
+      <c r="D3" s="186"/>
+      <c r="E3" s="186"/>
+      <c r="F3" s="186"/>
+      <c r="G3" s="186"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="174" t="s">
+        <v>304</v>
+      </c>
+      <c r="B4" s="174" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="178"/>
+      <c r="D4" s="179"/>
+      <c r="E4" s="179"/>
+      <c r="F4" s="179"/>
+      <c r="G4" s="179"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="174" t="s">
+        <v>281</v>
+      </c>
+      <c r="B5" s="174">
+        <v>190.5</v>
+      </c>
+      <c r="C5" s="178"/>
+      <c r="D5" s="179"/>
+      <c r="E5" s="179"/>
+      <c r="F5" s="179"/>
+      <c r="G5" s="179"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="174" t="s">
+        <v>323</v>
+      </c>
+      <c r="B6" s="174">
+        <v>152.19999999999999</v>
+      </c>
+      <c r="C6" s="178"/>
+      <c r="D6" s="179"/>
+      <c r="E6" s="179"/>
+      <c r="F6" s="179"/>
+      <c r="G6" s="179"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="174" t="s">
+        <v>298</v>
+      </c>
+      <c r="B7" s="165">
+        <f>SUM(B5:B6)</f>
+        <v>342.7</v>
+      </c>
+      <c r="C7" s="178"/>
+      <c r="D7" s="179"/>
+      <c r="E7" s="179"/>
+      <c r="F7" s="179"/>
+      <c r="G7" s="179"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C4:G7"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="A3:G3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="51" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="58"/>
-      <c r="B1" s="59" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="G1" s="67"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="60" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="67"/>
-    </row>
-    <row r="3" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="62">
-        <v>1</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="63">
-        <v>1</v>
-      </c>
-      <c r="E3" s="17">
-        <v>37.44</v>
-      </c>
-      <c r="F3" s="68"/>
-      <c r="G3" s="67"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="62" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" s="63">
-        <v>1</v>
-      </c>
-      <c r="E4" s="17">
-        <v>22</v>
-      </c>
-      <c r="F4" s="68"/>
-      <c r="G4" s="67"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="62" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" s="63">
-        <v>1</v>
-      </c>
-      <c r="E5" s="17">
-        <v>201</v>
-      </c>
-      <c r="F5" s="68"/>
-      <c r="G5" s="67"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="62" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="63">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E6" s="17">
-        <v>41.183999999999997</v>
-      </c>
-      <c r="F6" s="68"/>
-      <c r="G6" s="67"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="165"/>
-      <c r="B7" s="165"/>
-      <c r="C7" s="165"/>
-      <c r="D7" s="165"/>
-      <c r="E7" s="165"/>
-      <c r="G7" s="67"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="58"/>
-      <c r="B8" s="59" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="60"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="G8" s="66"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="60" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" s="66"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="62">
-        <v>1</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="63">
-        <v>1</v>
-      </c>
-      <c r="E10" s="17">
-        <v>37.44</v>
-      </c>
-      <c r="G10" s="66"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="62">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B11" s="64" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="63">
-        <v>1.8</v>
-      </c>
-      <c r="E11" s="17">
-        <f>E10*D11</f>
-        <v>67.391999999999996</v>
-      </c>
-      <c r="G11" s="66"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="62" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E12" s="17">
-        <f>E10*D12</f>
-        <v>5.6159999999999997</v>
-      </c>
-      <c r="G12" s="66"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="166"/>
-      <c r="B13" s="166"/>
-      <c r="C13" s="166"/>
-      <c r="D13" s="166"/>
-      <c r="E13" s="166"/>
-      <c r="G13" s="66"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="58"/>
-      <c r="B14" s="59" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="G14" s="66"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15" s="60" t="s">
-        <v>51</v>
-      </c>
-      <c r="G15" s="66"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="62">
-        <v>1</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="63">
-        <v>1</v>
-      </c>
-      <c r="E16" s="17">
-        <f>E10</f>
-        <v>37.44</v>
-      </c>
-      <c r="G16" s="66"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="62">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B17" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E17" s="17">
-        <f>E16*D17</f>
-        <v>5.6159999999999997</v>
-      </c>
-      <c r="G17" s="66"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="62" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" s="65" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="63">
-        <v>1.8</v>
-      </c>
-      <c r="E18" s="17">
-        <f>E16*D18</f>
-        <v>67.391999999999996</v>
-      </c>
-      <c r="G18" s="66"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="165"/>
-      <c r="B19" s="165"/>
-      <c r="C19" s="165"/>
-      <c r="D19" s="165"/>
-      <c r="E19" s="165"/>
-      <c r="G19" s="66"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="58"/>
-      <c r="B20" s="59" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="G20" s="66"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21" s="60" t="s">
-        <v>51</v>
-      </c>
-      <c r="G21" s="66"/>
-    </row>
-    <row r="22" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="62">
-        <v>1</v>
-      </c>
-      <c r="B22" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" s="63">
-        <v>1</v>
-      </c>
-      <c r="E22" s="17">
-        <v>37.44</v>
-      </c>
-      <c r="G22" s="66"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="62">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B23" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E23" s="17">
-        <f>E22*D23</f>
-        <v>5.6159999999999997</v>
-      </c>
-      <c r="G23" s="66"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="62" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="65" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" s="63">
-        <v>0.3</v>
-      </c>
-      <c r="E24" s="17">
-        <f>E22*D24</f>
-        <v>11.231999999999999</v>
-      </c>
-      <c r="G24" s="66"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A13:E13"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7.5546875" customWidth="1"/>
-    <col min="2" max="2" width="54.88671875" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" customWidth="1"/>
-    <col min="4" max="4" width="14.5546875" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="58"/>
-      <c r="B1" s="116" t="s">
-        <v>102</v>
-      </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-    </row>
-    <row r="2" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="60" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="62">
-        <v>1</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D3" s="63">
-        <v>1</v>
-      </c>
-      <c r="E3" s="17">
-        <v>16.54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="62" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="D4" s="63">
-        <v>1</v>
-      </c>
-      <c r="E4" s="17">
-        <f>E3</f>
-        <v>16.54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="62" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" s="63">
-        <v>1.42</v>
-      </c>
-      <c r="E5" s="17">
-        <f>D5*E3*2</f>
-        <v>46.973599999999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="62" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="63">
-        <v>2.1</v>
-      </c>
-      <c r="E6" s="17">
-        <f>D6*E3</f>
-        <v>34.734000000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="62" t="s">
-        <v>120</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" s="63">
-        <v>4.07</v>
-      </c>
-      <c r="E7" s="17">
-        <f>D7*E3</f>
-        <v>67.317800000000005</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="107"/>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="96"/>
-      <c r="B9" s="97" t="s">
-        <v>110</v>
-      </c>
-      <c r="C9" s="98"/>
-      <c r="D9" s="98"/>
-      <c r="E9" s="99"/>
-    </row>
-    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="100" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="101" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="102" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="102" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="103" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="90">
-        <v>1</v>
-      </c>
-      <c r="B11" s="91" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" s="92" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="93">
-        <v>1</v>
-      </c>
-      <c r="E11" s="94">
-        <v>33.25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B12" s="85" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="63">
-        <v>0.3</v>
-      </c>
-      <c r="E12" s="74">
-        <f>E11*D12</f>
-        <v>9.9749999999999996</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="85" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="63">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E13" s="74">
-        <f>D13*E11</f>
-        <v>36.575000000000003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="107"/>
-      <c r="B14" s="107"/>
-      <c r="C14" s="107"/>
-      <c r="D14" s="107"/>
-      <c r="E14" s="107"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="108"/>
-      <c r="B15" s="109" t="s">
-        <v>111</v>
-      </c>
-      <c r="C15" s="110"/>
-      <c r="D15" s="110"/>
-      <c r="E15" s="111"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="113" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="73">
-        <v>1</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="63">
-        <v>1</v>
-      </c>
-      <c r="E17" s="74">
-        <f>E3</f>
-        <v>16.54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B18" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="63">
-        <v>2</v>
-      </c>
-      <c r="E18" s="74">
-        <f>E17*D18</f>
-        <v>33.08</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" s="63">
-        <v>0.3</v>
-      </c>
-      <c r="E19" s="74">
-        <f>ROUNDDOWN(E17*D19,0)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="75" t="s">
-        <v>72</v>
-      </c>
-      <c r="B20" s="106" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="78">
-        <v>0.15</v>
-      </c>
-      <c r="E20" s="79">
-        <f>D20*E17</f>
-        <v>2.4809999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="107"/>
-      <c r="B21" s="107"/>
-      <c r="C21" s="107"/>
-      <c r="D21" s="107"/>
-      <c r="E21" s="107"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="108"/>
-      <c r="B22" s="109" t="s">
-        <v>112</v>
-      </c>
-      <c r="C22" s="110"/>
-      <c r="D22" s="110"/>
-      <c r="E22" s="111"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23" s="113" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="73">
-        <v>1</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="63">
-        <v>1</v>
-      </c>
-      <c r="E24" s="74">
-        <f>79.16+E3</f>
-        <v>95.699999999999989</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B25" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E25" s="115">
-        <f>E24*D25</f>
-        <v>14.354999999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="65" t="s">
-        <v>105</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D26" s="63">
-        <v>2</v>
-      </c>
-      <c r="E26" s="74">
-        <f>E24*D26</f>
-        <v>191.39999999999998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="107"/>
-      <c r="B27" s="107"/>
-      <c r="C27" s="107"/>
-      <c r="D27" s="107"/>
-      <c r="E27" s="107"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="108"/>
-      <c r="B28" s="109" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="110"/>
-      <c r="D28" s="110"/>
-      <c r="E28" s="111"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D29" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E29" s="113" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="73">
-        <v>1</v>
-      </c>
-      <c r="B30" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="63">
-        <v>1</v>
-      </c>
-      <c r="E30" s="74">
-        <v>970.52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B31" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D31" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E31" s="74">
-        <f>E30*D31</f>
-        <v>145.578</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="75" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" s="105" t="s">
-        <v>105</v>
-      </c>
-      <c r="C32" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D32" s="78">
-        <v>2</v>
-      </c>
-      <c r="E32" s="79">
-        <f>D32*E30</f>
-        <v>1941.04</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="107"/>
-      <c r="B33" s="107"/>
-      <c r="C33" s="107"/>
-      <c r="D33" s="107"/>
-      <c r="E33" s="107"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="96"/>
-      <c r="B34" s="97" t="s">
-        <v>60</v>
-      </c>
-      <c r="C34" s="98"/>
-      <c r="D34" s="98"/>
-      <c r="E34" s="99"/>
-    </row>
-    <row r="35" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="100" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" s="101" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="102" t="s">
-        <v>49</v>
-      </c>
-      <c r="D35" s="102" t="s">
-        <v>50</v>
-      </c>
-      <c r="E35" s="103" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="90">
-        <v>1</v>
-      </c>
-      <c r="B36" s="91" t="s">
-        <v>95</v>
-      </c>
-      <c r="C36" s="92" t="s">
-        <v>52</v>
-      </c>
-      <c r="D36" s="93">
-        <v>1</v>
-      </c>
-      <c r="E36" s="94">
-        <f>E24+E30</f>
-        <v>1066.22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B37" s="86" t="s">
-        <v>96</v>
-      </c>
-      <c r="C37" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D37" s="88">
-        <v>0.15</v>
-      </c>
-      <c r="E37" s="89">
-        <f>D37*E36</f>
-        <v>159.93299999999999</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="75" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" s="95" t="s">
-        <v>97</v>
-      </c>
-      <c r="C38" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D38" s="78">
-        <v>0.3</v>
-      </c>
-      <c r="E38" s="79">
-        <f>D38*E36</f>
-        <v>319.86599999999999</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7.5546875" customWidth="1"/>
-    <col min="2" max="2" width="54.88671875" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" customWidth="1"/>
-    <col min="4" max="4" width="14.5546875" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="69"/>
-      <c r="B1" s="70" t="s">
-        <v>81</v>
-      </c>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="72"/>
-    </row>
-    <row r="2" spans="1:6" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="73" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D2" s="63">
-        <v>1</v>
-      </c>
-      <c r="E2" s="74">
-        <v>21.7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="80" t="s">
-        <v>86</v>
-      </c>
-      <c r="B3" s="81" t="s">
-        <v>253</v>
-      </c>
-      <c r="C3" s="82" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="83">
-        <v>1</v>
-      </c>
-      <c r="E3" s="84">
-        <v>134.57999999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="107"/>
-      <c r="B4" s="107"/>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="108"/>
-      <c r="B5" s="109" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="107"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="113" t="s">
-        <v>51</v>
-      </c>
-      <c r="F6" s="107"/>
-    </row>
-    <row r="7" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="73">
-        <v>1</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" s="63">
-        <v>1</v>
-      </c>
-      <c r="E7" s="74">
-        <f>E3</f>
-        <v>134.57999999999998</v>
-      </c>
-      <c r="F7" s="107"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B8" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="63">
-        <v>2</v>
-      </c>
-      <c r="E8" s="74">
-        <f>E7*D8</f>
-        <v>269.15999999999997</v>
-      </c>
-      <c r="F8" s="107"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="63">
-        <v>0.3</v>
-      </c>
-      <c r="E9" s="74">
-        <f>ROUNDDOWN(E7*D9,0)</f>
-        <v>40</v>
-      </c>
-      <c r="F9" s="107"/>
-    </row>
-    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="75" t="s">
-        <v>72</v>
-      </c>
-      <c r="B10" s="106" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="78">
-        <v>0.15</v>
-      </c>
-      <c r="E10" s="79">
-        <f>D10*E7</f>
-        <v>20.186999999999998</v>
-      </c>
-      <c r="F10" s="107"/>
-    </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="114"/>
-      <c r="B11" s="114"/>
-      <c r="C11" s="114"/>
-      <c r="D11" s="114"/>
-      <c r="E11" s="114"/>
-      <c r="F11" s="107"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="108"/>
-      <c r="B12" s="109" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="110"/>
-      <c r="E12" s="111"/>
-      <c r="F12" s="107"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="113" t="s">
-        <v>51</v>
-      </c>
-      <c r="F13" s="107"/>
-    </row>
-    <row r="14" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="73">
-        <v>1</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="63">
-        <v>1</v>
-      </c>
-      <c r="E14" s="74">
-        <f>E7</f>
-        <v>134.57999999999998</v>
-      </c>
-      <c r="F14" s="107"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B15" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E15" s="74">
-        <f>E14*D15</f>
-        <v>20.186999999999998</v>
-      </c>
-      <c r="F15" s="107"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" s="65" t="s">
-        <v>106</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" s="63">
-        <v>0.3</v>
-      </c>
-      <c r="E16" s="74">
-        <f>ROUNDDOWN(E14*D16,0)</f>
-        <v>40</v>
-      </c>
-      <c r="F16" s="107"/>
-    </row>
-    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="75" t="s">
-        <v>72</v>
-      </c>
-      <c r="B17" s="105" t="s">
-        <v>107</v>
-      </c>
-      <c r="C17" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="78">
-        <v>1</v>
-      </c>
-      <c r="E17" s="79">
-        <f>D17*E14</f>
-        <v>134.57999999999998</v>
-      </c>
-      <c r="F17" s="107"/>
-    </row>
-    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="107"/>
-      <c r="B18" s="107"/>
-      <c r="C18" s="107"/>
-      <c r="D18" s="107"/>
-      <c r="E18" s="107"/>
-      <c r="F18" s="107"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="108"/>
-      <c r="B19" s="109" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" s="110"/>
-      <c r="D19" s="110"/>
-      <c r="E19" s="111"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E20" s="113" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="73">
-        <v>1</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="63">
-        <v>1</v>
-      </c>
-      <c r="E21" s="74">
-        <f>E14</f>
-        <v>134.57999999999998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B22" s="85" t="s">
-        <v>96</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E22" s="74">
-        <f>D22*E21</f>
-        <v>20.186999999999998</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="75" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="95" t="s">
-        <v>97</v>
-      </c>
-      <c r="C23" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="78">
-        <v>0.3</v>
-      </c>
-      <c r="E23" s="79">
-        <f>D23*E21</f>
-        <v>40.373999999999995</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7.5546875" customWidth="1"/>
-    <col min="2" max="2" width="54.88671875" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" customWidth="1"/>
-    <col min="4" max="4" width="14.5546875" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="69"/>
-      <c r="B1" s="70" t="s">
-        <v>81</v>
-      </c>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="72"/>
-    </row>
-    <row r="2" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="73" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D2" s="63">
-        <v>1</v>
-      </c>
-      <c r="E2" s="74">
-        <v>21.7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="63">
-        <v>0.1</v>
-      </c>
-      <c r="E3" s="74">
-        <f>D3*E2</f>
-        <v>2.17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="75" t="s">
-        <v>72</v>
-      </c>
-      <c r="B4" s="76" t="s">
-        <v>85</v>
-      </c>
-      <c r="C4" s="77" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" s="78">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E4" s="79">
-        <f>D4*E2</f>
-        <v>23.87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="80" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" s="81" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" s="82" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="83">
-        <v>1</v>
-      </c>
-      <c r="E5" s="84">
-        <v>30.17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="73" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="85" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="63">
-        <v>0.25</v>
-      </c>
-      <c r="E6" s="74">
-        <f>E5*D6</f>
-        <v>7.5425000000000004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="73" t="s">
-        <v>88</v>
-      </c>
-      <c r="B7" s="86" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="87" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" s="88">
-        <v>1.8</v>
-      </c>
-      <c r="E7" s="89">
-        <f>E5*D7*20</f>
-        <v>1086.1200000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="73" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="86" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="87" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" s="88">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E8" s="89">
-        <f>E5*D8</f>
-        <v>33.187000000000005</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="90" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="91" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9" s="92" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="93">
-        <v>1</v>
-      </c>
-      <c r="E9" s="94">
-        <v>104.41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="73" t="s">
-        <v>90</v>
-      </c>
-      <c r="B10" s="85" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" s="63">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E10" s="74">
-        <f>E9*D10</f>
-        <v>114.851</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="73" t="s">
-        <v>91</v>
-      </c>
-      <c r="B11" s="85" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="63">
-        <v>1.8</v>
-      </c>
-      <c r="E11" s="74">
-        <f>E9*D11*20</f>
-        <v>3758.7599999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="73" t="s">
-        <v>92</v>
-      </c>
-      <c r="B12" s="104" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E12" s="74">
-        <f>E9*D12</f>
-        <v>15.661499999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="75" t="s">
-        <v>93</v>
-      </c>
-      <c r="B13" s="95" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="77" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="78">
-        <v>1</v>
-      </c>
-      <c r="E13" s="79">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="107"/>
-      <c r="B14" s="107"/>
-      <c r="C14" s="107"/>
-      <c r="D14" s="107"/>
-      <c r="E14" s="107"/>
-      <c r="F14" s="107"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="108"/>
-      <c r="B15" s="109" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="110"/>
-      <c r="D15" s="110"/>
-      <c r="E15" s="111"/>
-      <c r="F15" s="107"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="113" t="s">
-        <v>51</v>
-      </c>
-      <c r="F16" s="107"/>
-    </row>
-    <row r="17" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="73">
-        <v>1</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="63">
-        <v>1</v>
-      </c>
-      <c r="E17" s="74">
-        <f>E9+E5</f>
-        <v>134.57999999999998</v>
-      </c>
-      <c r="F17" s="107"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B18" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="63">
-        <v>2</v>
-      </c>
-      <c r="E18" s="74">
-        <f>E17*D18</f>
-        <v>269.15999999999997</v>
-      </c>
-      <c r="F18" s="107"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" s="63">
-        <v>0.3</v>
-      </c>
-      <c r="E19" s="74">
-        <f>ROUNDDOWN(E17*D19,0)</f>
-        <v>40</v>
-      </c>
-      <c r="F19" s="107"/>
-    </row>
-    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="75" t="s">
-        <v>72</v>
-      </c>
-      <c r="B20" s="106" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="78">
-        <v>0.15</v>
-      </c>
-      <c r="E20" s="79">
-        <f>D20*E17</f>
-        <v>20.186999999999998</v>
-      </c>
-      <c r="F20" s="107"/>
-    </row>
-    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="114"/>
-      <c r="B21" s="114"/>
-      <c r="C21" s="114"/>
-      <c r="D21" s="114"/>
-      <c r="E21" s="114"/>
-      <c r="F21" s="107"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="108"/>
-      <c r="B22" s="109" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" s="110"/>
-      <c r="D22" s="110"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="107"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23" s="113" t="s">
-        <v>51</v>
-      </c>
-      <c r="F23" s="107"/>
-    </row>
-    <row r="24" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="73">
-        <v>1</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="63">
-        <v>1</v>
-      </c>
-      <c r="E24" s="74">
-        <f>E17</f>
-        <v>134.57999999999998</v>
-      </c>
-      <c r="F24" s="107"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B25" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E25" s="74">
-        <f>E24*D25</f>
-        <v>20.186999999999998</v>
-      </c>
-      <c r="F25" s="107"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="65" t="s">
-        <v>106</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="63">
-        <v>0.3</v>
-      </c>
-      <c r="E26" s="74">
-        <f>ROUNDDOWN(E24*D26,0)</f>
-        <v>40</v>
-      </c>
-      <c r="F26" s="107"/>
-    </row>
-    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="75" t="s">
-        <v>72</v>
-      </c>
-      <c r="B27" s="105" t="s">
-        <v>107</v>
-      </c>
-      <c r="C27" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" s="78">
-        <v>1</v>
-      </c>
-      <c r="E27" s="79">
-        <f>D27*E24</f>
-        <v>134.57999999999998</v>
-      </c>
-      <c r="F27" s="107"/>
-    </row>
-    <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="107"/>
-      <c r="B28" s="107"/>
-      <c r="C28" s="107"/>
-      <c r="D28" s="107"/>
-      <c r="E28" s="107"/>
-      <c r="F28" s="107"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="108"/>
-      <c r="B29" s="109" t="s">
-        <v>60</v>
-      </c>
-      <c r="C29" s="110"/>
-      <c r="D29" s="110"/>
-      <c r="E29" s="111"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D30" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E30" s="113" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="73">
-        <v>1</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31" s="63">
-        <v>1</v>
-      </c>
-      <c r="E31" s="74">
-        <f>E24</f>
-        <v>134.57999999999998</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B32" s="85" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D32" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E32" s="74">
-        <f>D32*E31</f>
-        <v>20.186999999999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="75" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" s="95" t="s">
-        <v>97</v>
-      </c>
-      <c r="C33" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D33" s="78">
-        <v>0.3</v>
-      </c>
-      <c r="E33" s="79">
-        <f>D33*E31</f>
-        <v>40.373999999999995</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.21875" style="149" customWidth="1"/>
-    <col min="2" max="2" width="51.5546875" style="142" customWidth="1"/>
-    <col min="3" max="3" width="21.109375" style="142" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" style="142" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="142"/>
-    <col min="6" max="6" width="17.77734375" style="142" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="142"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="141" t="s">
-        <v>122</v>
-      </c>
-      <c r="B1" s="141" t="s">
-        <v>271</v>
-      </c>
-      <c r="C1" s="141" t="s">
-        <v>270</v>
-      </c>
-      <c r="D1" s="141" t="s">
-        <v>49</v>
-      </c>
-      <c r="E1" s="141" t="s">
-        <v>126</v>
-      </c>
-      <c r="F1" s="141" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="130">
-        <v>1</v>
-      </c>
-      <c r="B2" s="143" t="s">
-        <v>108</v>
-      </c>
-      <c r="C2" s="144" t="s">
-        <v>265</v>
-      </c>
-      <c r="D2" s="144" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" s="145">
-        <v>1</v>
-      </c>
-      <c r="F2" s="169">
-        <f>'2-С-Ш1, баз'!F2</f>
-        <v>1350.87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="146" t="s">
-        <v>77</v>
-      </c>
-      <c r="B3" s="147" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="144"/>
-      <c r="D3" s="130" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="148">
-        <v>0.15</v>
-      </c>
-      <c r="F3" s="170">
-        <f>$F$2*E3</f>
-        <v>202.63049999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="146" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="147" t="s">
-        <v>201</v>
-      </c>
-      <c r="C4" s="144"/>
-      <c r="D4" s="130" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="148">
-        <v>1.5</v>
-      </c>
-      <c r="F4" s="170">
-        <f>$F$2*E4</f>
-        <v>2026.3049999999998</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -4566,7 +2970,7 @@
       <c r="E2" s="145">
         <v>1</v>
       </c>
-      <c r="F2" s="169">
+      <c r="F2" s="162">
         <f>611.19+739.68</f>
         <v>1350.87</v>
       </c>
@@ -4585,7 +2989,7 @@
       <c r="E3" s="148">
         <v>1.5</v>
       </c>
-      <c r="F3" s="170">
+      <c r="F3" s="163">
         <f>$F$2*E3</f>
         <v>2026.3049999999998</v>
       </c>
@@ -4604,7 +3008,7 @@
       <c r="E4" s="148">
         <v>0.3</v>
       </c>
-      <c r="F4" s="170">
+      <c r="F4" s="163">
         <f>$F$2*E4</f>
         <v>405.26099999999997</v>
       </c>
@@ -4623,7 +3027,7 @@
       <c r="E5" s="148">
         <v>0.15</v>
       </c>
-      <c r="F5" s="170">
+      <c r="F5" s="163">
         <f>$F$2*E5</f>
         <v>202.63049999999998</v>
       </c>
@@ -4633,7 +3037,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -4683,7 +3087,7 @@
       <c r="E2" s="136">
         <v>1</v>
       </c>
-      <c r="F2" s="167">
+      <c r="F2" s="160">
         <f>685.31+(3.1+4.2+4.8)*3.12-11</f>
         <v>712.0619999999999</v>
       </c>
@@ -4702,7 +3106,7 @@
       <c r="E3" s="138">
         <v>1</v>
       </c>
-      <c r="F3" s="168">
+      <c r="F3" s="161">
         <f>$F$2*E3</f>
         <v>712.0619999999999</v>
       </c>
@@ -4723,7 +3127,7 @@
       <c r="E4" s="138">
         <v>0.8</v>
       </c>
-      <c r="F4" s="168">
+      <c r="F4" s="161">
         <f>$F$2*E4</f>
         <v>569.64959999999996</v>
       </c>
@@ -4744,7 +3148,7 @@
       <c r="E5" s="138">
         <v>2.1</v>
       </c>
-      <c r="F5" s="168">
+      <c r="F5" s="161">
         <f t="shared" ref="F5:F7" si="0">$F$2*E5</f>
         <v>1495.3301999999999</v>
       </c>
@@ -4765,7 +3169,7 @@
       <c r="E6" s="138">
         <v>4.2</v>
       </c>
-      <c r="F6" s="168">
+      <c r="F6" s="161">
         <f t="shared" si="0"/>
         <v>2990.6603999999998</v>
       </c>
@@ -4786,7 +3190,7 @@
       <c r="E7" s="138">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="F7" s="168">
+      <c r="F7" s="161">
         <f t="shared" si="0"/>
         <v>37.02722399999999</v>
       </c>
@@ -4797,7 +3201,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I86"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
@@ -4836,15 +3240,15 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="163" t="s">
+      <c r="A2" s="206" t="s">
         <v>251</v>
       </c>
-      <c r="B2" s="164"/>
-      <c r="C2" s="164"/>
-      <c r="D2" s="164"/>
-      <c r="E2" s="164"/>
-      <c r="F2" s="164"/>
-      <c r="G2" s="164"/>
+      <c r="B2" s="207"/>
+      <c r="C2" s="207"/>
+      <c r="D2" s="207"/>
+      <c r="E2" s="207"/>
+      <c r="F2" s="207"/>
+      <c r="G2" s="207"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="117" t="s">
@@ -4853,13 +3257,13 @@
       <c r="B3" s="117" t="s">
         <v>249</v>
       </c>
-      <c r="C3" s="160" t="s">
+      <c r="C3" s="203" t="s">
         <v>248</v>
       </c>
-      <c r="D3" s="161"/>
-      <c r="E3" s="161"/>
-      <c r="F3" s="161"/>
-      <c r="G3" s="161"/>
+      <c r="D3" s="204"/>
+      <c r="E3" s="204"/>
+      <c r="F3" s="204"/>
+      <c r="G3" s="204"/>
     </row>
     <row r="4" spans="1:7" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="117" t="s">
@@ -4967,13 +3371,13 @@
       <c r="B9" s="117" t="s">
         <v>129</v>
       </c>
-      <c r="C9" s="160" t="s">
+      <c r="C9" s="203" t="s">
         <v>130</v>
       </c>
-      <c r="D9" s="161"/>
-      <c r="E9" s="161"/>
-      <c r="F9" s="161"/>
-      <c r="G9" s="162"/>
+      <c r="D9" s="204"/>
+      <c r="E9" s="204"/>
+      <c r="F9" s="204"/>
+      <c r="G9" s="205"/>
     </row>
     <row r="10" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A10" s="117" t="s">
@@ -6450,13 +4854,13 @@
       <c r="B83" s="117" t="s">
         <v>229</v>
       </c>
-      <c r="C83" s="160" t="s">
+      <c r="C83" s="203" t="s">
         <v>230</v>
       </c>
-      <c r="D83" s="161"/>
-      <c r="E83" s="161"/>
-      <c r="F83" s="161"/>
-      <c r="G83" s="162"/>
+      <c r="D83" s="204"/>
+      <c r="E83" s="204"/>
+      <c r="F83" s="204"/>
+      <c r="G83" s="205"/>
     </row>
     <row r="84" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A84" s="117" t="s">
@@ -6506,7 +4910,7 @@
         <v>113.11499999999999</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A86" s="117" t="s">
         <v>235</v>
       </c>
@@ -6539,7 +4943,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:D18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6692,7 +5096,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A4:F92"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
@@ -7552,7 +5956,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A15:E33"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7783,7 +6187,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7836,11 +6240,11 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="165"/>
-      <c r="B4" s="165"/>
-      <c r="C4" s="165"/>
-      <c r="D4" s="165"/>
-      <c r="E4" s="165"/>
+      <c r="A4" s="208"/>
+      <c r="B4" s="208"/>
+      <c r="C4" s="208"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="208"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="58"/>
@@ -7922,11 +6326,11 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="166"/>
-      <c r="B10" s="166"/>
-      <c r="C10" s="166"/>
-      <c r="D10" s="166"/>
-      <c r="E10" s="166"/>
+      <c r="A10" s="209"/>
+      <c r="B10" s="209"/>
+      <c r="C10" s="209"/>
+      <c r="D10" s="209"/>
+      <c r="E10" s="209"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="58"/>
@@ -8009,11 +6413,11 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="165"/>
-      <c r="B16" s="165"/>
-      <c r="C16" s="165"/>
-      <c r="D16" s="165"/>
-      <c r="E16" s="165"/>
+      <c r="A16" s="208"/>
+      <c r="B16" s="208"/>
+      <c r="C16" s="208"/>
+      <c r="D16" s="208"/>
+      <c r="E16" s="208"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="58"/>
@@ -8103,4 +6507,3700 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="51" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="58"/>
+      <c r="B1" s="59" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="G1" s="67"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="67"/>
+    </row>
+    <row r="3" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="62">
+        <v>1</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="63">
+        <v>1</v>
+      </c>
+      <c r="E3" s="17">
+        <v>37.44</v>
+      </c>
+      <c r="F3" s="68"/>
+      <c r="G3" s="67"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="63">
+        <v>1</v>
+      </c>
+      <c r="E4" s="17">
+        <v>22</v>
+      </c>
+      <c r="F4" s="68"/>
+      <c r="G4" s="67"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="63">
+        <v>1</v>
+      </c>
+      <c r="E5" s="17">
+        <v>201</v>
+      </c>
+      <c r="F5" s="68"/>
+      <c r="G5" s="67"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="62" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="63">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E6" s="17">
+        <v>41.183999999999997</v>
+      </c>
+      <c r="F6" s="68"/>
+      <c r="G6" s="67"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="208"/>
+      <c r="B7" s="208"/>
+      <c r="C7" s="208"/>
+      <c r="D7" s="208"/>
+      <c r="E7" s="208"/>
+      <c r="G7" s="67"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="58"/>
+      <c r="B8" s="59" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="G8" s="66"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="66"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="62">
+        <v>1</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="63">
+        <v>1</v>
+      </c>
+      <c r="E10" s="17">
+        <v>37.44</v>
+      </c>
+      <c r="G10" s="66"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="62">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B11" s="64" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="63">
+        <v>1.8</v>
+      </c>
+      <c r="E11" s="17">
+        <f>E10*D11</f>
+        <v>67.391999999999996</v>
+      </c>
+      <c r="G11" s="66"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="17">
+        <f>E10*D12</f>
+        <v>5.6159999999999997</v>
+      </c>
+      <c r="G12" s="66"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="209"/>
+      <c r="B13" s="209"/>
+      <c r="C13" s="209"/>
+      <c r="D13" s="209"/>
+      <c r="E13" s="209"/>
+      <c r="G13" s="66"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="58"/>
+      <c r="B14" s="59" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="G14" s="66"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15" s="66"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="62">
+        <v>1</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="63">
+        <v>1</v>
+      </c>
+      <c r="E16" s="17">
+        <f>E10</f>
+        <v>37.44</v>
+      </c>
+      <c r="G16" s="66"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="62">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B17" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E17" s="17">
+        <f>E16*D17</f>
+        <v>5.6159999999999997</v>
+      </c>
+      <c r="G17" s="66"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="65" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="63">
+        <v>1.8</v>
+      </c>
+      <c r="E18" s="17">
+        <f>E16*D18</f>
+        <v>67.391999999999996</v>
+      </c>
+      <c r="G18" s="66"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="208"/>
+      <c r="B19" s="208"/>
+      <c r="C19" s="208"/>
+      <c r="D19" s="208"/>
+      <c r="E19" s="208"/>
+      <c r="G19" s="66"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="58"/>
+      <c r="B20" s="59" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="G20" s="66"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" s="66"/>
+    </row>
+    <row r="22" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="62">
+        <v>1</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="63">
+        <v>1</v>
+      </c>
+      <c r="E22" s="17">
+        <v>37.44</v>
+      </c>
+      <c r="G22" s="66"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="62">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B23" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E23" s="17">
+        <f>E22*D23</f>
+        <v>5.6159999999999997</v>
+      </c>
+      <c r="G23" s="66"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E24" s="17">
+        <f>E22*D24</f>
+        <v>11.231999999999999</v>
+      </c>
+      <c r="G24" s="66"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A13:E13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.5546875" customWidth="1"/>
+    <col min="2" max="2" width="54.88671875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="58"/>
+      <c r="B1" s="116" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+    </row>
+    <row r="2" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="60" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="62">
+        <v>1</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="63">
+        <v>1</v>
+      </c>
+      <c r="E3" s="17">
+        <v>16.54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" s="63">
+        <v>1</v>
+      </c>
+      <c r="E4" s="17">
+        <f>E3</f>
+        <v>16.54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="63">
+        <v>1.42</v>
+      </c>
+      <c r="E5" s="17">
+        <f>D5*E3*2</f>
+        <v>46.973599999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="62" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="63">
+        <v>2.1</v>
+      </c>
+      <c r="E6" s="17">
+        <f>D6*E3</f>
+        <v>34.734000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="62" t="s">
+        <v>120</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="63">
+        <v>4.07</v>
+      </c>
+      <c r="E7" s="17">
+        <f>D7*E3</f>
+        <v>67.317800000000005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="107"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="96"/>
+      <c r="B9" s="97" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="98"/>
+      <c r="D9" s="98"/>
+      <c r="E9" s="99"/>
+    </row>
+    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="100" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="101" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="102" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="102" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="103" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="90">
+        <v>1</v>
+      </c>
+      <c r="B11" s="91" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="92" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="93">
+        <v>1</v>
+      </c>
+      <c r="E11" s="94">
+        <v>33.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B12" s="85" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E12" s="74">
+        <f>E11*D12</f>
+        <v>9.9749999999999996</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="85" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="63">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E13" s="74">
+        <f>D13*E11</f>
+        <v>36.575000000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="107"/>
+      <c r="B14" s="107"/>
+      <c r="C14" s="107"/>
+      <c r="D14" s="107"/>
+      <c r="E14" s="107"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="108"/>
+      <c r="B15" s="109" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="110"/>
+      <c r="D15" s="110"/>
+      <c r="E15" s="111"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="113" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="73">
+        <v>1</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="63">
+        <v>1</v>
+      </c>
+      <c r="E17" s="74">
+        <f>E3</f>
+        <v>16.54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B18" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="63">
+        <v>2</v>
+      </c>
+      <c r="E18" s="74">
+        <f>E17*D18</f>
+        <v>33.08</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E19" s="74">
+        <f>ROUNDDOWN(E17*D19,0)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="78">
+        <v>0.15</v>
+      </c>
+      <c r="E20" s="79">
+        <f>D20*E17</f>
+        <v>2.4809999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="107"/>
+      <c r="B21" s="107"/>
+      <c r="C21" s="107"/>
+      <c r="D21" s="107"/>
+      <c r="E21" s="107"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="108"/>
+      <c r="B22" s="109" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" s="110"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="111"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="113" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="73">
+        <v>1</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="63">
+        <v>1</v>
+      </c>
+      <c r="E24" s="74">
+        <f>79.16+E3</f>
+        <v>95.699999999999989</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B25" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E25" s="115">
+        <f>E24*D25</f>
+        <v>14.354999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="65" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="63">
+        <v>2</v>
+      </c>
+      <c r="E26" s="74">
+        <f>E24*D26</f>
+        <v>191.39999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="107"/>
+      <c r="B27" s="107"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="107"/>
+      <c r="E27" s="107"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="108"/>
+      <c r="B28" s="109" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" s="110"/>
+      <c r="D28" s="110"/>
+      <c r="E28" s="111"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29" s="113" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="73">
+        <v>1</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" s="63">
+        <v>1</v>
+      </c>
+      <c r="E30" s="74">
+        <v>970.52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B31" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E31" s="74">
+        <f>E30*D31</f>
+        <v>145.578</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="105" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="78">
+        <v>2</v>
+      </c>
+      <c r="E32" s="79">
+        <f>D32*E30</f>
+        <v>1941.04</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="107"/>
+      <c r="B33" s="107"/>
+      <c r="C33" s="107"/>
+      <c r="D33" s="107"/>
+      <c r="E33" s="107"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="96"/>
+      <c r="B34" s="97" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" s="98"/>
+      <c r="D34" s="98"/>
+      <c r="E34" s="99"/>
+    </row>
+    <row r="35" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="100" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" s="101" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="102" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="102" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="103" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A36" s="90">
+        <v>1</v>
+      </c>
+      <c r="B36" s="91" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" s="93">
+        <v>1</v>
+      </c>
+      <c r="E36" s="94">
+        <f>E24+E30</f>
+        <v>1066.22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B37" s="86" t="s">
+        <v>96</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" s="88">
+        <v>0.15</v>
+      </c>
+      <c r="E37" s="89">
+        <f>D37*E36</f>
+        <v>159.93299999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="95" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D38" s="78">
+        <v>0.3</v>
+      </c>
+      <c r="E38" s="79">
+        <f>D38*E36</f>
+        <v>319.86599999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.5546875" customWidth="1"/>
+    <col min="2" max="2" width="54.88671875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="69"/>
+      <c r="B1" s="70" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="72"/>
+    </row>
+    <row r="2" spans="1:6" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="73" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="63">
+        <v>1</v>
+      </c>
+      <c r="E2" s="74">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="80" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="81" t="s">
+        <v>253</v>
+      </c>
+      <c r="C3" s="82" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="83">
+        <v>1</v>
+      </c>
+      <c r="E3" s="84">
+        <v>134.57999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="107"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="108"/>
+      <c r="B5" s="109" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="111"/>
+      <c r="F5" s="107"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="113" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="107"/>
+    </row>
+    <row r="7" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="73">
+        <v>1</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="63">
+        <v>1</v>
+      </c>
+      <c r="E7" s="74">
+        <f>E3</f>
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F7" s="107"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="63">
+        <v>2</v>
+      </c>
+      <c r="E8" s="74">
+        <f>E7*D8</f>
+        <v>269.15999999999997</v>
+      </c>
+      <c r="F8" s="107"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E9" s="74">
+        <f>ROUNDDOWN(E7*D9,0)</f>
+        <v>40</v>
+      </c>
+      <c r="F9" s="107"/>
+    </row>
+    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="78">
+        <v>0.15</v>
+      </c>
+      <c r="E10" s="79">
+        <f>D10*E7</f>
+        <v>20.186999999999998</v>
+      </c>
+      <c r="F10" s="107"/>
+    </row>
+    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="114"/>
+      <c r="B11" s="114"/>
+      <c r="C11" s="114"/>
+      <c r="D11" s="114"/>
+      <c r="E11" s="114"/>
+      <c r="F11" s="107"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="108"/>
+      <c r="B12" s="109" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="110"/>
+      <c r="D12" s="110"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="107"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="113" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="107"/>
+    </row>
+    <row r="14" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="73">
+        <v>1</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="63">
+        <v>1</v>
+      </c>
+      <c r="E14" s="74">
+        <f>E7</f>
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F14" s="107"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B15" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E15" s="74">
+        <f>E14*D15</f>
+        <v>20.186999999999998</v>
+      </c>
+      <c r="F15" s="107"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="65" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E16" s="74">
+        <f>ROUNDDOWN(E14*D16,0)</f>
+        <v>40</v>
+      </c>
+      <c r="F16" s="107"/>
+    </row>
+    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="105" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="78">
+        <v>1</v>
+      </c>
+      <c r="E17" s="79">
+        <f>D17*E14</f>
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F17" s="107"/>
+    </row>
+    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="107"/>
+      <c r="B18" s="107"/>
+      <c r="C18" s="107"/>
+      <c r="D18" s="107"/>
+      <c r="E18" s="107"/>
+      <c r="F18" s="107"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="108"/>
+      <c r="B19" s="109" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="110"/>
+      <c r="D19" s="110"/>
+      <c r="E19" s="111"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="113" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="73">
+        <v>1</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="63">
+        <v>1</v>
+      </c>
+      <c r="E21" s="74">
+        <f>E14</f>
+        <v>134.57999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B22" s="85" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E22" s="74">
+        <f>D22*E21</f>
+        <v>20.186999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="95" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="78">
+        <v>0.3</v>
+      </c>
+      <c r="E23" s="79">
+        <f>D23*E21</f>
+        <v>40.373999999999995</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.21875" style="166" customWidth="1"/>
+    <col min="2" max="2" width="37" style="142" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" style="142" customWidth="1"/>
+    <col min="4" max="4" width="9" style="142" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" style="142" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="142"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="141" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="150" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1" s="150" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1" s="150" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="150" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="130">
+        <v>1</v>
+      </c>
+      <c r="B2" s="152" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="152" t="s">
+        <v>263</v>
+      </c>
+      <c r="D2" s="152" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="176">
+        <v>74.599999999999994</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="130">
+        <v>2</v>
+      </c>
+      <c r="B3" s="152" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="152" t="s">
+        <v>265</v>
+      </c>
+      <c r="D3" s="152" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="177">
+        <v>74.599999999999994</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.5546875" customWidth="1"/>
+    <col min="2" max="2" width="54.88671875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="69"/>
+      <c r="B1" s="70" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="72"/>
+    </row>
+    <row r="2" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="73" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="63">
+        <v>1</v>
+      </c>
+      <c r="E2" s="74">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="63">
+        <v>0.1</v>
+      </c>
+      <c r="E3" s="74">
+        <f>D3*E2</f>
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="76" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="78">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E4" s="79">
+        <f>D4*E2</f>
+        <v>23.87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="80" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="81" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="82" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="83">
+        <v>1</v>
+      </c>
+      <c r="E5" s="84">
+        <v>30.17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="73" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="85" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="63">
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="74">
+        <f>E5*D6</f>
+        <v>7.5425000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="73" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="87" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="88">
+        <v>1.8</v>
+      </c>
+      <c r="E7" s="89">
+        <f>E5*D7*20</f>
+        <v>1086.1200000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="73" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="86" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="87" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="88">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E8" s="89">
+        <f>E5*D8</f>
+        <v>33.187000000000005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="90" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="91" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="92" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="93">
+        <v>1</v>
+      </c>
+      <c r="E9" s="94">
+        <v>104.41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="73" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="85" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="63">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E10" s="74">
+        <f>E9*D10</f>
+        <v>114.851</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="73" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="85" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="63">
+        <v>1.8</v>
+      </c>
+      <c r="E11" s="74">
+        <f>E9*D11*20</f>
+        <v>3758.7599999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="73" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="104" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="74">
+        <f>E9*D12</f>
+        <v>15.661499999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="75" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="95" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="78">
+        <v>1</v>
+      </c>
+      <c r="E13" s="79">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="107"/>
+      <c r="B14" s="107"/>
+      <c r="C14" s="107"/>
+      <c r="D14" s="107"/>
+      <c r="E14" s="107"/>
+      <c r="F14" s="107"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="108"/>
+      <c r="B15" s="109" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="110"/>
+      <c r="D15" s="110"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="107"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="113" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" s="107"/>
+    </row>
+    <row r="17" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="73">
+        <v>1</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="63">
+        <v>1</v>
+      </c>
+      <c r="E17" s="74">
+        <f>E9+E5</f>
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F17" s="107"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B18" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="63">
+        <v>2</v>
+      </c>
+      <c r="E18" s="74">
+        <f>E17*D18</f>
+        <v>269.15999999999997</v>
+      </c>
+      <c r="F18" s="107"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E19" s="74">
+        <f>ROUNDDOWN(E17*D19,0)</f>
+        <v>40</v>
+      </c>
+      <c r="F19" s="107"/>
+    </row>
+    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="78">
+        <v>0.15</v>
+      </c>
+      <c r="E20" s="79">
+        <f>D20*E17</f>
+        <v>20.186999999999998</v>
+      </c>
+      <c r="F20" s="107"/>
+    </row>
+    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="114"/>
+      <c r="B21" s="114"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="114"/>
+      <c r="E21" s="114"/>
+      <c r="F21" s="107"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="108"/>
+      <c r="B22" s="109" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="110"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="111"/>
+      <c r="F22" s="107"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="113" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="107"/>
+    </row>
+    <row r="24" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="73">
+        <v>1</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="63">
+        <v>1</v>
+      </c>
+      <c r="E24" s="74">
+        <f>E17</f>
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F24" s="107"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B25" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E25" s="74">
+        <f>E24*D25</f>
+        <v>20.186999999999998</v>
+      </c>
+      <c r="F25" s="107"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="65" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E26" s="74">
+        <f>ROUNDDOWN(E24*D26,0)</f>
+        <v>40</v>
+      </c>
+      <c r="F26" s="107"/>
+    </row>
+    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" s="105" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="78">
+        <v>1</v>
+      </c>
+      <c r="E27" s="79">
+        <f>D27*E24</f>
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F27" s="107"/>
+    </row>
+    <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="107"/>
+      <c r="B28" s="107"/>
+      <c r="C28" s="107"/>
+      <c r="D28" s="107"/>
+      <c r="E28" s="107"/>
+      <c r="F28" s="107"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="108"/>
+      <c r="B29" s="109" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="110"/>
+      <c r="D29" s="110"/>
+      <c r="E29" s="111"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30" s="113" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="73">
+        <v>1</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="63">
+        <v>1</v>
+      </c>
+      <c r="E31" s="74">
+        <f>E24</f>
+        <v>134.57999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B32" s="85" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E32" s="74">
+        <f>D32*E31</f>
+        <v>20.186999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="95" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="78">
+        <v>0.3</v>
+      </c>
+      <c r="E33" s="79">
+        <f>D33*E31</f>
+        <v>40.373999999999995</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.21875" style="159" customWidth="1"/>
+    <col min="2" max="2" width="37" style="142" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" style="142" customWidth="1"/>
+    <col min="4" max="4" width="9" style="142" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" style="142" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="142"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="141" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="150" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1" s="150" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1" s="150" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="150" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="130">
+        <v>1</v>
+      </c>
+      <c r="B2" s="152" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2" s="152" t="s">
+        <v>308</v>
+      </c>
+      <c r="D2" s="152" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="176">
+        <v>74.599999999999994</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.21875" style="159" customWidth="1"/>
+    <col min="2" max="2" width="37" style="142" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" style="142" customWidth="1"/>
+    <col min="4" max="4" width="9" style="142" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" style="142" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="142"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="141" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="150" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1" s="150" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1" s="150" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="150" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="130">
+        <v>1</v>
+      </c>
+      <c r="B2" s="152" t="s">
+        <v>311</v>
+      </c>
+      <c r="C2" s="152" t="s">
+        <v>306</v>
+      </c>
+      <c r="D2" s="152" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="177">
+        <v>74.599999999999994</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.21875" style="159" customWidth="1"/>
+    <col min="2" max="2" width="12" style="142" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" style="142" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" style="142" customWidth="1"/>
+    <col min="5" max="5" width="16.21875" style="142" customWidth="1"/>
+    <col min="6" max="6" width="9" style="142" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" style="142" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="142"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="141" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="180" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1" s="181"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="150" t="s">
+        <v>270</v>
+      </c>
+      <c r="F1" s="150" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" s="150" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="130">
+        <v>1</v>
+      </c>
+      <c r="B2" s="183" t="s">
+        <v>322</v>
+      </c>
+      <c r="C2" s="184"/>
+      <c r="D2" s="185"/>
+      <c r="E2" s="152" t="s">
+        <v>320</v>
+      </c>
+      <c r="F2" s="152" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="154">
+        <v>242.10000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="130">
+        <v>2</v>
+      </c>
+      <c r="B3" s="183" t="s">
+        <v>322</v>
+      </c>
+      <c r="C3" s="184"/>
+      <c r="D3" s="185"/>
+      <c r="E3" s="152" t="s">
+        <v>321</v>
+      </c>
+      <c r="F3" s="152" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="158">
+        <v>723.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="130">
+        <v>3</v>
+      </c>
+      <c r="B4" s="183" t="s">
+        <v>314</v>
+      </c>
+      <c r="C4" s="184"/>
+      <c r="D4" s="185"/>
+      <c r="E4" s="152" t="s">
+        <v>319</v>
+      </c>
+      <c r="F4" s="152" t="s">
+        <v>313</v>
+      </c>
+      <c r="G4" s="154">
+        <v>302.39999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="186"/>
+      <c r="B5" s="186"/>
+      <c r="C5" s="186"/>
+      <c r="D5" s="186"/>
+      <c r="E5" s="186"/>
+      <c r="F5" s="186"/>
+      <c r="G5" s="186"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="175" t="s">
+        <v>304</v>
+      </c>
+      <c r="B6" s="175" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="210"/>
+      <c r="D6" s="175" t="s">
+        <v>304</v>
+      </c>
+      <c r="E6" s="175" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="178"/>
+      <c r="G6" s="212"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="175" t="s">
+        <v>327</v>
+      </c>
+      <c r="B7" s="175">
+        <v>63.9</v>
+      </c>
+      <c r="C7" s="210"/>
+      <c r="D7" s="175" t="s">
+        <v>329</v>
+      </c>
+      <c r="E7" s="175">
+        <v>157.30000000000001</v>
+      </c>
+      <c r="F7" s="178"/>
+      <c r="G7" s="212"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="175" t="s">
+        <v>293</v>
+      </c>
+      <c r="B8" s="175">
+        <v>143.4</v>
+      </c>
+      <c r="C8" s="210"/>
+      <c r="D8" s="175" t="s">
+        <v>330</v>
+      </c>
+      <c r="E8" s="175">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="F8" s="178"/>
+      <c r="G8" s="212"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="175" t="s">
+        <v>328</v>
+      </c>
+      <c r="B9" s="175">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="C9" s="210"/>
+      <c r="D9" s="175" t="s">
+        <v>331</v>
+      </c>
+      <c r="E9" s="175">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F9" s="178"/>
+      <c r="G9" s="212"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="175" t="s">
+        <v>298</v>
+      </c>
+      <c r="B10" s="165">
+        <f>SUM(B7:B9)</f>
+        <v>242.10000000000002</v>
+      </c>
+      <c r="C10" s="210"/>
+      <c r="D10" s="175" t="s">
+        <v>332</v>
+      </c>
+      <c r="E10" s="175">
+        <v>20.6</v>
+      </c>
+      <c r="F10" s="178"/>
+      <c r="G10" s="212"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="193"/>
+      <c r="B11" s="193"/>
+      <c r="C11" s="210"/>
+      <c r="D11" s="175" t="s">
+        <v>284</v>
+      </c>
+      <c r="E11" s="175">
+        <v>104.1</v>
+      </c>
+      <c r="F11" s="178"/>
+      <c r="G11" s="212"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="198"/>
+      <c r="B12" s="198"/>
+      <c r="C12" s="210"/>
+      <c r="D12" s="175" t="s">
+        <v>277</v>
+      </c>
+      <c r="E12" s="175">
+        <v>108.2</v>
+      </c>
+      <c r="F12" s="178"/>
+      <c r="G12" s="212"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="198"/>
+      <c r="B13" s="198"/>
+      <c r="C13" s="210"/>
+      <c r="D13" s="175" t="s">
+        <v>274</v>
+      </c>
+      <c r="E13" s="175">
+        <v>305.39999999999998</v>
+      </c>
+      <c r="F13" s="178"/>
+      <c r="G13" s="212"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="198"/>
+      <c r="B14" s="198"/>
+      <c r="C14" s="210"/>
+      <c r="D14" s="175" t="s">
+        <v>298</v>
+      </c>
+      <c r="E14" s="165">
+        <f>SUM(E7:E13)</f>
+        <v>723.39999999999986</v>
+      </c>
+      <c r="F14" s="178"/>
+      <c r="G14" s="212"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="F6:G14"/>
+    <mergeCell ref="A11:B14"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="C6:C14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.21875" style="159" customWidth="1"/>
+    <col min="2" max="2" width="12" style="142" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" style="142" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" style="142" customWidth="1"/>
+    <col min="5" max="5" width="16.21875" style="142" customWidth="1"/>
+    <col min="6" max="6" width="9" style="142" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" style="142" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="142"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="141" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="180" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1" s="181"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="150" t="s">
+        <v>270</v>
+      </c>
+      <c r="F1" s="150" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" s="150" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="130">
+        <v>1</v>
+      </c>
+      <c r="B2" s="183" t="s">
+        <v>318</v>
+      </c>
+      <c r="C2" s="184"/>
+      <c r="D2" s="185"/>
+      <c r="E2" s="152" t="s">
+        <v>309</v>
+      </c>
+      <c r="F2" s="152" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="154">
+        <f>B10</f>
+        <v>242.10000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="130">
+        <v>2</v>
+      </c>
+      <c r="B3" s="183" t="s">
+        <v>318</v>
+      </c>
+      <c r="C3" s="184"/>
+      <c r="D3" s="185"/>
+      <c r="E3" s="152" t="s">
+        <v>310</v>
+      </c>
+      <c r="F3" s="152" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="158">
+        <f>E14</f>
+        <v>723.39999999999986</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="130">
+        <v>3</v>
+      </c>
+      <c r="B4" s="183" t="s">
+        <v>312</v>
+      </c>
+      <c r="C4" s="184"/>
+      <c r="D4" s="185"/>
+      <c r="E4" s="152" t="s">
+        <v>315</v>
+      </c>
+      <c r="F4" s="152" t="s">
+        <v>313</v>
+      </c>
+      <c r="G4" s="154">
+        <v>302.39999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="186"/>
+      <c r="B5" s="186"/>
+      <c r="C5" s="186"/>
+      <c r="D5" s="186"/>
+      <c r="E5" s="186"/>
+      <c r="F5" s="186"/>
+      <c r="G5" s="186"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="175" t="s">
+        <v>304</v>
+      </c>
+      <c r="B6" s="175" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="210"/>
+      <c r="D6" s="175" t="s">
+        <v>304</v>
+      </c>
+      <c r="E6" s="175" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="178"/>
+      <c r="G6" s="212"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="175" t="s">
+        <v>327</v>
+      </c>
+      <c r="B7" s="175">
+        <v>63.9</v>
+      </c>
+      <c r="C7" s="210"/>
+      <c r="D7" s="175" t="s">
+        <v>329</v>
+      </c>
+      <c r="E7" s="175">
+        <v>157.30000000000001</v>
+      </c>
+      <c r="F7" s="178"/>
+      <c r="G7" s="212"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="175" t="s">
+        <v>293</v>
+      </c>
+      <c r="B8" s="175">
+        <v>143.4</v>
+      </c>
+      <c r="C8" s="210"/>
+      <c r="D8" s="175" t="s">
+        <v>330</v>
+      </c>
+      <c r="E8" s="175">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="F8" s="178"/>
+      <c r="G8" s="212"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="175" t="s">
+        <v>328</v>
+      </c>
+      <c r="B9" s="175">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="C9" s="210"/>
+      <c r="D9" s="175" t="s">
+        <v>331</v>
+      </c>
+      <c r="E9" s="175">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F9" s="178"/>
+      <c r="G9" s="212"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="175" t="s">
+        <v>298</v>
+      </c>
+      <c r="B10" s="165">
+        <f>SUM(B7:B9)</f>
+        <v>242.10000000000002</v>
+      </c>
+      <c r="C10" s="210"/>
+      <c r="D10" s="175" t="s">
+        <v>332</v>
+      </c>
+      <c r="E10" s="175">
+        <v>20.6</v>
+      </c>
+      <c r="F10" s="178"/>
+      <c r="G10" s="212"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="193"/>
+      <c r="B11" s="193"/>
+      <c r="C11" s="210"/>
+      <c r="D11" s="175" t="s">
+        <v>284</v>
+      </c>
+      <c r="E11" s="175">
+        <v>104.1</v>
+      </c>
+      <c r="F11" s="178"/>
+      <c r="G11" s="212"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="198"/>
+      <c r="B12" s="198"/>
+      <c r="C12" s="210"/>
+      <c r="D12" s="175" t="s">
+        <v>277</v>
+      </c>
+      <c r="E12" s="175">
+        <v>108.2</v>
+      </c>
+      <c r="F12" s="178"/>
+      <c r="G12" s="212"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="198"/>
+      <c r="B13" s="198"/>
+      <c r="C13" s="210"/>
+      <c r="D13" s="175" t="s">
+        <v>274</v>
+      </c>
+      <c r="E13" s="175">
+        <v>305.39999999999998</v>
+      </c>
+      <c r="F13" s="178"/>
+      <c r="G13" s="212"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="198"/>
+      <c r="B14" s="198"/>
+      <c r="C14" s="210"/>
+      <c r="D14" s="175" t="s">
+        <v>298</v>
+      </c>
+      <c r="E14" s="165">
+        <f>SUM(E7:E13)</f>
+        <v>723.39999999999986</v>
+      </c>
+      <c r="F14" s="178"/>
+      <c r="G14" s="212"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="C6:C14"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="F6:G14"/>
+    <mergeCell ref="A11:B14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.77734375" style="159" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" style="142" customWidth="1"/>
+    <col min="3" max="4" width="9.77734375" style="142" customWidth="1"/>
+    <col min="5" max="5" width="12" style="142" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" style="142" customWidth="1"/>
+    <col min="7" max="7" width="9" style="142" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="142" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="142"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="169" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="187" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1" s="189"/>
+      <c r="D1" s="188"/>
+      <c r="E1" s="187" t="s">
+        <v>270</v>
+      </c>
+      <c r="F1" s="188"/>
+      <c r="G1" s="170" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="170" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="171">
+        <v>1</v>
+      </c>
+      <c r="B2" s="190" t="s">
+        <v>295</v>
+      </c>
+      <c r="C2" s="191"/>
+      <c r="D2" s="192"/>
+      <c r="E2" s="187" t="s">
+        <v>299</v>
+      </c>
+      <c r="F2" s="188"/>
+      <c r="G2" s="170" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" s="172">
+        <f>B35</f>
+        <v>4042.9000000000005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="171">
+        <v>2</v>
+      </c>
+      <c r="B3" s="190" t="s">
+        <v>295</v>
+      </c>
+      <c r="C3" s="191"/>
+      <c r="D3" s="192"/>
+      <c r="E3" s="187" t="s">
+        <v>301</v>
+      </c>
+      <c r="F3" s="188"/>
+      <c r="G3" s="170" t="s">
+        <v>70</v>
+      </c>
+      <c r="H3" s="173">
+        <f>E39</f>
+        <v>3847.3999999999996</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="171">
+        <v>3</v>
+      </c>
+      <c r="B4" s="190" t="s">
+        <v>295</v>
+      </c>
+      <c r="C4" s="191"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="187" t="s">
+        <v>316</v>
+      </c>
+      <c r="F4" s="188"/>
+      <c r="G4" s="170" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" s="172">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="171">
+        <v>4</v>
+      </c>
+      <c r="B5" s="190" t="s">
+        <v>295</v>
+      </c>
+      <c r="C5" s="191"/>
+      <c r="D5" s="192"/>
+      <c r="E5" s="187" t="s">
+        <v>317</v>
+      </c>
+      <c r="F5" s="188"/>
+      <c r="G5" s="170" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" s="173">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="171">
+        <v>5</v>
+      </c>
+      <c r="B6" s="190" t="s">
+        <v>295</v>
+      </c>
+      <c r="C6" s="191"/>
+      <c r="D6" s="192"/>
+      <c r="E6" s="187" t="s">
+        <v>302</v>
+      </c>
+      <c r="F6" s="188"/>
+      <c r="G6" s="170" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" s="172">
+        <f>H14</f>
+        <v>62.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="171">
+        <v>6</v>
+      </c>
+      <c r="B7" s="190" t="s">
+        <v>295</v>
+      </c>
+      <c r="C7" s="191"/>
+      <c r="D7" s="192"/>
+      <c r="E7" s="187" t="s">
+        <v>300</v>
+      </c>
+      <c r="F7" s="188"/>
+      <c r="G7" s="170" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" s="172">
+        <f>H21</f>
+        <v>55.900000000000006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="171">
+        <v>7</v>
+      </c>
+      <c r="B8" s="190" t="s">
+        <v>295</v>
+      </c>
+      <c r="C8" s="191"/>
+      <c r="D8" s="192"/>
+      <c r="E8" s="187" t="s">
+        <v>303</v>
+      </c>
+      <c r="F8" s="188"/>
+      <c r="G8" s="170" t="s">
+        <v>70</v>
+      </c>
+      <c r="H8" s="173">
+        <f>H28</f>
+        <v>56.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="193"/>
+      <c r="B9" s="193"/>
+      <c r="C9" s="193"/>
+      <c r="D9" s="193"/>
+      <c r="E9" s="193"/>
+      <c r="F9" s="194"/>
+      <c r="G9" s="167" t="s">
+        <v>298</v>
+      </c>
+      <c r="H9" s="168">
+        <f>SUM(H2:H8)</f>
+        <v>8112.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="195" t="s">
+        <v>305</v>
+      </c>
+      <c r="B10" s="195"/>
+      <c r="C10" s="199"/>
+      <c r="D10" s="195" t="s">
+        <v>305</v>
+      </c>
+      <c r="E10" s="195"/>
+      <c r="F10" s="198"/>
+      <c r="G10" s="200"/>
+      <c r="H10" s="201"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="164" t="s">
+        <v>304</v>
+      </c>
+      <c r="B11" s="164" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="199"/>
+      <c r="D11" s="164" t="s">
+        <v>304</v>
+      </c>
+      <c r="E11" s="164" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="198"/>
+      <c r="G11" s="196" t="s">
+        <v>297</v>
+      </c>
+      <c r="H11" s="196"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="164" t="s">
+        <v>285</v>
+      </c>
+      <c r="B12" s="164">
+        <v>523.6</v>
+      </c>
+      <c r="C12" s="199"/>
+      <c r="D12" s="175" t="s">
+        <v>330</v>
+      </c>
+      <c r="E12" s="175">
+        <v>73.099999999999994</v>
+      </c>
+      <c r="F12" s="198"/>
+      <c r="G12" s="164" t="s">
+        <v>304</v>
+      </c>
+      <c r="H12" s="164" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="164" t="s">
+        <v>286</v>
+      </c>
+      <c r="B13" s="164">
+        <v>88.4</v>
+      </c>
+      <c r="C13" s="199"/>
+      <c r="D13" s="175" t="s">
+        <v>274</v>
+      </c>
+      <c r="E13" s="175">
+        <v>301.2</v>
+      </c>
+      <c r="F13" s="198"/>
+      <c r="G13" s="164" t="s">
+        <v>283</v>
+      </c>
+      <c r="H13" s="164">
+        <v>62.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="164" t="s">
+        <v>287</v>
+      </c>
+      <c r="B14" s="164">
+        <v>84.1</v>
+      </c>
+      <c r="C14" s="199"/>
+      <c r="D14" s="175" t="s">
+        <v>275</v>
+      </c>
+      <c r="E14" s="175">
+        <v>79.3</v>
+      </c>
+      <c r="F14" s="198"/>
+      <c r="G14" s="164" t="s">
+        <v>298</v>
+      </c>
+      <c r="H14" s="165">
+        <f>SUM(H13:H13)</f>
+        <v>62.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="164" t="s">
+        <v>288</v>
+      </c>
+      <c r="B15" s="164">
+        <v>32.1</v>
+      </c>
+      <c r="C15" s="199"/>
+      <c r="D15" s="175" t="s">
+        <v>276</v>
+      </c>
+      <c r="E15" s="175">
+        <v>137.1</v>
+      </c>
+      <c r="F15" s="198"/>
+      <c r="G15" s="197"/>
+      <c r="H15" s="197"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="164" t="s">
+        <v>289</v>
+      </c>
+      <c r="B16" s="164">
+        <v>34.6</v>
+      </c>
+      <c r="C16" s="199"/>
+      <c r="D16" s="175" t="s">
+        <v>277</v>
+      </c>
+      <c r="E16" s="175">
+        <v>356.9</v>
+      </c>
+      <c r="F16" s="198"/>
+      <c r="G16" s="202"/>
+      <c r="H16" s="202"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="164" t="s">
+        <v>290</v>
+      </c>
+      <c r="B17" s="164">
+        <v>112.9</v>
+      </c>
+      <c r="C17" s="199"/>
+      <c r="D17" s="175" t="s">
+        <v>278</v>
+      </c>
+      <c r="E17" s="175">
+        <v>115.1</v>
+      </c>
+      <c r="F17" s="198"/>
+      <c r="G17" s="196" t="s">
+        <v>296</v>
+      </c>
+      <c r="H17" s="196"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="164" t="s">
+        <v>291</v>
+      </c>
+      <c r="B18" s="164">
+        <v>181.3</v>
+      </c>
+      <c r="C18" s="199"/>
+      <c r="D18" s="175" t="s">
+        <v>279</v>
+      </c>
+      <c r="E18" s="175">
+        <v>117.9</v>
+      </c>
+      <c r="F18" s="198"/>
+      <c r="G18" s="164" t="s">
+        <v>304</v>
+      </c>
+      <c r="H18" s="164" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="164" t="s">
+        <v>292</v>
+      </c>
+      <c r="B19" s="164">
+        <v>278.60000000000002</v>
+      </c>
+      <c r="C19" s="199"/>
+      <c r="D19" s="175" t="s">
+        <v>280</v>
+      </c>
+      <c r="E19" s="175">
+        <v>244.2</v>
+      </c>
+      <c r="F19" s="198"/>
+      <c r="G19" s="164" t="s">
+        <v>336</v>
+      </c>
+      <c r="H19" s="164">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="164" t="s">
+        <v>293</v>
+      </c>
+      <c r="B20" s="164">
+        <v>367</v>
+      </c>
+      <c r="C20" s="199"/>
+      <c r="D20" s="175" t="s">
+        <v>281</v>
+      </c>
+      <c r="E20" s="175">
+        <v>259.60000000000002</v>
+      </c>
+      <c r="F20" s="198"/>
+      <c r="G20" s="164" t="s">
+        <v>333</v>
+      </c>
+      <c r="H20" s="164">
+        <v>31.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="164" t="s">
+        <v>294</v>
+      </c>
+      <c r="B21" s="164">
+        <v>89.2</v>
+      </c>
+      <c r="C21" s="199"/>
+      <c r="D21" s="175" t="s">
+        <v>347</v>
+      </c>
+      <c r="E21" s="175">
+        <v>70.7</v>
+      </c>
+      <c r="F21" s="198"/>
+      <c r="G21" s="164" t="s">
+        <v>298</v>
+      </c>
+      <c r="H21" s="165">
+        <f>SUM(H19:H20)</f>
+        <v>55.900000000000006</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="164" t="s">
+        <v>334</v>
+      </c>
+      <c r="B22" s="164">
+        <v>230.9</v>
+      </c>
+      <c r="C22" s="199"/>
+      <c r="D22" s="175" t="s">
+        <v>348</v>
+      </c>
+      <c r="E22" s="175">
+        <v>175.7</v>
+      </c>
+      <c r="F22" s="198"/>
+      <c r="G22" s="197"/>
+      <c r="H22" s="197"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="164" t="s">
+        <v>335</v>
+      </c>
+      <c r="B23" s="164">
+        <v>269.60000000000002</v>
+      </c>
+      <c r="C23" s="199"/>
+      <c r="D23" s="175" t="s">
+        <v>329</v>
+      </c>
+      <c r="E23" s="175">
+        <v>352.3</v>
+      </c>
+      <c r="F23" s="198"/>
+      <c r="G23" s="202"/>
+      <c r="H23" s="202"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="164" t="s">
+        <v>328</v>
+      </c>
+      <c r="B24" s="164">
+        <v>89.8</v>
+      </c>
+      <c r="C24" s="199"/>
+      <c r="D24" s="175" t="s">
+        <v>349</v>
+      </c>
+      <c r="E24" s="175">
+        <v>86.2</v>
+      </c>
+      <c r="F24" s="198"/>
+      <c r="G24" s="196" t="s">
+        <v>296</v>
+      </c>
+      <c r="H24" s="196"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="164" t="s">
+        <v>337</v>
+      </c>
+      <c r="B25" s="164">
+        <v>65</v>
+      </c>
+      <c r="C25" s="199"/>
+      <c r="D25" s="175" t="s">
+        <v>350</v>
+      </c>
+      <c r="E25" s="175">
+        <v>86.7</v>
+      </c>
+      <c r="F25" s="198"/>
+      <c r="G25" s="164" t="s">
+        <v>304</v>
+      </c>
+      <c r="H25" s="164" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="164" t="s">
+        <v>338</v>
+      </c>
+      <c r="B26" s="164">
+        <v>93.7</v>
+      </c>
+      <c r="C26" s="199"/>
+      <c r="D26" s="175" t="s">
+        <v>351</v>
+      </c>
+      <c r="E26" s="175">
+        <v>31.6</v>
+      </c>
+      <c r="F26" s="198"/>
+      <c r="G26" s="164" t="s">
+        <v>353</v>
+      </c>
+      <c r="H26" s="164">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="164" t="s">
+        <v>339</v>
+      </c>
+      <c r="B27" s="164">
+        <v>221.1</v>
+      </c>
+      <c r="C27" s="199"/>
+      <c r="D27" s="175" t="s">
+        <v>352</v>
+      </c>
+      <c r="E27" s="175">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="F27" s="198"/>
+      <c r="G27" s="164" t="s">
+        <v>346</v>
+      </c>
+      <c r="H27" s="164">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="164" t="s">
+        <v>340</v>
+      </c>
+      <c r="B28" s="164">
+        <v>280.3</v>
+      </c>
+      <c r="C28" s="199"/>
+      <c r="D28" s="175" t="s">
+        <v>354</v>
+      </c>
+      <c r="E28" s="175">
+        <v>109.4</v>
+      </c>
+      <c r="F28" s="198"/>
+      <c r="G28" s="164" t="s">
+        <v>298</v>
+      </c>
+      <c r="H28" s="165">
+        <f>SUM(H26:H27)</f>
+        <v>56.6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="164" t="s">
+        <v>327</v>
+      </c>
+      <c r="B29" s="164">
+        <v>116.4</v>
+      </c>
+      <c r="C29" s="199"/>
+      <c r="D29" s="175" t="s">
+        <v>282</v>
+      </c>
+      <c r="E29" s="175">
+        <v>172.5</v>
+      </c>
+      <c r="F29" s="198"/>
+      <c r="G29" s="197"/>
+      <c r="H29" s="197"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="164" t="s">
+        <v>341</v>
+      </c>
+      <c r="B30" s="164">
+        <v>31.2</v>
+      </c>
+      <c r="C30" s="199"/>
+      <c r="D30" s="175" t="s">
+        <v>355</v>
+      </c>
+      <c r="E30" s="175">
+        <v>98.9</v>
+      </c>
+      <c r="F30" s="198"/>
+      <c r="G30" s="179"/>
+      <c r="H30" s="179"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="164" t="s">
+        <v>342</v>
+      </c>
+      <c r="B31" s="164">
+        <v>165.5</v>
+      </c>
+      <c r="C31" s="199"/>
+      <c r="D31" s="175" t="s">
+        <v>323</v>
+      </c>
+      <c r="E31" s="175">
+        <v>223.7</v>
+      </c>
+      <c r="F31" s="198"/>
+      <c r="G31" s="179"/>
+      <c r="H31" s="179"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="164" t="s">
+        <v>343</v>
+      </c>
+      <c r="B32" s="164">
+        <v>239.3</v>
+      </c>
+      <c r="C32" s="199"/>
+      <c r="D32" s="175" t="s">
+        <v>356</v>
+      </c>
+      <c r="E32" s="175">
+        <v>227.1</v>
+      </c>
+      <c r="F32" s="198"/>
+      <c r="G32" s="179"/>
+      <c r="H32" s="179"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="164" t="s">
+        <v>344</v>
+      </c>
+      <c r="B33" s="164">
+        <v>200.9</v>
+      </c>
+      <c r="C33" s="199"/>
+      <c r="D33" s="175" t="s">
+        <v>357</v>
+      </c>
+      <c r="E33" s="175">
+        <v>165.6</v>
+      </c>
+      <c r="F33" s="198"/>
+      <c r="G33" s="179"/>
+      <c r="H33" s="179"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="164" t="s">
+        <v>345</v>
+      </c>
+      <c r="B34" s="214">
+        <v>247.4</v>
+      </c>
+      <c r="C34" s="199"/>
+      <c r="D34" s="175" t="s">
+        <v>358</v>
+      </c>
+      <c r="E34" s="175">
+        <v>136.19999999999999</v>
+      </c>
+      <c r="F34" s="198"/>
+      <c r="G34" s="179"/>
+      <c r="H34" s="179"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="213" t="s">
+        <v>298</v>
+      </c>
+      <c r="B35" s="165">
+        <f>SUM(B12:B34)</f>
+        <v>4042.9000000000005</v>
+      </c>
+      <c r="C35" s="198"/>
+      <c r="D35" s="175" t="s">
+        <v>359</v>
+      </c>
+      <c r="E35" s="175">
+        <v>52.9</v>
+      </c>
+      <c r="F35" s="198"/>
+      <c r="G35" s="179"/>
+      <c r="H35" s="179"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="193"/>
+      <c r="B36" s="193"/>
+      <c r="C36" s="198"/>
+      <c r="D36" s="175" t="s">
+        <v>360</v>
+      </c>
+      <c r="E36" s="175">
+        <v>43.8</v>
+      </c>
+      <c r="F36" s="198"/>
+      <c r="G36" s="179"/>
+      <c r="H36" s="179"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="211"/>
+      <c r="B37" s="211"/>
+      <c r="C37" s="198"/>
+      <c r="D37" s="175" t="s">
+        <v>331</v>
+      </c>
+      <c r="E37" s="175">
+        <v>49.2</v>
+      </c>
+      <c r="F37" s="198"/>
+      <c r="G37" s="179"/>
+      <c r="H37" s="179"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="211"/>
+      <c r="B38" s="211"/>
+      <c r="C38" s="198"/>
+      <c r="D38" s="175" t="s">
+        <v>332</v>
+      </c>
+      <c r="E38" s="175">
+        <v>46.2</v>
+      </c>
+      <c r="F38" s="198"/>
+      <c r="G38" s="179"/>
+      <c r="H38" s="179"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="211"/>
+      <c r="B39" s="211"/>
+      <c r="C39" s="198"/>
+      <c r="D39" s="175" t="s">
+        <v>298</v>
+      </c>
+      <c r="E39" s="165">
+        <f>SUM(E12:E38)</f>
+        <v>3847.3999999999996</v>
+      </c>
+      <c r="F39" s="198"/>
+      <c r="G39" s="179"/>
+      <c r="H39" s="179"/>
+    </row>
+  </sheetData>
+  <mergeCells count="29">
+    <mergeCell ref="A36:B39"/>
+    <mergeCell ref="G29:H39"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="F10:F39"/>
+    <mergeCell ref="C10:C39"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G15:H16"/>
+    <mergeCell ref="G22:H23"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.21875" style="159" customWidth="1"/>
+    <col min="2" max="2" width="54.77734375" style="142" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" style="142" customWidth="1"/>
+    <col min="4" max="4" width="18.21875" style="142" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="142"/>
+    <col min="6" max="6" width="17.77734375" style="142" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="142"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="141" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="150" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1" s="150" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1" s="150" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="150" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1" s="150" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="130">
+        <v>1</v>
+      </c>
+      <c r="B2" s="151" t="s">
+        <v>272</v>
+      </c>
+      <c r="C2" s="152" t="s">
+        <v>273</v>
+      </c>
+      <c r="D2" s="152" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="153">
+        <v>1</v>
+      </c>
+      <c r="F2" s="154">
+        <f>(2.1*2+1.15)*0.125*17</f>
+        <v>11.368749999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="130">
+        <v>2</v>
+      </c>
+      <c r="B3" s="151" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="152" t="s">
+        <v>263</v>
+      </c>
+      <c r="D3" s="152" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="153">
+        <v>1</v>
+      </c>
+      <c r="F3" s="154">
+        <f>F2</f>
+        <v>11.368749999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="146" t="s">
+        <v>267</v>
+      </c>
+      <c r="B4" s="155" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="152"/>
+      <c r="D4" s="156" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="157">
+        <v>1.5</v>
+      </c>
+      <c r="F4" s="158">
+        <f>$F$3*E4</f>
+        <v>17.053124999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="146" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="155" t="s">
+        <v>264</v>
+      </c>
+      <c r="C5" s="152"/>
+      <c r="D5" s="156" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="157">
+        <v>0.3</v>
+      </c>
+      <c r="F5" s="158">
+        <f t="shared" ref="F5:F9" si="0">$F$3*E5</f>
+        <v>3.4106249999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="146" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="155" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="152"/>
+      <c r="D6" s="156" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="157">
+        <v>0.15</v>
+      </c>
+      <c r="F6" s="158">
+        <f t="shared" si="0"/>
+        <v>1.7053124999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="130">
+        <v>3</v>
+      </c>
+      <c r="B7" s="151" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="152" t="s">
+        <v>265</v>
+      </c>
+      <c r="D7" s="152" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="153">
+        <v>1</v>
+      </c>
+      <c r="F7" s="158">
+        <f t="shared" si="0"/>
+        <v>11.368749999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="146" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="155" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="152"/>
+      <c r="D8" s="156" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="157">
+        <v>0.15</v>
+      </c>
+      <c r="F8" s="158">
+        <f t="shared" si="0"/>
+        <v>1.7053124999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="146" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="155" t="s">
+        <v>201</v>
+      </c>
+      <c r="C9" s="152"/>
+      <c r="D9" s="156" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="157">
+        <v>1.5</v>
+      </c>
+      <c r="F9" s="158">
+        <f t="shared" si="0"/>
+        <v>17.053124999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.21875" style="149" customWidth="1"/>
+    <col min="2" max="2" width="51.5546875" style="142" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="142" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="142" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="142"/>
+    <col min="6" max="6" width="17.77734375" style="142" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="142"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="141" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="141" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1" s="141" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1" s="141" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="141" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1" s="141" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="130">
+        <v>1</v>
+      </c>
+      <c r="B2" s="143" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="144" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2" s="144" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="145">
+        <v>1</v>
+      </c>
+      <c r="F2" s="162">
+        <f>'2-С-Ш1, баз'!F2</f>
+        <v>1350.87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="146" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="147" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="144"/>
+      <c r="D3" s="130" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="148">
+        <v>0.15</v>
+      </c>
+      <c r="F3" s="163">
+        <f>$F$2*E3</f>
+        <v>202.63049999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="146" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="147" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="144"/>
+      <c r="D4" s="130" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="148">
+        <v>1.5</v>
+      </c>
+      <c r="F4" s="163">
+        <f>$F$2*E4</f>
+        <v>2026.3049999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/school_1/walls/vor_spartac_1_walls.xlsx
+++ b/school_1/walls/vor_spartac_1_walls.xlsx
@@ -9,36 +9,37 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5568" windowWidth="5532" windowHeight="1512" firstSheet="4" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="5568" windowWidth="5532" windowHeight="1512"/>
   </bookViews>
   <sheets>
-    <sheet name="15ДмПот" sheetId="21" r:id="rId1"/>
-    <sheet name="14МонтСт" sheetId="20" r:id="rId2"/>
-    <sheet name="13МонтСт" sheetId="17" r:id="rId3"/>
-    <sheet name="12ДмСт" sheetId="16" r:id="rId4"/>
-    <sheet name="11ПВХплитка" sheetId="19" r:id="rId5"/>
-    <sheet name="10ПВХплиткаДм" sheetId="15" r:id="rId6"/>
-    <sheet name="9 Краска" sheetId="14" r:id="rId7"/>
-    <sheet name="4-С-Ш1" sheetId="13" r:id="rId8"/>
-    <sheet name="3-С-Ш1фин" sheetId="12" r:id="rId9"/>
-    <sheet name="2-С-Ш1, баз" sheetId="11" r:id="rId10"/>
-    <sheet name="1-С-Ш1, ГКЛ" sheetId="9" r:id="rId11"/>
-    <sheet name="Общий" sheetId="8" r:id="rId12"/>
-    <sheet name="Пример" sheetId="1" r:id="rId13"/>
-    <sheet name="Спортзал" sheetId="2" r:id="rId14"/>
-    <sheet name="библиотека" sheetId="3" r:id="rId15"/>
-    <sheet name="Библ откосы" sheetId="4" r:id="rId16"/>
-    <sheet name="ВОР2FB" sheetId="5" r:id="rId17"/>
-    <sheet name="1.030 ВОР" sheetId="7" r:id="rId18"/>
-    <sheet name="1.032 ВОР" sheetId="6" r:id="rId19"/>
-    <sheet name="1.032 ВОР (2)" sheetId="10" r:id="rId20"/>
+    <sheet name="16 Краска" sheetId="22" r:id="rId1"/>
+    <sheet name="15ДмПот" sheetId="21" r:id="rId2"/>
+    <sheet name="14МонтСт" sheetId="20" r:id="rId3"/>
+    <sheet name="13МонтСт" sheetId="17" r:id="rId4"/>
+    <sheet name="12ДмСт" sheetId="16" r:id="rId5"/>
+    <sheet name="11ПВХплитка" sheetId="19" r:id="rId6"/>
+    <sheet name="10ПВХплиткаДм" sheetId="15" r:id="rId7"/>
+    <sheet name="9 Краска" sheetId="14" r:id="rId8"/>
+    <sheet name="4-С-Ш1" sheetId="13" r:id="rId9"/>
+    <sheet name="3-С-Ш1фин" sheetId="12" r:id="rId10"/>
+    <sheet name="2-С-Ш1, баз" sheetId="11" r:id="rId11"/>
+    <sheet name="1-С-Ш1, ГКЛ" sheetId="9" r:id="rId12"/>
+    <sheet name="Общий" sheetId="8" r:id="rId13"/>
+    <sheet name="Пример" sheetId="1" r:id="rId14"/>
+    <sheet name="Спортзал" sheetId="2" r:id="rId15"/>
+    <sheet name="библиотека" sheetId="3" r:id="rId16"/>
+    <sheet name="Библ откосы" sheetId="4" r:id="rId17"/>
+    <sheet name="ВОР2FB" sheetId="5" r:id="rId18"/>
+    <sheet name="1.030 ВОР" sheetId="7" r:id="rId19"/>
+    <sheet name="1.032 ВОР" sheetId="6" r:id="rId20"/>
+    <sheet name="1.032 ВОР (2)" sheetId="10" r:id="rId21"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="384">
   <si>
     <t>Штукатурка цементным составом толщиной 16‐20 мм</t>
   </si>
@@ -1128,6 +1129,75 @@
   </si>
   <si>
     <t>3.060</t>
+  </si>
+  <si>
+    <t>Коридоры</t>
+  </si>
+  <si>
+    <t>Библиоттека</t>
+  </si>
+  <si>
+    <t>Лиф. Холлы</t>
+  </si>
+  <si>
+    <t>Актовые залы</t>
+  </si>
+  <si>
+    <t>1.073</t>
+  </si>
+  <si>
+    <t>1.067</t>
+  </si>
+  <si>
+    <t>1.062</t>
+  </si>
+  <si>
+    <t>1.055</t>
+  </si>
+  <si>
+    <t>1.050</t>
+  </si>
+  <si>
+    <t>1.023</t>
+  </si>
+  <si>
+    <t>1.002</t>
+  </si>
+  <si>
+    <t>1 этаж, h = 1.6 м</t>
+  </si>
+  <si>
+    <t>2 этаж, h = 1.6 м</t>
+  </si>
+  <si>
+    <t>3 этаж, h = 1.6 м</t>
+  </si>
+  <si>
+    <t>1.012</t>
+  </si>
+  <si>
+    <t>1.056</t>
+  </si>
+  <si>
+    <t>3.007</t>
+  </si>
+  <si>
+    <t>2.017</t>
+  </si>
+  <si>
+    <t>2.003</t>
+  </si>
+  <si>
+    <t>2.009</t>
+  </si>
+  <si>
+    <t>3.004</t>
+  </si>
+  <si>
+    <t>3.012</t>
+  </si>
+  <si>
+    <t>2.006</t>
   </si>
 </sst>
 </file>
@@ -1350,7 +1420,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -1858,13 +1928,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="227">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2377,6 +2458,15 @@
     <xf numFmtId="166" fontId="21" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2404,54 +2494,63 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2473,20 +2572,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="21" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="21" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2794,126 +2911,859 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="166" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="142"/>
     <col min="2" max="2" width="12" style="142" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" style="142" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="142" customWidth="1"/>
-    <col min="5" max="5" width="13" style="142" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="142" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5546875" style="142" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="142"/>
+    <col min="3" max="3" width="3.44140625" style="142" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" style="142"/>
+    <col min="5" max="5" width="12" style="142" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.6640625" style="142" customWidth="1"/>
+    <col min="7" max="8" width="8.88671875" style="142"/>
+    <col min="9" max="9" width="2.77734375" style="142" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" style="142"/>
+    <col min="11" max="11" width="12" style="142" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="142"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="141" t="s">
+    <row r="1" spans="1:11" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="169" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="180" t="s">
+      <c r="B1" s="219" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="181"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="150" t="s">
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219" t="s">
         <v>270</v>
       </c>
-      <c r="F1" s="150" t="s">
+      <c r="G1" s="219"/>
+      <c r="H1" s="219" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="150" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="130">
-        <v>1</v>
-      </c>
-      <c r="B2" s="183" t="s">
-        <v>324</v>
-      </c>
-      <c r="C2" s="184"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="152" t="s">
-        <v>325</v>
-      </c>
-      <c r="F2" s="152" t="s">
+      <c r="I1" s="219"/>
+      <c r="J1" s="219" t="s">
+        <v>127</v>
+      </c>
+      <c r="K1" s="219"/>
+    </row>
+    <row r="2" spans="1:11" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="171">
+        <v>1</v>
+      </c>
+      <c r="B2" s="222" t="s">
+        <v>295</v>
+      </c>
+      <c r="C2" s="222"/>
+      <c r="D2" s="222"/>
+      <c r="E2" s="222"/>
+      <c r="F2" s="219" t="s">
+        <v>372</v>
+      </c>
+      <c r="G2" s="219"/>
+      <c r="H2" s="219" t="s">
         <v>70</v>
       </c>
-      <c r="G2" s="154">
-        <f>B7</f>
-        <v>342.7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="186"/>
-      <c r="B3" s="186"/>
-      <c r="C3" s="186"/>
-      <c r="D3" s="186"/>
-      <c r="E3" s="186"/>
-      <c r="F3" s="186"/>
-      <c r="G3" s="186"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="174" t="s">
+      <c r="I2" s="219"/>
+      <c r="J2" s="220">
+        <f>B15+E12</f>
+        <v>707.00800000000004</v>
+      </c>
+      <c r="K2" s="220"/>
+    </row>
+    <row r="3" spans="1:11" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="171">
+        <v>2</v>
+      </c>
+      <c r="B3" s="222" t="s">
+        <v>295</v>
+      </c>
+      <c r="C3" s="222"/>
+      <c r="D3" s="222"/>
+      <c r="E3" s="222"/>
+      <c r="F3" s="219" t="s">
+        <v>373</v>
+      </c>
+      <c r="G3" s="219"/>
+      <c r="H3" s="219" t="s">
+        <v>70</v>
+      </c>
+      <c r="I3" s="219"/>
+      <c r="J3" s="221">
+        <f>B26+E22+H20+K21</f>
+        <v>1124.0320000000002</v>
+      </c>
+      <c r="K3" s="221"/>
+    </row>
+    <row r="4" spans="1:11" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="171">
+        <v>3</v>
+      </c>
+      <c r="B4" s="222" t="s">
+        <v>295</v>
+      </c>
+      <c r="C4" s="222"/>
+      <c r="D4" s="222"/>
+      <c r="E4" s="222"/>
+      <c r="F4" s="219" t="s">
+        <v>374</v>
+      </c>
+      <c r="G4" s="219"/>
+      <c r="H4" s="219" t="s">
+        <v>70</v>
+      </c>
+      <c r="I4" s="219"/>
+      <c r="J4" s="220">
+        <f>B37+E33+H31</f>
+        <v>881.952</v>
+      </c>
+      <c r="K4" s="220"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="216"/>
+      <c r="B5" s="224"/>
+      <c r="C5" s="224"/>
+      <c r="D5" s="224"/>
+      <c r="E5" s="224"/>
+      <c r="F5" s="224"/>
+      <c r="G5" s="217"/>
+      <c r="H5" s="204" t="s">
+        <v>298</v>
+      </c>
+      <c r="I5" s="204"/>
+      <c r="J5" s="223">
+        <f>SUM(J2:K4)</f>
+        <v>2712.9920000000002</v>
+      </c>
+      <c r="K5" s="223"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="225"/>
+      <c r="B6" s="195"/>
+      <c r="C6" s="195"/>
+      <c r="D6" s="195"/>
+      <c r="E6" s="195"/>
+      <c r="F6" s="195"/>
+      <c r="G6" s="195"/>
+      <c r="H6" s="195"/>
+      <c r="I6" s="195"/>
+      <c r="J6" s="195"/>
+      <c r="K6" s="226"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="204" t="s">
+        <v>361</v>
+      </c>
+      <c r="B7" s="204"/>
+      <c r="C7" s="182"/>
+      <c r="D7" s="204" t="s">
+        <v>363</v>
+      </c>
+      <c r="E7" s="204"/>
+      <c r="F7" s="182"/>
+      <c r="G7" s="182"/>
+      <c r="H7" s="182"/>
+      <c r="I7" s="182"/>
+      <c r="J7" s="182"/>
+      <c r="K7" s="182"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="178" t="s">
         <v>304</v>
       </c>
-      <c r="B4" s="174" t="s">
+      <c r="B8" s="178" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="178"/>
-      <c r="D4" s="179"/>
-      <c r="E4" s="179"/>
-      <c r="F4" s="179"/>
-      <c r="G4" s="179"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="174" t="s">
-        <v>281</v>
-      </c>
-      <c r="B5" s="174">
-        <v>190.5</v>
-      </c>
-      <c r="C5" s="178"/>
-      <c r="D5" s="179"/>
-      <c r="E5" s="179"/>
-      <c r="F5" s="179"/>
-      <c r="G5" s="179"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="174" t="s">
-        <v>323</v>
-      </c>
-      <c r="B6" s="174">
-        <v>152.19999999999999</v>
-      </c>
-      <c r="C6" s="178"/>
-      <c r="D6" s="179"/>
-      <c r="E6" s="179"/>
-      <c r="F6" s="179"/>
-      <c r="G6" s="179"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="174" t="s">
+      <c r="C8" s="182"/>
+      <c r="D8" s="178" t="s">
+        <v>304</v>
+      </c>
+      <c r="E8" s="178" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="182"/>
+      <c r="G8" s="182"/>
+      <c r="H8" s="182"/>
+      <c r="I8" s="182"/>
+      <c r="J8" s="182"/>
+      <c r="K8" s="182"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="178" t="s">
+        <v>365</v>
+      </c>
+      <c r="B9" s="178">
+        <f>68.9*1.6</f>
+        <v>110.24000000000001</v>
+      </c>
+      <c r="C9" s="182"/>
+      <c r="D9" s="178" t="s">
+        <v>366</v>
+      </c>
+      <c r="E9" s="178">
+        <f>10.6*1.6</f>
+        <v>16.96</v>
+      </c>
+      <c r="F9" s="182"/>
+      <c r="G9" s="182"/>
+      <c r="H9" s="182"/>
+      <c r="I9" s="182"/>
+      <c r="J9" s="182"/>
+      <c r="K9" s="182"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="178" t="s">
+        <v>367</v>
+      </c>
+      <c r="B10" s="178">
+        <f>65.6*1.6</f>
+        <v>104.96</v>
+      </c>
+      <c r="C10" s="182"/>
+      <c r="D10" s="178" t="s">
+        <v>375</v>
+      </c>
+      <c r="E10" s="178">
+        <f>10.7*1.6</f>
+        <v>17.12</v>
+      </c>
+      <c r="F10" s="182"/>
+      <c r="G10" s="182"/>
+      <c r="H10" s="182"/>
+      <c r="I10" s="182"/>
+      <c r="J10" s="182"/>
+      <c r="K10" s="182"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="178" t="s">
+        <v>368</v>
+      </c>
+      <c r="B11" s="178">
+        <f>68.2*1.6</f>
+        <v>109.12</v>
+      </c>
+      <c r="C11" s="182"/>
+      <c r="D11" s="178" t="s">
+        <v>376</v>
+      </c>
+      <c r="E11" s="178">
+        <f>10.7*1.6</f>
+        <v>17.12</v>
+      </c>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
+      <c r="I11" s="182"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="182"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="178" t="s">
+        <v>369</v>
+      </c>
+      <c r="B12" s="178">
+        <f>(24.58+53.3)*1.6</f>
+        <v>124.608</v>
+      </c>
+      <c r="C12" s="182"/>
+      <c r="D12" s="178" t="s">
         <v>298</v>
       </c>
-      <c r="B7" s="165">
-        <f>SUM(B5:B6)</f>
-        <v>342.7</v>
-      </c>
-      <c r="C7" s="178"/>
-      <c r="D7" s="179"/>
-      <c r="E7" s="179"/>
-      <c r="F7" s="179"/>
-      <c r="G7" s="179"/>
+      <c r="E12" s="165">
+        <f>SUM(E9:E11)</f>
+        <v>51.2</v>
+      </c>
+      <c r="F12" s="182"/>
+      <c r="G12" s="182"/>
+      <c r="H12" s="182"/>
+      <c r="I12" s="182"/>
+      <c r="J12" s="182"/>
+      <c r="K12" s="182"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="178" t="s">
+        <v>370</v>
+      </c>
+      <c r="B13" s="178">
+        <f>86.2*1.6</f>
+        <v>137.92000000000002</v>
+      </c>
+      <c r="C13" s="182"/>
+      <c r="D13" s="195"/>
+      <c r="E13" s="195"/>
+      <c r="F13" s="182"/>
+      <c r="G13" s="182"/>
+      <c r="H13" s="182"/>
+      <c r="I13" s="182"/>
+      <c r="J13" s="182"/>
+      <c r="K13" s="182"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="178" t="s">
+        <v>371</v>
+      </c>
+      <c r="B14" s="178">
+        <f>43.1*1.6</f>
+        <v>68.960000000000008</v>
+      </c>
+      <c r="C14" s="182"/>
+      <c r="D14" s="182"/>
+      <c r="E14" s="182"/>
+      <c r="F14" s="182"/>
+      <c r="G14" s="182"/>
+      <c r="H14" s="182"/>
+      <c r="I14" s="182"/>
+      <c r="J14" s="182"/>
+      <c r="K14" s="182"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="179" t="s">
+        <v>298</v>
+      </c>
+      <c r="B15" s="165">
+        <f>SUM(B9:B14)</f>
+        <v>655.80799999999999</v>
+      </c>
+      <c r="C15" s="182"/>
+      <c r="D15" s="182"/>
+      <c r="E15" s="182"/>
+      <c r="F15" s="182"/>
+      <c r="G15" s="182"/>
+      <c r="H15" s="182"/>
+      <c r="I15" s="182"/>
+      <c r="J15" s="182"/>
+      <c r="K15" s="182"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="198"/>
+      <c r="B16" s="198"/>
+      <c r="C16" s="182"/>
+      <c r="D16" s="200"/>
+      <c r="E16" s="200"/>
+      <c r="F16" s="182"/>
+      <c r="G16" s="200"/>
+      <c r="H16" s="200"/>
+      <c r="I16" s="182"/>
+      <c r="J16" s="200"/>
+      <c r="K16" s="200"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="218" t="s">
+        <v>361</v>
+      </c>
+      <c r="B17" s="199"/>
+      <c r="C17" s="182"/>
+      <c r="D17" s="204" t="s">
+        <v>363</v>
+      </c>
+      <c r="E17" s="204"/>
+      <c r="F17" s="182"/>
+      <c r="G17" s="218" t="s">
+        <v>362</v>
+      </c>
+      <c r="H17" s="199"/>
+      <c r="I17" s="182"/>
+      <c r="J17" s="216" t="s">
+        <v>364</v>
+      </c>
+      <c r="K17" s="217"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="178" t="s">
+        <v>304</v>
+      </c>
+      <c r="B18" s="178" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="182"/>
+      <c r="D18" s="178" t="s">
+        <v>304</v>
+      </c>
+      <c r="E18" s="178" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="182"/>
+      <c r="G18" s="178" t="s">
+        <v>304</v>
+      </c>
+      <c r="H18" s="178" t="s">
+        <v>29</v>
+      </c>
+      <c r="I18" s="182"/>
+      <c r="J18" s="178" t="s">
+        <v>304</v>
+      </c>
+      <c r="K18" s="178" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="178" t="s">
+        <v>340</v>
+      </c>
+      <c r="B19" s="178">
+        <f>66.1*1.6</f>
+        <v>105.75999999999999</v>
+      </c>
+      <c r="C19" s="182"/>
+      <c r="D19" s="178" t="s">
+        <v>380</v>
+      </c>
+      <c r="E19" s="178">
+        <f>10.51*1.6</f>
+        <v>16.815999999999999</v>
+      </c>
+      <c r="F19" s="182"/>
+      <c r="G19" s="178" t="s">
+        <v>285</v>
+      </c>
+      <c r="H19" s="178">
+        <f>136.3*1.6</f>
+        <v>218.08000000000004</v>
+      </c>
+      <c r="I19" s="182"/>
+      <c r="J19" s="178" t="s">
+        <v>341</v>
+      </c>
+      <c r="K19" s="178">
+        <f>72.2*1.6</f>
+        <v>115.52000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="178" t="s">
+        <v>335</v>
+      </c>
+      <c r="B20" s="178">
+        <f>53.8*1.6</f>
+        <v>86.08</v>
+      </c>
+      <c r="C20" s="182"/>
+      <c r="D20" s="178" t="s">
+        <v>336</v>
+      </c>
+      <c r="E20" s="178">
+        <f>8.6*1.6</f>
+        <v>13.76</v>
+      </c>
+      <c r="F20" s="182"/>
+      <c r="G20" s="178" t="s">
+        <v>298</v>
+      </c>
+      <c r="H20" s="165">
+        <f>SUM(H19:H19)</f>
+        <v>218.08000000000004</v>
+      </c>
+      <c r="I20" s="182"/>
+      <c r="J20" s="178" t="s">
+        <v>383</v>
+      </c>
+      <c r="K20" s="178">
+        <f>33.1*1.6</f>
+        <v>52.960000000000008</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="178" t="s">
+        <v>293</v>
+      </c>
+      <c r="B21" s="178">
+        <f>74.2*1.6</f>
+        <v>118.72000000000001</v>
+      </c>
+      <c r="C21" s="182"/>
+      <c r="D21" s="178" t="s">
+        <v>333</v>
+      </c>
+      <c r="E21" s="178">
+        <f>8.67*1.6</f>
+        <v>13.872</v>
+      </c>
+      <c r="F21" s="182"/>
+      <c r="G21" s="195"/>
+      <c r="H21" s="195"/>
+      <c r="I21" s="182"/>
+      <c r="J21" s="178" t="s">
+        <v>298</v>
+      </c>
+      <c r="K21" s="165">
+        <f>SUM(K19:K20)</f>
+        <v>168.48000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="178" t="s">
+        <v>291</v>
+      </c>
+      <c r="B22" s="178">
+        <f>43.6*1.6</f>
+        <v>69.760000000000005</v>
+      </c>
+      <c r="C22" s="182"/>
+      <c r="D22" s="178" t="s">
+        <v>298</v>
+      </c>
+      <c r="E22" s="165">
+        <f>SUM(E19:E21)</f>
+        <v>44.448</v>
+      </c>
+      <c r="F22" s="182"/>
+      <c r="G22" s="182"/>
+      <c r="H22" s="182"/>
+      <c r="I22" s="182"/>
+      <c r="J22" s="195"/>
+      <c r="K22" s="195"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="178" t="s">
+        <v>345</v>
+      </c>
+      <c r="B23" s="178">
+        <f>61.04*1.6</f>
+        <v>97.664000000000001</v>
+      </c>
+      <c r="C23" s="182"/>
+      <c r="D23" s="195"/>
+      <c r="E23" s="195"/>
+      <c r="F23" s="182"/>
+      <c r="G23" s="182"/>
+      <c r="H23" s="182"/>
+      <c r="I23" s="182"/>
+      <c r="J23" s="182"/>
+      <c r="K23" s="182"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="178" t="s">
+        <v>378</v>
+      </c>
+      <c r="B24" s="178">
+        <f>87.6*1.6</f>
+        <v>140.16</v>
+      </c>
+      <c r="C24" s="182"/>
+      <c r="D24" s="182"/>
+      <c r="E24" s="182"/>
+      <c r="F24" s="182"/>
+      <c r="G24" s="182"/>
+      <c r="H24" s="182"/>
+      <c r="I24" s="182"/>
+      <c r="J24" s="182"/>
+      <c r="K24" s="182"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="178" t="s">
+        <v>379</v>
+      </c>
+      <c r="B25" s="178">
+        <f>46.8*1.6</f>
+        <v>74.88</v>
+      </c>
+      <c r="C25" s="182"/>
+      <c r="D25" s="182"/>
+      <c r="E25" s="182"/>
+      <c r="F25" s="182"/>
+      <c r="G25" s="182"/>
+      <c r="H25" s="182"/>
+      <c r="I25" s="182"/>
+      <c r="J25" s="182"/>
+      <c r="K25" s="182"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="179" t="s">
+        <v>298</v>
+      </c>
+      <c r="B26" s="165">
+        <f>SUM(B19:B25)</f>
+        <v>693.024</v>
+      </c>
+      <c r="C26" s="182"/>
+      <c r="D26" s="182"/>
+      <c r="E26" s="182"/>
+      <c r="F26" s="182"/>
+      <c r="G26" s="182"/>
+      <c r="H26" s="182"/>
+      <c r="I26" s="182"/>
+      <c r="J26" s="182"/>
+      <c r="K26" s="182"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="198"/>
+      <c r="B27" s="198"/>
+      <c r="C27" s="182"/>
+      <c r="D27" s="200"/>
+      <c r="E27" s="200"/>
+      <c r="F27" s="182"/>
+      <c r="G27" s="200"/>
+      <c r="H27" s="200"/>
+      <c r="I27" s="182"/>
+      <c r="J27" s="182"/>
+      <c r="K27" s="182"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="218" t="s">
+        <v>361</v>
+      </c>
+      <c r="B28" s="199"/>
+      <c r="C28" s="182"/>
+      <c r="D28" s="204" t="s">
+        <v>363</v>
+      </c>
+      <c r="E28" s="204"/>
+      <c r="F28" s="182"/>
+      <c r="G28" s="218" t="s">
+        <v>362</v>
+      </c>
+      <c r="H28" s="199"/>
+      <c r="I28" s="182"/>
+      <c r="J28" s="182"/>
+      <c r="K28" s="182"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="178" t="s">
+        <v>304</v>
+      </c>
+      <c r="B29" s="178" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="182"/>
+      <c r="D29" s="178" t="s">
+        <v>304</v>
+      </c>
+      <c r="E29" s="178" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29" s="182"/>
+      <c r="G29" s="178" t="s">
+        <v>304</v>
+      </c>
+      <c r="H29" s="178" t="s">
+        <v>29</v>
+      </c>
+      <c r="I29" s="182"/>
+      <c r="J29" s="182"/>
+      <c r="K29" s="182"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="178" t="s">
+        <v>283</v>
+      </c>
+      <c r="B30" s="178">
+        <f>60.9*1.6</f>
+        <v>97.44</v>
+      </c>
+      <c r="C30" s="182"/>
+      <c r="D30" s="178" t="s">
+        <v>377</v>
+      </c>
+      <c r="E30" s="178">
+        <f>10.05*1.6</f>
+        <v>16.080000000000002</v>
+      </c>
+      <c r="F30" s="182"/>
+      <c r="G30" s="178" t="s">
+        <v>274</v>
+      </c>
+      <c r="H30" s="178">
+        <f>106.4*1.6</f>
+        <v>170.24</v>
+      </c>
+      <c r="I30" s="182"/>
+      <c r="J30" s="182"/>
+      <c r="K30" s="182"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="178" t="s">
+        <v>329</v>
+      </c>
+      <c r="B31" s="178">
+        <f>74.4*1.6</f>
+        <v>119.04000000000002</v>
+      </c>
+      <c r="C31" s="182"/>
+      <c r="D31" s="178" t="s">
+        <v>353</v>
+      </c>
+      <c r="E31" s="178">
+        <f>8.25*1.6</f>
+        <v>13.200000000000001</v>
+      </c>
+      <c r="F31" s="182"/>
+      <c r="G31" s="178" t="s">
+        <v>298</v>
+      </c>
+      <c r="H31" s="165">
+        <f>SUM(H30:H30)</f>
+        <v>170.24</v>
+      </c>
+      <c r="I31" s="182"/>
+      <c r="J31" s="182"/>
+      <c r="K31" s="182"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="178" t="s">
+        <v>280</v>
+      </c>
+      <c r="B32" s="178">
+        <f>53.2*1.6</f>
+        <v>85.12</v>
+      </c>
+      <c r="C32" s="182"/>
+      <c r="D32" s="178" t="s">
+        <v>346</v>
+      </c>
+      <c r="E32" s="178">
+        <f>8.17*1.6</f>
+        <v>13.072000000000001</v>
+      </c>
+      <c r="F32" s="182"/>
+      <c r="G32" s="195"/>
+      <c r="H32" s="195"/>
+      <c r="I32" s="182"/>
+      <c r="J32" s="182"/>
+      <c r="K32" s="182"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" s="178" t="s">
+        <v>284</v>
+      </c>
+      <c r="B33" s="178">
+        <f>46.56*1.6</f>
+        <v>74.496000000000009</v>
+      </c>
+      <c r="C33" s="182"/>
+      <c r="D33" s="178" t="s">
+        <v>298</v>
+      </c>
+      <c r="E33" s="165">
+        <f>SUM(E30:E32)</f>
+        <v>42.352000000000004</v>
+      </c>
+      <c r="F33" s="182"/>
+      <c r="G33" s="182"/>
+      <c r="H33" s="182"/>
+      <c r="I33" s="182"/>
+      <c r="J33" s="182"/>
+      <c r="K33" s="182"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" s="178" t="s">
+        <v>277</v>
+      </c>
+      <c r="B34" s="178">
+        <f>76.09*1.6</f>
+        <v>121.74400000000001</v>
+      </c>
+      <c r="C34" s="182"/>
+      <c r="D34" s="195"/>
+      <c r="E34" s="195"/>
+      <c r="F34" s="182"/>
+      <c r="G34" s="182"/>
+      <c r="H34" s="182"/>
+      <c r="I34" s="182"/>
+      <c r="J34" s="182"/>
+      <c r="K34" s="182"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="178" t="s">
+        <v>382</v>
+      </c>
+      <c r="B35" s="178">
+        <f>75.1*1.6</f>
+        <v>120.16</v>
+      </c>
+      <c r="C35" s="182"/>
+      <c r="D35" s="182"/>
+      <c r="E35" s="182"/>
+      <c r="F35" s="182"/>
+      <c r="G35" s="182"/>
+      <c r="H35" s="182"/>
+      <c r="I35" s="182"/>
+      <c r="J35" s="182"/>
+      <c r="K35" s="182"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" s="178" t="s">
+        <v>381</v>
+      </c>
+      <c r="B36" s="178">
+        <f>32.1*1.6</f>
+        <v>51.360000000000007</v>
+      </c>
+      <c r="C36" s="182"/>
+      <c r="D36" s="182"/>
+      <c r="E36" s="182"/>
+      <c r="F36" s="182"/>
+      <c r="G36" s="182"/>
+      <c r="H36" s="182"/>
+      <c r="I36" s="182"/>
+      <c r="J36" s="182"/>
+      <c r="K36" s="182"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" s="179" t="s">
+        <v>298</v>
+      </c>
+      <c r="B37" s="165">
+        <f>SUM(B30:B36)</f>
+        <v>669.36</v>
+      </c>
+      <c r="C37" s="182"/>
+      <c r="D37" s="182"/>
+      <c r="E37" s="182"/>
+      <c r="F37" s="182"/>
+      <c r="G37" s="182"/>
+      <c r="H37" s="182"/>
+      <c r="I37" s="182"/>
+      <c r="J37" s="182"/>
+      <c r="K37" s="182"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="C4:G7"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="A3:G3"/>
+  <mergeCells count="42">
+    <mergeCell ref="J7:K16"/>
+    <mergeCell ref="J22:K37"/>
+    <mergeCell ref="I7:I37"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="D34:E37"/>
+    <mergeCell ref="D23:E27"/>
+    <mergeCell ref="D13:E16"/>
+    <mergeCell ref="G7:H16"/>
+    <mergeCell ref="G21:H27"/>
+    <mergeCell ref="G32:H37"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="C7:C37"/>
+    <mergeCell ref="F7:F37"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -2921,6 +3771,104 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.21875" style="149" customWidth="1"/>
+    <col min="2" max="2" width="51.5546875" style="142" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="142" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="142" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="142"/>
+    <col min="6" max="6" width="17.77734375" style="142" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="142"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="141" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="141" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1" s="141" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1" s="141" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="141" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1" s="141" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="130">
+        <v>1</v>
+      </c>
+      <c r="B2" s="143" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="144" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2" s="144" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="145">
+        <v>1</v>
+      </c>
+      <c r="F2" s="162">
+        <f>'2-С-Ш1, баз'!F2</f>
+        <v>1350.87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="146" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="147" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="144"/>
+      <c r="D3" s="130" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="148">
+        <v>0.15</v>
+      </c>
+      <c r="F3" s="163">
+        <f>$F$2*E3</f>
+        <v>202.63049999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="146" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="147" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="144"/>
+      <c r="D4" s="130" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="148">
+        <v>1.5</v>
+      </c>
+      <c r="F4" s="163">
+        <f>$F$2*E4</f>
+        <v>2026.3049999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -3037,7 +3985,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -3201,7 +4149,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I86"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
@@ -3240,15 +4188,15 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="206" t="s">
+      <c r="A2" s="212" t="s">
         <v>251</v>
       </c>
-      <c r="B2" s="207"/>
-      <c r="C2" s="207"/>
-      <c r="D2" s="207"/>
-      <c r="E2" s="207"/>
-      <c r="F2" s="207"/>
-      <c r="G2" s="207"/>
+      <c r="B2" s="213"/>
+      <c r="C2" s="213"/>
+      <c r="D2" s="213"/>
+      <c r="E2" s="213"/>
+      <c r="F2" s="213"/>
+      <c r="G2" s="213"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="117" t="s">
@@ -3257,13 +4205,13 @@
       <c r="B3" s="117" t="s">
         <v>249</v>
       </c>
-      <c r="C3" s="203" t="s">
+      <c r="C3" s="209" t="s">
         <v>248</v>
       </c>
-      <c r="D3" s="204"/>
-      <c r="E3" s="204"/>
-      <c r="F3" s="204"/>
-      <c r="G3" s="204"/>
+      <c r="D3" s="210"/>
+      <c r="E3" s="210"/>
+      <c r="F3" s="210"/>
+      <c r="G3" s="210"/>
     </row>
     <row r="4" spans="1:7" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="117" t="s">
@@ -3371,13 +4319,13 @@
       <c r="B9" s="117" t="s">
         <v>129</v>
       </c>
-      <c r="C9" s="203" t="s">
+      <c r="C9" s="209" t="s">
         <v>130</v>
       </c>
-      <c r="D9" s="204"/>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="205"/>
+      <c r="D9" s="210"/>
+      <c r="E9" s="210"/>
+      <c r="F9" s="210"/>
+      <c r="G9" s="211"/>
     </row>
     <row r="10" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A10" s="117" t="s">
@@ -4854,13 +5802,13 @@
       <c r="B83" s="117" t="s">
         <v>229</v>
       </c>
-      <c r="C83" s="203" t="s">
+      <c r="C83" s="209" t="s">
         <v>230</v>
       </c>
-      <c r="D83" s="204"/>
-      <c r="E83" s="204"/>
-      <c r="F83" s="204"/>
-      <c r="G83" s="205"/>
+      <c r="D83" s="210"/>
+      <c r="E83" s="210"/>
+      <c r="F83" s="210"/>
+      <c r="G83" s="211"/>
     </row>
     <row r="84" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A84" s="117" t="s">
@@ -4910,7 +5858,7 @@
         <v>113.11499999999999</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" ht="66" x14ac:dyDescent="0.25">
       <c r="A86" s="117" t="s">
         <v>235</v>
       </c>
@@ -4943,7 +5891,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:D18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5096,7 +6044,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A4:F92"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
@@ -5956,7 +6904,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A15:E33"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6187,7 +7135,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6240,11 +7188,11 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="208"/>
-      <c r="B4" s="208"/>
-      <c r="C4" s="208"/>
-      <c r="D4" s="208"/>
-      <c r="E4" s="208"/>
+      <c r="A4" s="214"/>
+      <c r="B4" s="214"/>
+      <c r="C4" s="214"/>
+      <c r="D4" s="214"/>
+      <c r="E4" s="214"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="58"/>
@@ -6326,11 +7274,11 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="209"/>
-      <c r="B10" s="209"/>
-      <c r="C10" s="209"/>
-      <c r="D10" s="209"/>
-      <c r="E10" s="209"/>
+      <c r="A10" s="215"/>
+      <c r="B10" s="215"/>
+      <c r="C10" s="215"/>
+      <c r="D10" s="215"/>
+      <c r="E10" s="215"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="58"/>
@@ -6413,11 +7361,11 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="208"/>
-      <c r="B16" s="208"/>
-      <c r="C16" s="208"/>
-      <c r="D16" s="208"/>
-      <c r="E16" s="208"/>
+      <c r="A16" s="214"/>
+      <c r="B16" s="214"/>
+      <c r="C16" s="214"/>
+      <c r="D16" s="214"/>
+      <c r="E16" s="214"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="58"/>
@@ -6509,7 +7457,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6623,11 +7571,11 @@
       <c r="G6" s="67"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="208"/>
-      <c r="B7" s="208"/>
-      <c r="C7" s="208"/>
-      <c r="D7" s="208"/>
-      <c r="E7" s="208"/>
+      <c r="A7" s="214"/>
+      <c r="B7" s="214"/>
+      <c r="C7" s="214"/>
+      <c r="D7" s="214"/>
+      <c r="E7" s="214"/>
       <c r="G7" s="67"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -6715,11 +7663,11 @@
       <c r="G12" s="66"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="209"/>
-      <c r="B13" s="209"/>
-      <c r="C13" s="209"/>
-      <c r="D13" s="209"/>
-      <c r="E13" s="209"/>
+      <c r="A13" s="215"/>
+      <c r="B13" s="215"/>
+      <c r="C13" s="215"/>
+      <c r="D13" s="215"/>
+      <c r="E13" s="215"/>
       <c r="G13" s="66"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -6808,11 +7756,11 @@
       <c r="G18" s="66"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="208"/>
-      <c r="B19" s="208"/>
-      <c r="C19" s="208"/>
-      <c r="D19" s="208"/>
-      <c r="E19" s="208"/>
+      <c r="A19" s="214"/>
+      <c r="B19" s="214"/>
+      <c r="C19" s="214"/>
+      <c r="D19" s="214"/>
+      <c r="E19" s="214"/>
       <c r="G19" s="66"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -6909,7 +7857,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7492,7 +8440,135 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.21875" style="166" customWidth="1"/>
+    <col min="2" max="2" width="12" style="142" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" style="142" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="142" customWidth="1"/>
+    <col min="5" max="5" width="13" style="142" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="142" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5546875" style="142" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="142"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="141" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="183" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1" s="184"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="150" t="s">
+        <v>270</v>
+      </c>
+      <c r="F1" s="150" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" s="150" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="130">
+        <v>1</v>
+      </c>
+      <c r="B2" s="186" t="s">
+        <v>324</v>
+      </c>
+      <c r="C2" s="187"/>
+      <c r="D2" s="188"/>
+      <c r="E2" s="152" t="s">
+        <v>325</v>
+      </c>
+      <c r="F2" s="152" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="154">
+        <f>B7</f>
+        <v>342.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="189"/>
+      <c r="B3" s="189"/>
+      <c r="C3" s="189"/>
+      <c r="D3" s="189"/>
+      <c r="E3" s="189"/>
+      <c r="F3" s="189"/>
+      <c r="G3" s="189"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="174" t="s">
+        <v>304</v>
+      </c>
+      <c r="B4" s="174" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="181"/>
+      <c r="D4" s="182"/>
+      <c r="E4" s="182"/>
+      <c r="F4" s="182"/>
+      <c r="G4" s="182"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="174" t="s">
+        <v>281</v>
+      </c>
+      <c r="B5" s="174">
+        <v>190.5</v>
+      </c>
+      <c r="C5" s="181"/>
+      <c r="D5" s="182"/>
+      <c r="E5" s="182"/>
+      <c r="F5" s="182"/>
+      <c r="G5" s="182"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="174" t="s">
+        <v>323</v>
+      </c>
+      <c r="B6" s="174">
+        <v>152.19999999999999</v>
+      </c>
+      <c r="C6" s="181"/>
+      <c r="D6" s="182"/>
+      <c r="E6" s="182"/>
+      <c r="F6" s="182"/>
+      <c r="G6" s="182"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="174" t="s">
+        <v>298</v>
+      </c>
+      <c r="B7" s="165">
+        <f>SUM(B5:B6)</f>
+        <v>342.7</v>
+      </c>
+      <c r="C7" s="181"/>
+      <c r="D7" s="182"/>
+      <c r="E7" s="182"/>
+      <c r="F7" s="182"/>
+      <c r="G7" s="182"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C4:G7"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="A3:G3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7864,7 +8940,557 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.5546875" customWidth="1"/>
+    <col min="2" max="2" width="54.88671875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="69"/>
+      <c r="B1" s="70" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="72"/>
+    </row>
+    <row r="2" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="73" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="63">
+        <v>1</v>
+      </c>
+      <c r="E2" s="74">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="63">
+        <v>0.1</v>
+      </c>
+      <c r="E3" s="74">
+        <f>D3*E2</f>
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="76" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="78">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E4" s="79">
+        <f>D4*E2</f>
+        <v>23.87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="80" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="81" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="82" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="83">
+        <v>1</v>
+      </c>
+      <c r="E5" s="84">
+        <v>30.17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="73" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="85" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="63">
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="74">
+        <f>E5*D6</f>
+        <v>7.5425000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="73" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="87" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="88">
+        <v>1.8</v>
+      </c>
+      <c r="E7" s="89">
+        <f>E5*D7*20</f>
+        <v>1086.1200000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="73" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="86" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="87" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="88">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E8" s="89">
+        <f>E5*D8</f>
+        <v>33.187000000000005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="90" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="91" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="92" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="93">
+        <v>1</v>
+      </c>
+      <c r="E9" s="94">
+        <v>104.41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="73" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="85" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="63">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E10" s="74">
+        <f>E9*D10</f>
+        <v>114.851</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="73" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="85" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="63">
+        <v>1.8</v>
+      </c>
+      <c r="E11" s="74">
+        <f>E9*D11*20</f>
+        <v>3758.7599999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="73" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="104" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="74">
+        <f>E9*D12</f>
+        <v>15.661499999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="75" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="95" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="78">
+        <v>1</v>
+      </c>
+      <c r="E13" s="79">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="107"/>
+      <c r="B14" s="107"/>
+      <c r="C14" s="107"/>
+      <c r="D14" s="107"/>
+      <c r="E14" s="107"/>
+      <c r="F14" s="107"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="108"/>
+      <c r="B15" s="109" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="110"/>
+      <c r="D15" s="110"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="107"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="113" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" s="107"/>
+    </row>
+    <row r="17" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="73">
+        <v>1</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="63">
+        <v>1</v>
+      </c>
+      <c r="E17" s="74">
+        <f>E9+E5</f>
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F17" s="107"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B18" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="63">
+        <v>2</v>
+      </c>
+      <c r="E18" s="74">
+        <f>E17*D18</f>
+        <v>269.15999999999997</v>
+      </c>
+      <c r="F18" s="107"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E19" s="74">
+        <f>ROUNDDOWN(E17*D19,0)</f>
+        <v>40</v>
+      </c>
+      <c r="F19" s="107"/>
+    </row>
+    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="78">
+        <v>0.15</v>
+      </c>
+      <c r="E20" s="79">
+        <f>D20*E17</f>
+        <v>20.186999999999998</v>
+      </c>
+      <c r="F20" s="107"/>
+    </row>
+    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="114"/>
+      <c r="B21" s="114"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="114"/>
+      <c r="E21" s="114"/>
+      <c r="F21" s="107"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="108"/>
+      <c r="B22" s="109" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="110"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="111"/>
+      <c r="F22" s="107"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="113" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="107"/>
+    </row>
+    <row r="24" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="73">
+        <v>1</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="63">
+        <v>1</v>
+      </c>
+      <c r="E24" s="74">
+        <f>E17</f>
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F24" s="107"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B25" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E25" s="74">
+        <f>E24*D25</f>
+        <v>20.186999999999998</v>
+      </c>
+      <c r="F25" s="107"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="65" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="E26" s="74">
+        <f>ROUNDDOWN(E24*D26,0)</f>
+        <v>40</v>
+      </c>
+      <c r="F26" s="107"/>
+    </row>
+    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" s="105" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="78">
+        <v>1</v>
+      </c>
+      <c r="E27" s="79">
+        <f>D27*E24</f>
+        <v>134.57999999999998</v>
+      </c>
+      <c r="F27" s="107"/>
+    </row>
+    <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="107"/>
+      <c r="B28" s="107"/>
+      <c r="C28" s="107"/>
+      <c r="D28" s="107"/>
+      <c r="E28" s="107"/>
+      <c r="F28" s="107"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="108"/>
+      <c r="B29" s="109" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="110"/>
+      <c r="D29" s="110"/>
+      <c r="E29" s="111"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30" s="113" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="73">
+        <v>1</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="63">
+        <v>1</v>
+      </c>
+      <c r="E31" s="74">
+        <f>E24</f>
+        <v>134.57999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="73">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B32" s="85" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="63">
+        <v>0.15</v>
+      </c>
+      <c r="E32" s="74">
+        <f>D32*E31</f>
+        <v>20.186999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="95" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="78">
+        <v>0.3</v>
+      </c>
+      <c r="E33" s="79">
+        <f>D33*E31</f>
+        <v>40.373999999999995</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -7925,609 +9551,6 @@
         <v>70</v>
       </c>
       <c r="E3" s="177">
-        <v>74.599999999999994</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7.5546875" customWidth="1"/>
-    <col min="2" max="2" width="54.88671875" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" customWidth="1"/>
-    <col min="4" max="4" width="14.5546875" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="69"/>
-      <c r="B1" s="70" t="s">
-        <v>81</v>
-      </c>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="72"/>
-    </row>
-    <row r="2" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="73" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D2" s="63">
-        <v>1</v>
-      </c>
-      <c r="E2" s="74">
-        <v>21.7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="63">
-        <v>0.1</v>
-      </c>
-      <c r="E3" s="74">
-        <f>D3*E2</f>
-        <v>2.17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="75" t="s">
-        <v>72</v>
-      </c>
-      <c r="B4" s="76" t="s">
-        <v>85</v>
-      </c>
-      <c r="C4" s="77" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" s="78">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E4" s="79">
-        <f>D4*E2</f>
-        <v>23.87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="80" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" s="81" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" s="82" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="83">
-        <v>1</v>
-      </c>
-      <c r="E5" s="84">
-        <v>30.17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="73" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="85" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="63">
-        <v>0.25</v>
-      </c>
-      <c r="E6" s="74">
-        <f>E5*D6</f>
-        <v>7.5425000000000004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="73" t="s">
-        <v>88</v>
-      </c>
-      <c r="B7" s="86" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="87" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" s="88">
-        <v>1.8</v>
-      </c>
-      <c r="E7" s="89">
-        <f>E5*D7*20</f>
-        <v>1086.1200000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="73" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="86" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="87" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" s="88">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E8" s="89">
-        <f>E5*D8</f>
-        <v>33.187000000000005</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="90" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="91" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9" s="92" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="93">
-        <v>1</v>
-      </c>
-      <c r="E9" s="94">
-        <v>104.41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="73" t="s">
-        <v>90</v>
-      </c>
-      <c r="B10" s="85" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" s="63">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E10" s="74">
-        <f>E9*D10</f>
-        <v>114.851</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="73" t="s">
-        <v>91</v>
-      </c>
-      <c r="B11" s="85" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="63">
-        <v>1.8</v>
-      </c>
-      <c r="E11" s="74">
-        <f>E9*D11*20</f>
-        <v>3758.7599999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="73" t="s">
-        <v>92</v>
-      </c>
-      <c r="B12" s="104" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E12" s="74">
-        <f>E9*D12</f>
-        <v>15.661499999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="75" t="s">
-        <v>93</v>
-      </c>
-      <c r="B13" s="95" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="77" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="78">
-        <v>1</v>
-      </c>
-      <c r="E13" s="79">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="107"/>
-      <c r="B14" s="107"/>
-      <c r="C14" s="107"/>
-      <c r="D14" s="107"/>
-      <c r="E14" s="107"/>
-      <c r="F14" s="107"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="108"/>
-      <c r="B15" s="109" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="110"/>
-      <c r="D15" s="110"/>
-      <c r="E15" s="111"/>
-      <c r="F15" s="107"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="113" t="s">
-        <v>51</v>
-      </c>
-      <c r="F16" s="107"/>
-    </row>
-    <row r="17" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="73">
-        <v>1</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="63">
-        <v>1</v>
-      </c>
-      <c r="E17" s="74">
-        <f>E9+E5</f>
-        <v>134.57999999999998</v>
-      </c>
-      <c r="F17" s="107"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B18" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="63">
-        <v>2</v>
-      </c>
-      <c r="E18" s="74">
-        <f>E17*D18</f>
-        <v>269.15999999999997</v>
-      </c>
-      <c r="F18" s="107"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" s="63">
-        <v>0.3</v>
-      </c>
-      <c r="E19" s="74">
-        <f>ROUNDDOWN(E17*D19,0)</f>
-        <v>40</v>
-      </c>
-      <c r="F19" s="107"/>
-    </row>
-    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="75" t="s">
-        <v>72</v>
-      </c>
-      <c r="B20" s="106" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="78">
-        <v>0.15</v>
-      </c>
-      <c r="E20" s="79">
-        <f>D20*E17</f>
-        <v>20.186999999999998</v>
-      </c>
-      <c r="F20" s="107"/>
-    </row>
-    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="114"/>
-      <c r="B21" s="114"/>
-      <c r="C21" s="114"/>
-      <c r="D21" s="114"/>
-      <c r="E21" s="114"/>
-      <c r="F21" s="107"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="108"/>
-      <c r="B22" s="109" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" s="110"/>
-      <c r="D22" s="110"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="107"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23" s="113" t="s">
-        <v>51</v>
-      </c>
-      <c r="F23" s="107"/>
-    </row>
-    <row r="24" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="73">
-        <v>1</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="63">
-        <v>1</v>
-      </c>
-      <c r="E24" s="74">
-        <f>E17</f>
-        <v>134.57999999999998</v>
-      </c>
-      <c r="F24" s="107"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B25" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E25" s="74">
-        <f>E24*D25</f>
-        <v>20.186999999999998</v>
-      </c>
-      <c r="F25" s="107"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="65" t="s">
-        <v>106</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="63">
-        <v>0.3</v>
-      </c>
-      <c r="E26" s="74">
-        <f>ROUNDDOWN(E24*D26,0)</f>
-        <v>40</v>
-      </c>
-      <c r="F26" s="107"/>
-    </row>
-    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="75" t="s">
-        <v>72</v>
-      </c>
-      <c r="B27" s="105" t="s">
-        <v>107</v>
-      </c>
-      <c r="C27" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" s="78">
-        <v>1</v>
-      </c>
-      <c r="E27" s="79">
-        <f>D27*E24</f>
-        <v>134.57999999999998</v>
-      </c>
-      <c r="F27" s="107"/>
-    </row>
-    <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="107"/>
-      <c r="B28" s="107"/>
-      <c r="C28" s="107"/>
-      <c r="D28" s="107"/>
-      <c r="E28" s="107"/>
-      <c r="F28" s="107"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="108"/>
-      <c r="B29" s="109" t="s">
-        <v>60</v>
-      </c>
-      <c r="C29" s="110"/>
-      <c r="D29" s="110"/>
-      <c r="E29" s="111"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="D30" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="E30" s="113" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="73">
-        <v>1</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31" s="63">
-        <v>1</v>
-      </c>
-      <c r="E31" s="74">
-        <f>E24</f>
-        <v>134.57999999999998</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="73">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B32" s="85" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D32" s="63">
-        <v>0.15</v>
-      </c>
-      <c r="E32" s="74">
-        <f>D32*E31</f>
-        <v>20.186999999999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="75" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" s="95" t="s">
-        <v>97</v>
-      </c>
-      <c r="C33" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D33" s="78">
-        <v>0.3</v>
-      </c>
-      <c r="E33" s="79">
-        <f>D33*E31</f>
-        <v>40.373999999999995</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.21875" style="159" customWidth="1"/>
-    <col min="2" max="2" width="37" style="142" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" style="142" customWidth="1"/>
-    <col min="4" max="4" width="9" style="142" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15" style="142" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="142"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="141" t="s">
-        <v>122</v>
-      </c>
-      <c r="B1" s="150" t="s">
-        <v>271</v>
-      </c>
-      <c r="C1" s="150" t="s">
-        <v>270</v>
-      </c>
-      <c r="D1" s="150" t="s">
-        <v>49</v>
-      </c>
-      <c r="E1" s="150" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="130">
-        <v>1</v>
-      </c>
-      <c r="B2" s="152" t="s">
-        <v>307</v>
-      </c>
-      <c r="C2" s="152" t="s">
-        <v>308</v>
-      </c>
-      <c r="D2" s="152" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" s="176">
         <v>74.599999999999994</v>
       </c>
     </row>
@@ -8572,15 +9595,15 @@
         <v>1</v>
       </c>
       <c r="B2" s="152" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C2" s="152" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D2" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="177">
+      <c r="E2" s="176">
         <v>74.599999999999994</v>
       </c>
     </row>
@@ -8592,254 +9615,52 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.21875" style="159" customWidth="1"/>
-    <col min="2" max="2" width="12" style="142" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" style="142" customWidth="1"/>
-    <col min="4" max="4" width="14.5546875" style="142" customWidth="1"/>
-    <col min="5" max="5" width="16.21875" style="142" customWidth="1"/>
-    <col min="6" max="6" width="9" style="142" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" style="142" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="142"/>
+    <col min="2" max="2" width="37" style="142" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" style="142" customWidth="1"/>
+    <col min="4" max="4" width="9" style="142" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" style="142" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="142"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A1" s="141" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="180" t="s">
+      <c r="B1" s="150" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="181"/>
-      <c r="D1" s="182"/>
+      <c r="C1" s="150" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1" s="150" t="s">
+        <v>49</v>
+      </c>
       <c r="E1" s="150" t="s">
-        <v>270</v>
-      </c>
-      <c r="F1" s="150" t="s">
-        <v>49</v>
-      </c>
-      <c r="G1" s="150" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A2" s="130">
         <v>1</v>
       </c>
-      <c r="B2" s="183" t="s">
-        <v>322</v>
-      </c>
-      <c r="C2" s="184"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="152" t="s">
-        <v>320</v>
-      </c>
-      <c r="F2" s="152" t="s">
+      <c r="B2" s="152" t="s">
+        <v>311</v>
+      </c>
+      <c r="C2" s="152" t="s">
+        <v>306</v>
+      </c>
+      <c r="D2" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="G2" s="154">
-        <v>242.10000000000002</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="130">
-        <v>2</v>
-      </c>
-      <c r="B3" s="183" t="s">
-        <v>322</v>
-      </c>
-      <c r="C3" s="184"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="152" t="s">
-        <v>321</v>
-      </c>
-      <c r="F3" s="152" t="s">
-        <v>70</v>
-      </c>
-      <c r="G3" s="158">
-        <v>723.4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="130">
-        <v>3</v>
-      </c>
-      <c r="B4" s="183" t="s">
-        <v>314</v>
-      </c>
-      <c r="C4" s="184"/>
-      <c r="D4" s="185"/>
-      <c r="E4" s="152" t="s">
-        <v>319</v>
-      </c>
-      <c r="F4" s="152" t="s">
-        <v>313</v>
-      </c>
-      <c r="G4" s="154">
-        <v>302.39999999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="186"/>
-      <c r="B5" s="186"/>
-      <c r="C5" s="186"/>
-      <c r="D5" s="186"/>
-      <c r="E5" s="186"/>
-      <c r="F5" s="186"/>
-      <c r="G5" s="186"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="175" t="s">
-        <v>304</v>
-      </c>
-      <c r="B6" s="175" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="210"/>
-      <c r="D6" s="175" t="s">
-        <v>304</v>
-      </c>
-      <c r="E6" s="175" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="178"/>
-      <c r="G6" s="212"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="175" t="s">
-        <v>327</v>
-      </c>
-      <c r="B7" s="175">
-        <v>63.9</v>
-      </c>
-      <c r="C7" s="210"/>
-      <c r="D7" s="175" t="s">
-        <v>329</v>
-      </c>
-      <c r="E7" s="175">
-        <v>157.30000000000001</v>
-      </c>
-      <c r="F7" s="178"/>
-      <c r="G7" s="212"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="175" t="s">
-        <v>293</v>
-      </c>
-      <c r="B8" s="175">
-        <v>143.4</v>
-      </c>
-      <c r="C8" s="210"/>
-      <c r="D8" s="175" t="s">
-        <v>330</v>
-      </c>
-      <c r="E8" s="175">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="F8" s="178"/>
-      <c r="G8" s="212"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="175" t="s">
-        <v>328</v>
-      </c>
-      <c r="B9" s="175">
-        <v>34.799999999999997</v>
-      </c>
-      <c r="C9" s="210"/>
-      <c r="D9" s="175" t="s">
-        <v>331</v>
-      </c>
-      <c r="E9" s="175">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="F9" s="178"/>
-      <c r="G9" s="212"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="175" t="s">
-        <v>298</v>
-      </c>
-      <c r="B10" s="165">
-        <f>SUM(B7:B9)</f>
-        <v>242.10000000000002</v>
-      </c>
-      <c r="C10" s="210"/>
-      <c r="D10" s="175" t="s">
-        <v>332</v>
-      </c>
-      <c r="E10" s="175">
-        <v>20.6</v>
-      </c>
-      <c r="F10" s="178"/>
-      <c r="G10" s="212"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="193"/>
-      <c r="B11" s="193"/>
-      <c r="C11" s="210"/>
-      <c r="D11" s="175" t="s">
-        <v>284</v>
-      </c>
-      <c r="E11" s="175">
-        <v>104.1</v>
-      </c>
-      <c r="F11" s="178"/>
-      <c r="G11" s="212"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="198"/>
-      <c r="B12" s="198"/>
-      <c r="C12" s="210"/>
-      <c r="D12" s="175" t="s">
-        <v>277</v>
-      </c>
-      <c r="E12" s="175">
-        <v>108.2</v>
-      </c>
-      <c r="F12" s="178"/>
-      <c r="G12" s="212"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="198"/>
-      <c r="B13" s="198"/>
-      <c r="C13" s="210"/>
-      <c r="D13" s="175" t="s">
-        <v>274</v>
-      </c>
-      <c r="E13" s="175">
-        <v>305.39999999999998</v>
-      </c>
-      <c r="F13" s="178"/>
-      <c r="G13" s="212"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="198"/>
-      <c r="B14" s="198"/>
-      <c r="C14" s="210"/>
-      <c r="D14" s="175" t="s">
-        <v>298</v>
-      </c>
-      <c r="E14" s="165">
-        <f>SUM(E7:E13)</f>
-        <v>723.39999999999986</v>
-      </c>
-      <c r="F14" s="178"/>
-      <c r="G14" s="212"/>
+      <c r="E2" s="177">
+        <v>74.599999999999994</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="F6:G14"/>
-    <mergeCell ref="A11:B14"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="C6:C14"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -8864,11 +9685,11 @@
       <c r="A1" s="141" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="180" t="s">
+      <c r="B1" s="183" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="181"/>
-      <c r="D1" s="182"/>
+      <c r="C1" s="184"/>
+      <c r="D1" s="185"/>
       <c r="E1" s="150" t="s">
         <v>270</v>
       </c>
@@ -8879,15 +9700,270 @@
         <v>127</v>
       </c>
     </row>
+    <row r="2" spans="1:7" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="130">
+        <v>1</v>
+      </c>
+      <c r="B2" s="186" t="s">
+        <v>322</v>
+      </c>
+      <c r="C2" s="187"/>
+      <c r="D2" s="188"/>
+      <c r="E2" s="152" t="s">
+        <v>320</v>
+      </c>
+      <c r="F2" s="152" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="154">
+        <v>242.10000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="130">
+        <v>2</v>
+      </c>
+      <c r="B3" s="186" t="s">
+        <v>322</v>
+      </c>
+      <c r="C3" s="187"/>
+      <c r="D3" s="188"/>
+      <c r="E3" s="152" t="s">
+        <v>321</v>
+      </c>
+      <c r="F3" s="152" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="158">
+        <v>723.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="130">
+        <v>3</v>
+      </c>
+      <c r="B4" s="186" t="s">
+        <v>314</v>
+      </c>
+      <c r="C4" s="187"/>
+      <c r="D4" s="188"/>
+      <c r="E4" s="152" t="s">
+        <v>319</v>
+      </c>
+      <c r="F4" s="152" t="s">
+        <v>313</v>
+      </c>
+      <c r="G4" s="154">
+        <v>302.39999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="189"/>
+      <c r="B5" s="189"/>
+      <c r="C5" s="189"/>
+      <c r="D5" s="189"/>
+      <c r="E5" s="189"/>
+      <c r="F5" s="189"/>
+      <c r="G5" s="189"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="175" t="s">
+        <v>304</v>
+      </c>
+      <c r="B6" s="175" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="193"/>
+      <c r="D6" s="175" t="s">
+        <v>304</v>
+      </c>
+      <c r="E6" s="175" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="181"/>
+      <c r="G6" s="190"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="175" t="s">
+        <v>327</v>
+      </c>
+      <c r="B7" s="175">
+        <v>63.9</v>
+      </c>
+      <c r="C7" s="193"/>
+      <c r="D7" s="175" t="s">
+        <v>329</v>
+      </c>
+      <c r="E7" s="175">
+        <v>157.30000000000001</v>
+      </c>
+      <c r="F7" s="181"/>
+      <c r="G7" s="190"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="175" t="s">
+        <v>293</v>
+      </c>
+      <c r="B8" s="175">
+        <v>143.4</v>
+      </c>
+      <c r="C8" s="193"/>
+      <c r="D8" s="175" t="s">
+        <v>330</v>
+      </c>
+      <c r="E8" s="175">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="F8" s="181"/>
+      <c r="G8" s="190"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="175" t="s">
+        <v>328</v>
+      </c>
+      <c r="B9" s="175">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="C9" s="193"/>
+      <c r="D9" s="175" t="s">
+        <v>331</v>
+      </c>
+      <c r="E9" s="175">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F9" s="181"/>
+      <c r="G9" s="190"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="175" t="s">
+        <v>298</v>
+      </c>
+      <c r="B10" s="165">
+        <f>SUM(B7:B9)</f>
+        <v>242.10000000000002</v>
+      </c>
+      <c r="C10" s="193"/>
+      <c r="D10" s="175" t="s">
+        <v>332</v>
+      </c>
+      <c r="E10" s="175">
+        <v>20.6</v>
+      </c>
+      <c r="F10" s="181"/>
+      <c r="G10" s="190"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="191"/>
+      <c r="B11" s="191"/>
+      <c r="C11" s="193"/>
+      <c r="D11" s="175" t="s">
+        <v>284</v>
+      </c>
+      <c r="E11" s="175">
+        <v>104.1</v>
+      </c>
+      <c r="F11" s="181"/>
+      <c r="G11" s="190"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="192"/>
+      <c r="B12" s="192"/>
+      <c r="C12" s="193"/>
+      <c r="D12" s="175" t="s">
+        <v>277</v>
+      </c>
+      <c r="E12" s="175">
+        <v>108.2</v>
+      </c>
+      <c r="F12" s="181"/>
+      <c r="G12" s="190"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="192"/>
+      <c r="B13" s="192"/>
+      <c r="C13" s="193"/>
+      <c r="D13" s="175" t="s">
+        <v>274</v>
+      </c>
+      <c r="E13" s="175">
+        <v>305.39999999999998</v>
+      </c>
+      <c r="F13" s="181"/>
+      <c r="G13" s="190"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="192"/>
+      <c r="B14" s="192"/>
+      <c r="C14" s="193"/>
+      <c r="D14" s="175" t="s">
+        <v>298</v>
+      </c>
+      <c r="E14" s="165">
+        <f>SUM(E7:E13)</f>
+        <v>723.39999999999986</v>
+      </c>
+      <c r="F14" s="181"/>
+      <c r="G14" s="190"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="F6:G14"/>
+    <mergeCell ref="A11:B14"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="C6:C14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.21875" style="159" customWidth="1"/>
+    <col min="2" max="2" width="12" style="142" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" style="142" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" style="142" customWidth="1"/>
+    <col min="5" max="5" width="16.21875" style="142" customWidth="1"/>
+    <col min="6" max="6" width="9" style="142" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" style="142" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="142"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="141" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="183" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1" s="184"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="150" t="s">
+        <v>270</v>
+      </c>
+      <c r="F1" s="150" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" s="150" t="s">
+        <v>127</v>
+      </c>
+    </row>
     <row r="2" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="130">
         <v>1</v>
       </c>
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="186" t="s">
         <v>318</v>
       </c>
-      <c r="C2" s="184"/>
-      <c r="D2" s="185"/>
+      <c r="C2" s="187"/>
+      <c r="D2" s="188"/>
       <c r="E2" s="152" t="s">
         <v>309</v>
       </c>
@@ -8903,11 +9979,11 @@
       <c r="A3" s="130">
         <v>2</v>
       </c>
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="186" t="s">
         <v>318</v>
       </c>
-      <c r="C3" s="184"/>
-      <c r="D3" s="185"/>
+      <c r="C3" s="187"/>
+      <c r="D3" s="188"/>
       <c r="E3" s="152" t="s">
         <v>310</v>
       </c>
@@ -8923,11 +9999,11 @@
       <c r="A4" s="130">
         <v>3</v>
       </c>
-      <c r="B4" s="183" t="s">
+      <c r="B4" s="186" t="s">
         <v>312</v>
       </c>
-      <c r="C4" s="184"/>
-      <c r="D4" s="185"/>
+      <c r="C4" s="187"/>
+      <c r="D4" s="188"/>
       <c r="E4" s="152" t="s">
         <v>315</v>
       </c>
@@ -8939,13 +10015,13 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="186"/>
-      <c r="B5" s="186"/>
-      <c r="C5" s="186"/>
-      <c r="D5" s="186"/>
-      <c r="E5" s="186"/>
-      <c r="F5" s="186"/>
-      <c r="G5" s="186"/>
+      <c r="A5" s="189"/>
+      <c r="B5" s="189"/>
+      <c r="C5" s="189"/>
+      <c r="D5" s="189"/>
+      <c r="E5" s="189"/>
+      <c r="F5" s="189"/>
+      <c r="G5" s="189"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="175" t="s">
@@ -8954,15 +10030,15 @@
       <c r="B6" s="175" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="210"/>
+      <c r="C6" s="193"/>
       <c r="D6" s="175" t="s">
         <v>304</v>
       </c>
       <c r="E6" s="175" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="178"/>
-      <c r="G6" s="212"/>
+      <c r="F6" s="181"/>
+      <c r="G6" s="190"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="175" t="s">
@@ -8971,15 +10047,15 @@
       <c r="B7" s="175">
         <v>63.9</v>
       </c>
-      <c r="C7" s="210"/>
+      <c r="C7" s="193"/>
       <c r="D7" s="175" t="s">
         <v>329</v>
       </c>
       <c r="E7" s="175">
         <v>157.30000000000001</v>
       </c>
-      <c r="F7" s="178"/>
-      <c r="G7" s="212"/>
+      <c r="F7" s="181"/>
+      <c r="G7" s="190"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="175" t="s">
@@ -8988,15 +10064,15 @@
       <c r="B8" s="175">
         <v>143.4</v>
       </c>
-      <c r="C8" s="210"/>
+      <c r="C8" s="193"/>
       <c r="D8" s="175" t="s">
         <v>330</v>
       </c>
       <c r="E8" s="175">
         <v>18.600000000000001</v>
       </c>
-      <c r="F8" s="178"/>
-      <c r="G8" s="212"/>
+      <c r="F8" s="181"/>
+      <c r="G8" s="190"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="175" t="s">
@@ -9005,15 +10081,15 @@
       <c r="B9" s="175">
         <v>34.799999999999997</v>
       </c>
-      <c r="C9" s="210"/>
+      <c r="C9" s="193"/>
       <c r="D9" s="175" t="s">
         <v>331</v>
       </c>
       <c r="E9" s="175">
         <v>9.1999999999999993</v>
       </c>
-      <c r="F9" s="178"/>
-      <c r="G9" s="212"/>
+      <c r="F9" s="181"/>
+      <c r="G9" s="190"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="175" t="s">
@@ -9023,59 +10099,59 @@
         <f>SUM(B7:B9)</f>
         <v>242.10000000000002</v>
       </c>
-      <c r="C10" s="210"/>
+      <c r="C10" s="193"/>
       <c r="D10" s="175" t="s">
         <v>332</v>
       </c>
       <c r="E10" s="175">
         <v>20.6</v>
       </c>
-      <c r="F10" s="178"/>
-      <c r="G10" s="212"/>
+      <c r="F10" s="181"/>
+      <c r="G10" s="190"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="193"/>
-      <c r="B11" s="193"/>
-      <c r="C11" s="210"/>
+      <c r="A11" s="191"/>
+      <c r="B11" s="191"/>
+      <c r="C11" s="193"/>
       <c r="D11" s="175" t="s">
         <v>284</v>
       </c>
       <c r="E11" s="175">
         <v>104.1</v>
       </c>
-      <c r="F11" s="178"/>
-      <c r="G11" s="212"/>
+      <c r="F11" s="181"/>
+      <c r="G11" s="190"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="198"/>
-      <c r="B12" s="198"/>
-      <c r="C12" s="210"/>
+      <c r="A12" s="192"/>
+      <c r="B12" s="192"/>
+      <c r="C12" s="193"/>
       <c r="D12" s="175" t="s">
         <v>277</v>
       </c>
       <c r="E12" s="175">
         <v>108.2</v>
       </c>
-      <c r="F12" s="178"/>
-      <c r="G12" s="212"/>
+      <c r="F12" s="181"/>
+      <c r="G12" s="190"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="198"/>
-      <c r="B13" s="198"/>
-      <c r="C13" s="210"/>
+      <c r="A13" s="192"/>
+      <c r="B13" s="192"/>
+      <c r="C13" s="193"/>
       <c r="D13" s="175" t="s">
         <v>274</v>
       </c>
       <c r="E13" s="175">
         <v>305.39999999999998</v>
       </c>
-      <c r="F13" s="178"/>
-      <c r="G13" s="212"/>
+      <c r="F13" s="181"/>
+      <c r="G13" s="190"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="198"/>
-      <c r="B14" s="198"/>
-      <c r="C14" s="210"/>
+      <c r="A14" s="192"/>
+      <c r="B14" s="192"/>
+      <c r="C14" s="193"/>
       <c r="D14" s="175" t="s">
         <v>298</v>
       </c>
@@ -9083,8 +10159,8 @@
         <f>SUM(E7:E13)</f>
         <v>723.39999999999986</v>
       </c>
-      <c r="F14" s="178"/>
-      <c r="G14" s="212"/>
+      <c r="F14" s="181"/>
+      <c r="G14" s="190"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -9102,7 +10178,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -9121,15 +10197,15 @@
       <c r="A1" s="169" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="187" t="s">
+      <c r="B1" s="201" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="189"/>
-      <c r="D1" s="188"/>
-      <c r="E1" s="187" t="s">
+      <c r="C1" s="208"/>
+      <c r="D1" s="202"/>
+      <c r="E1" s="201" t="s">
         <v>270</v>
       </c>
-      <c r="F1" s="188"/>
+      <c r="F1" s="202"/>
       <c r="G1" s="170" t="s">
         <v>49</v>
       </c>
@@ -9141,15 +10217,15 @@
       <c r="A2" s="171">
         <v>1</v>
       </c>
-      <c r="B2" s="190" t="s">
+      <c r="B2" s="205" t="s">
         <v>295</v>
       </c>
-      <c r="C2" s="191"/>
-      <c r="D2" s="192"/>
-      <c r="E2" s="187" t="s">
+      <c r="C2" s="206"/>
+      <c r="D2" s="207"/>
+      <c r="E2" s="201" t="s">
         <v>299</v>
       </c>
-      <c r="F2" s="188"/>
+      <c r="F2" s="202"/>
       <c r="G2" s="170" t="s">
         <v>70</v>
       </c>
@@ -9162,15 +10238,15 @@
       <c r="A3" s="171">
         <v>2</v>
       </c>
-      <c r="B3" s="190" t="s">
+      <c r="B3" s="205" t="s">
         <v>295</v>
       </c>
-      <c r="C3" s="191"/>
-      <c r="D3" s="192"/>
-      <c r="E3" s="187" t="s">
+      <c r="C3" s="206"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="201" t="s">
         <v>301</v>
       </c>
-      <c r="F3" s="188"/>
+      <c r="F3" s="202"/>
       <c r="G3" s="170" t="s">
         <v>70</v>
       </c>
@@ -9183,15 +10259,15 @@
       <c r="A4" s="171">
         <v>3</v>
       </c>
-      <c r="B4" s="190" t="s">
+      <c r="B4" s="205" t="s">
         <v>295</v>
       </c>
-      <c r="C4" s="191"/>
-      <c r="D4" s="192"/>
-      <c r="E4" s="187" t="s">
+      <c r="C4" s="206"/>
+      <c r="D4" s="207"/>
+      <c r="E4" s="201" t="s">
         <v>316</v>
       </c>
-      <c r="F4" s="188"/>
+      <c r="F4" s="202"/>
       <c r="G4" s="170" t="s">
         <v>70</v>
       </c>
@@ -9203,15 +10279,15 @@
       <c r="A5" s="171">
         <v>4</v>
       </c>
-      <c r="B5" s="190" t="s">
+      <c r="B5" s="205" t="s">
         <v>295</v>
       </c>
-      <c r="C5" s="191"/>
-      <c r="D5" s="192"/>
-      <c r="E5" s="187" t="s">
+      <c r="C5" s="206"/>
+      <c r="D5" s="207"/>
+      <c r="E5" s="201" t="s">
         <v>317</v>
       </c>
-      <c r="F5" s="188"/>
+      <c r="F5" s="202"/>
       <c r="G5" s="170" t="s">
         <v>70</v>
       </c>
@@ -9223,15 +10299,15 @@
       <c r="A6" s="171">
         <v>5</v>
       </c>
-      <c r="B6" s="190" t="s">
+      <c r="B6" s="205" t="s">
         <v>295</v>
       </c>
-      <c r="C6" s="191"/>
-      <c r="D6" s="192"/>
-      <c r="E6" s="187" t="s">
+      <c r="C6" s="206"/>
+      <c r="D6" s="207"/>
+      <c r="E6" s="201" t="s">
         <v>302</v>
       </c>
-      <c r="F6" s="188"/>
+      <c r="F6" s="202"/>
       <c r="G6" s="170" t="s">
         <v>70</v>
       </c>
@@ -9244,15 +10320,15 @@
       <c r="A7" s="171">
         <v>6</v>
       </c>
-      <c r="B7" s="190" t="s">
+      <c r="B7" s="205" t="s">
         <v>295</v>
       </c>
-      <c r="C7" s="191"/>
-      <c r="D7" s="192"/>
-      <c r="E7" s="187" t="s">
+      <c r="C7" s="206"/>
+      <c r="D7" s="207"/>
+      <c r="E7" s="201" t="s">
         <v>300</v>
       </c>
-      <c r="F7" s="188"/>
+      <c r="F7" s="202"/>
       <c r="G7" s="170" t="s">
         <v>70</v>
       </c>
@@ -9265,15 +10341,15 @@
       <c r="A8" s="171">
         <v>7</v>
       </c>
-      <c r="B8" s="190" t="s">
+      <c r="B8" s="205" t="s">
         <v>295</v>
       </c>
-      <c r="C8" s="191"/>
-      <c r="D8" s="192"/>
-      <c r="E8" s="187" t="s">
+      <c r="C8" s="206"/>
+      <c r="D8" s="207"/>
+      <c r="E8" s="201" t="s">
         <v>303</v>
       </c>
-      <c r="F8" s="188"/>
+      <c r="F8" s="202"/>
       <c r="G8" s="170" t="s">
         <v>70</v>
       </c>
@@ -9283,12 +10359,12 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="193"/>
-      <c r="B9" s="193"/>
-      <c r="C9" s="193"/>
-      <c r="D9" s="193"/>
-      <c r="E9" s="193"/>
-      <c r="F9" s="194"/>
+      <c r="A9" s="191"/>
+      <c r="B9" s="191"/>
+      <c r="C9" s="191"/>
+      <c r="D9" s="191"/>
+      <c r="E9" s="191"/>
+      <c r="F9" s="203"/>
       <c r="G9" s="167" t="s">
         <v>298</v>
       </c>
@@ -9298,18 +10374,18 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="195" t="s">
+      <c r="A10" s="204" t="s">
         <v>305</v>
       </c>
-      <c r="B10" s="195"/>
-      <c r="C10" s="199"/>
-      <c r="D10" s="195" t="s">
+      <c r="B10" s="204"/>
+      <c r="C10" s="197"/>
+      <c r="D10" s="204" t="s">
         <v>305</v>
       </c>
-      <c r="E10" s="195"/>
-      <c r="F10" s="198"/>
-      <c r="G10" s="200"/>
-      <c r="H10" s="201"/>
+      <c r="E10" s="204"/>
+      <c r="F10" s="192"/>
+      <c r="G10" s="198"/>
+      <c r="H10" s="199"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="164" t="s">
@@ -9318,14 +10394,14 @@
       <c r="B11" s="164" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="199"/>
+      <c r="C11" s="197"/>
       <c r="D11" s="164" t="s">
         <v>304</v>
       </c>
       <c r="E11" s="164" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="198"/>
+      <c r="F11" s="192"/>
       <c r="G11" s="196" t="s">
         <v>297</v>
       </c>
@@ -9338,14 +10414,14 @@
       <c r="B12" s="164">
         <v>523.6</v>
       </c>
-      <c r="C12" s="199"/>
+      <c r="C12" s="197"/>
       <c r="D12" s="175" t="s">
         <v>330</v>
       </c>
       <c r="E12" s="175">
         <v>73.099999999999994</v>
       </c>
-      <c r="F12" s="198"/>
+      <c r="F12" s="192"/>
       <c r="G12" s="164" t="s">
         <v>304</v>
       </c>
@@ -9360,14 +10436,14 @@
       <c r="B13" s="164">
         <v>88.4</v>
       </c>
-      <c r="C13" s="199"/>
+      <c r="C13" s="197"/>
       <c r="D13" s="175" t="s">
         <v>274</v>
       </c>
       <c r="E13" s="175">
         <v>301.2</v>
       </c>
-      <c r="F13" s="198"/>
+      <c r="F13" s="192"/>
       <c r="G13" s="164" t="s">
         <v>283</v>
       </c>
@@ -9382,14 +10458,14 @@
       <c r="B14" s="164">
         <v>84.1</v>
       </c>
-      <c r="C14" s="199"/>
+      <c r="C14" s="197"/>
       <c r="D14" s="175" t="s">
         <v>275</v>
       </c>
       <c r="E14" s="175">
         <v>79.3</v>
       </c>
-      <c r="F14" s="198"/>
+      <c r="F14" s="192"/>
       <c r="G14" s="164" t="s">
         <v>298</v>
       </c>
@@ -9405,16 +10481,16 @@
       <c r="B15" s="164">
         <v>32.1</v>
       </c>
-      <c r="C15" s="199"/>
+      <c r="C15" s="197"/>
       <c r="D15" s="175" t="s">
         <v>276</v>
       </c>
       <c r="E15" s="175">
         <v>137.1</v>
       </c>
-      <c r="F15" s="198"/>
-      <c r="G15" s="197"/>
-      <c r="H15" s="197"/>
+      <c r="F15" s="192"/>
+      <c r="G15" s="195"/>
+      <c r="H15" s="195"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="164" t="s">
@@ -9423,16 +10499,16 @@
       <c r="B16" s="164">
         <v>34.6</v>
       </c>
-      <c r="C16" s="199"/>
+      <c r="C16" s="197"/>
       <c r="D16" s="175" t="s">
         <v>277</v>
       </c>
       <c r="E16" s="175">
         <v>356.9</v>
       </c>
-      <c r="F16" s="198"/>
-      <c r="G16" s="202"/>
-      <c r="H16" s="202"/>
+      <c r="F16" s="192"/>
+      <c r="G16" s="200"/>
+      <c r="H16" s="200"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="164" t="s">
@@ -9441,14 +10517,14 @@
       <c r="B17" s="164">
         <v>112.9</v>
       </c>
-      <c r="C17" s="199"/>
+      <c r="C17" s="197"/>
       <c r="D17" s="175" t="s">
         <v>278</v>
       </c>
       <c r="E17" s="175">
         <v>115.1</v>
       </c>
-      <c r="F17" s="198"/>
+      <c r="F17" s="192"/>
       <c r="G17" s="196" t="s">
         <v>296</v>
       </c>
@@ -9461,14 +10537,14 @@
       <c r="B18" s="164">
         <v>181.3</v>
       </c>
-      <c r="C18" s="199"/>
+      <c r="C18" s="197"/>
       <c r="D18" s="175" t="s">
         <v>279</v>
       </c>
       <c r="E18" s="175">
         <v>117.9</v>
       </c>
-      <c r="F18" s="198"/>
+      <c r="F18" s="192"/>
       <c r="G18" s="164" t="s">
         <v>304</v>
       </c>
@@ -9483,14 +10559,14 @@
       <c r="B19" s="164">
         <v>278.60000000000002</v>
       </c>
-      <c r="C19" s="199"/>
+      <c r="C19" s="197"/>
       <c r="D19" s="175" t="s">
         <v>280</v>
       </c>
       <c r="E19" s="175">
         <v>244.2</v>
       </c>
-      <c r="F19" s="198"/>
+      <c r="F19" s="192"/>
       <c r="G19" s="164" t="s">
         <v>336</v>
       </c>
@@ -9505,14 +10581,14 @@
       <c r="B20" s="164">
         <v>367</v>
       </c>
-      <c r="C20" s="199"/>
+      <c r="C20" s="197"/>
       <c r="D20" s="175" t="s">
         <v>281</v>
       </c>
       <c r="E20" s="175">
         <v>259.60000000000002</v>
       </c>
-      <c r="F20" s="198"/>
+      <c r="F20" s="192"/>
       <c r="G20" s="164" t="s">
         <v>333</v>
       </c>
@@ -9527,14 +10603,14 @@
       <c r="B21" s="164">
         <v>89.2</v>
       </c>
-      <c r="C21" s="199"/>
+      <c r="C21" s="197"/>
       <c r="D21" s="175" t="s">
         <v>347</v>
       </c>
       <c r="E21" s="175">
         <v>70.7</v>
       </c>
-      <c r="F21" s="198"/>
+      <c r="F21" s="192"/>
       <c r="G21" s="164" t="s">
         <v>298</v>
       </c>
@@ -9550,16 +10626,16 @@
       <c r="B22" s="164">
         <v>230.9</v>
       </c>
-      <c r="C22" s="199"/>
+      <c r="C22" s="197"/>
       <c r="D22" s="175" t="s">
         <v>348</v>
       </c>
       <c r="E22" s="175">
         <v>175.7</v>
       </c>
-      <c r="F22" s="198"/>
-      <c r="G22" s="197"/>
-      <c r="H22" s="197"/>
+      <c r="F22" s="192"/>
+      <c r="G22" s="195"/>
+      <c r="H22" s="195"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="164" t="s">
@@ -9568,16 +10644,16 @@
       <c r="B23" s="164">
         <v>269.60000000000002</v>
       </c>
-      <c r="C23" s="199"/>
+      <c r="C23" s="197"/>
       <c r="D23" s="175" t="s">
         <v>329</v>
       </c>
       <c r="E23" s="175">
         <v>352.3</v>
       </c>
-      <c r="F23" s="198"/>
-      <c r="G23" s="202"/>
-      <c r="H23" s="202"/>
+      <c r="F23" s="192"/>
+      <c r="G23" s="200"/>
+      <c r="H23" s="200"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="164" t="s">
@@ -9586,14 +10662,14 @@
       <c r="B24" s="164">
         <v>89.8</v>
       </c>
-      <c r="C24" s="199"/>
+      <c r="C24" s="197"/>
       <c r="D24" s="175" t="s">
         <v>349</v>
       </c>
       <c r="E24" s="175">
         <v>86.2</v>
       </c>
-      <c r="F24" s="198"/>
+      <c r="F24" s="192"/>
       <c r="G24" s="196" t="s">
         <v>296</v>
       </c>
@@ -9606,14 +10682,14 @@
       <c r="B25" s="164">
         <v>65</v>
       </c>
-      <c r="C25" s="199"/>
+      <c r="C25" s="197"/>
       <c r="D25" s="175" t="s">
         <v>350</v>
       </c>
       <c r="E25" s="175">
         <v>86.7</v>
       </c>
-      <c r="F25" s="198"/>
+      <c r="F25" s="192"/>
       <c r="G25" s="164" t="s">
         <v>304</v>
       </c>
@@ -9628,14 +10704,14 @@
       <c r="B26" s="164">
         <v>93.7</v>
       </c>
-      <c r="C26" s="199"/>
+      <c r="C26" s="197"/>
       <c r="D26" s="175" t="s">
         <v>351</v>
       </c>
       <c r="E26" s="175">
         <v>31.6</v>
       </c>
-      <c r="F26" s="198"/>
+      <c r="F26" s="192"/>
       <c r="G26" s="164" t="s">
         <v>353</v>
       </c>
@@ -9650,14 +10726,14 @@
       <c r="B27" s="164">
         <v>221.1</v>
       </c>
-      <c r="C27" s="199"/>
+      <c r="C27" s="197"/>
       <c r="D27" s="175" t="s">
         <v>352</v>
       </c>
       <c r="E27" s="175">
         <v>34.299999999999997</v>
       </c>
-      <c r="F27" s="198"/>
+      <c r="F27" s="192"/>
       <c r="G27" s="164" t="s">
         <v>346</v>
       </c>
@@ -9672,14 +10748,14 @@
       <c r="B28" s="164">
         <v>280.3</v>
       </c>
-      <c r="C28" s="199"/>
+      <c r="C28" s="197"/>
       <c r="D28" s="175" t="s">
         <v>354</v>
       </c>
       <c r="E28" s="175">
         <v>109.4</v>
       </c>
-      <c r="F28" s="198"/>
+      <c r="F28" s="192"/>
       <c r="G28" s="164" t="s">
         <v>298</v>
       </c>
@@ -9695,16 +10771,16 @@
       <c r="B29" s="164">
         <v>116.4</v>
       </c>
-      <c r="C29" s="199"/>
+      <c r="C29" s="197"/>
       <c r="D29" s="175" t="s">
         <v>282</v>
       </c>
       <c r="E29" s="175">
         <v>172.5</v>
       </c>
-      <c r="F29" s="198"/>
-      <c r="G29" s="197"/>
-      <c r="H29" s="197"/>
+      <c r="F29" s="192"/>
+      <c r="G29" s="195"/>
+      <c r="H29" s="195"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="164" t="s">
@@ -9713,16 +10789,16 @@
       <c r="B30" s="164">
         <v>31.2</v>
       </c>
-      <c r="C30" s="199"/>
+      <c r="C30" s="197"/>
       <c r="D30" s="175" t="s">
         <v>355</v>
       </c>
       <c r="E30" s="175">
         <v>98.9</v>
       </c>
-      <c r="F30" s="198"/>
-      <c r="G30" s="179"/>
-      <c r="H30" s="179"/>
+      <c r="F30" s="192"/>
+      <c r="G30" s="182"/>
+      <c r="H30" s="182"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="164" t="s">
@@ -9731,16 +10807,16 @@
       <c r="B31" s="164">
         <v>165.5</v>
       </c>
-      <c r="C31" s="199"/>
+      <c r="C31" s="197"/>
       <c r="D31" s="175" t="s">
         <v>323</v>
       </c>
       <c r="E31" s="175">
         <v>223.7</v>
       </c>
-      <c r="F31" s="198"/>
-      <c r="G31" s="179"/>
-      <c r="H31" s="179"/>
+      <c r="F31" s="192"/>
+      <c r="G31" s="182"/>
+      <c r="H31" s="182"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="164" t="s">
@@ -9749,16 +10825,16 @@
       <c r="B32" s="164">
         <v>239.3</v>
       </c>
-      <c r="C32" s="199"/>
+      <c r="C32" s="197"/>
       <c r="D32" s="175" t="s">
         <v>356</v>
       </c>
       <c r="E32" s="175">
         <v>227.1</v>
       </c>
-      <c r="F32" s="198"/>
-      <c r="G32" s="179"/>
-      <c r="H32" s="179"/>
+      <c r="F32" s="192"/>
+      <c r="G32" s="182"/>
+      <c r="H32" s="182"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="164" t="s">
@@ -9767,100 +10843,100 @@
       <c r="B33" s="164">
         <v>200.9</v>
       </c>
-      <c r="C33" s="199"/>
+      <c r="C33" s="197"/>
       <c r="D33" s="175" t="s">
         <v>357</v>
       </c>
       <c r="E33" s="175">
         <v>165.6</v>
       </c>
-      <c r="F33" s="198"/>
-      <c r="G33" s="179"/>
-      <c r="H33" s="179"/>
+      <c r="F33" s="192"/>
+      <c r="G33" s="182"/>
+      <c r="H33" s="182"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="164" t="s">
         <v>345</v>
       </c>
-      <c r="B34" s="214">
+      <c r="B34" s="180">
         <v>247.4</v>
       </c>
-      <c r="C34" s="199"/>
+      <c r="C34" s="197"/>
       <c r="D34" s="175" t="s">
         <v>358</v>
       </c>
       <c r="E34" s="175">
         <v>136.19999999999999</v>
       </c>
-      <c r="F34" s="198"/>
-      <c r="G34" s="179"/>
-      <c r="H34" s="179"/>
+      <c r="F34" s="192"/>
+      <c r="G34" s="182"/>
+      <c r="H34" s="182"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="213" t="s">
+      <c r="A35" s="179" t="s">
         <v>298</v>
       </c>
       <c r="B35" s="165">
         <f>SUM(B12:B34)</f>
         <v>4042.9000000000005</v>
       </c>
-      <c r="C35" s="198"/>
+      <c r="C35" s="192"/>
       <c r="D35" s="175" t="s">
         <v>359</v>
       </c>
       <c r="E35" s="175">
         <v>52.9</v>
       </c>
-      <c r="F35" s="198"/>
-      <c r="G35" s="179"/>
-      <c r="H35" s="179"/>
+      <c r="F35" s="192"/>
+      <c r="G35" s="182"/>
+      <c r="H35" s="182"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="193"/>
-      <c r="B36" s="193"/>
-      <c r="C36" s="198"/>
+      <c r="A36" s="191"/>
+      <c r="B36" s="191"/>
+      <c r="C36" s="192"/>
       <c r="D36" s="175" t="s">
         <v>360</v>
       </c>
       <c r="E36" s="175">
         <v>43.8</v>
       </c>
-      <c r="F36" s="198"/>
-      <c r="G36" s="179"/>
-      <c r="H36" s="179"/>
+      <c r="F36" s="192"/>
+      <c r="G36" s="182"/>
+      <c r="H36" s="182"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="211"/>
-      <c r="B37" s="211"/>
-      <c r="C37" s="198"/>
+      <c r="A37" s="194"/>
+      <c r="B37" s="194"/>
+      <c r="C37" s="192"/>
       <c r="D37" s="175" t="s">
         <v>331</v>
       </c>
       <c r="E37" s="175">
         <v>49.2</v>
       </c>
-      <c r="F37" s="198"/>
-      <c r="G37" s="179"/>
-      <c r="H37" s="179"/>
+      <c r="F37" s="192"/>
+      <c r="G37" s="182"/>
+      <c r="H37" s="182"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="211"/>
-      <c r="B38" s="211"/>
-      <c r="C38" s="198"/>
+      <c r="A38" s="194"/>
+      <c r="B38" s="194"/>
+      <c r="C38" s="192"/>
       <c r="D38" s="175" t="s">
         <v>332</v>
       </c>
       <c r="E38" s="175">
         <v>46.2</v>
       </c>
-      <c r="F38" s="198"/>
-      <c r="G38" s="179"/>
-      <c r="H38" s="179"/>
+      <c r="F38" s="192"/>
+      <c r="G38" s="182"/>
+      <c r="H38" s="182"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="211"/>
-      <c r="B39" s="211"/>
-      <c r="C39" s="198"/>
+      <c r="A39" s="194"/>
+      <c r="B39" s="194"/>
+      <c r="C39" s="192"/>
       <c r="D39" s="175" t="s">
         <v>298</v>
       </c>
@@ -9868,27 +10944,12 @@
         <f>SUM(E12:E38)</f>
         <v>3847.3999999999996</v>
       </c>
-      <c r="F39" s="198"/>
-      <c r="G39" s="179"/>
-      <c r="H39" s="179"/>
+      <c r="F39" s="192"/>
+      <c r="G39" s="182"/>
+      <c r="H39" s="182"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A36:B39"/>
-    <mergeCell ref="G29:H39"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="F10:F39"/>
-    <mergeCell ref="C10:C39"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G15:H16"/>
-    <mergeCell ref="G22:H23"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="B8:D8"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B2:D2"/>
@@ -9903,13 +10964,28 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="A36:B39"/>
+    <mergeCell ref="G29:H39"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="F10:F39"/>
+    <mergeCell ref="C10:C39"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G15:H16"/>
+    <mergeCell ref="G22:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -10105,102 +11181,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.21875" style="149" customWidth="1"/>
-    <col min="2" max="2" width="51.5546875" style="142" customWidth="1"/>
-    <col min="3" max="3" width="21.109375" style="142" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" style="142" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="142"/>
-    <col min="6" max="6" width="17.77734375" style="142" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="142"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="141" t="s">
-        <v>122</v>
-      </c>
-      <c r="B1" s="141" t="s">
-        <v>271</v>
-      </c>
-      <c r="C1" s="141" t="s">
-        <v>270</v>
-      </c>
-      <c r="D1" s="141" t="s">
-        <v>49</v>
-      </c>
-      <c r="E1" s="141" t="s">
-        <v>126</v>
-      </c>
-      <c r="F1" s="141" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="130">
-        <v>1</v>
-      </c>
-      <c r="B2" s="143" t="s">
-        <v>108</v>
-      </c>
-      <c r="C2" s="144" t="s">
-        <v>265</v>
-      </c>
-      <c r="D2" s="144" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" s="145">
-        <v>1</v>
-      </c>
-      <c r="F2" s="162">
-        <f>'2-С-Ш1, баз'!F2</f>
-        <v>1350.87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="146" t="s">
-        <v>77</v>
-      </c>
-      <c r="B3" s="147" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="144"/>
-      <c r="D3" s="130" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="148">
-        <v>0.15</v>
-      </c>
-      <c r="F3" s="163">
-        <f>$F$2*E3</f>
-        <v>202.63049999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="146" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="147" t="s">
-        <v>201</v>
-      </c>
-      <c r="C4" s="144"/>
-      <c r="D4" s="130" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="148">
-        <v>1.5</v>
-      </c>
-      <c r="F4" s="163">
-        <f>$F$2*E4</f>
-        <v>2026.3049999999998</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>